--- a/Financial Analysis/ADBE.xlsx
+++ b/Financial Analysis/ADBE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23217A42-15B5-4FEF-8A70-521DBD133B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6725D35-F213-461F-9C5F-1CA12262B900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{030F5AE8-2ADC-4446-9A99-98294E370635}"/>
   </bookViews>
@@ -301,7 +301,7 @@
     <t>Service revenue y/y</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -851,14 +851,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>364.59</v>
+        <v>412.39</v>
       </c>
       <c r="E3" s="4">
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
         <v>45820</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>158961.24</v>
+        <v>179802.04</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>39</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>157681.24</v>
+        <v>178522.04</v>
       </c>
     </row>
   </sheetData>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="BD38" s="6">
         <f>Main!D3</f>
-        <v>364.59</v>
+        <v>412.39</v>
       </c>
     </row>
     <row r="39" spans="2:57" x14ac:dyDescent="0.3">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="BD39" s="13">
         <f>BD37/BD38-1</f>
-        <v>-3.1856995145475464E-2</v>
+        <v>-0.14407415761800457</v>
       </c>
     </row>
     <row r="40" spans="2:57" x14ac:dyDescent="0.3">

--- a/Financial Analysis/ADBE.xlsx
+++ b/Financial Analysis/ADBE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6725D35-F213-461F-9C5F-1CA12262B900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFF1873-C50F-4D46-9A99-FA0984226A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{030F5AE8-2ADC-4446-9A99-98294E370635}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="91">
   <si>
     <t>ADBE</t>
   </si>
@@ -190,9 +190,6 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>good fundamentals but seems overvalued, weird, perhaps too much investor confidence?</t>
-  </si>
-  <si>
     <t>Earnings</t>
   </si>
   <si>
@@ -301,7 +298,7 @@
     <t>Service revenue y/y</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -419,14 +416,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -443,8 +440,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23507700" y="0"/>
-          <a:ext cx="0" cy="7780020"/>
+          <a:off x="24452580" y="0"/>
+          <a:ext cx="0" cy="8328660"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -833,7 +830,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>36</v>
@@ -851,17 +848,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>412.39</v>
+        <v>362.17</v>
       </c>
       <c r="E3" s="4">
-        <v>45804</v>
+        <v>45909</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45909</v>
       </c>
       <c r="G3" s="4">
-        <v>45820</v>
+        <v>45911</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>37</v>
@@ -874,7 +871,8 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>436</v>
+        <f>424.2</f>
+        <v>424.2</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>75</v>
@@ -891,7 +889,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>179802.04</v>
+        <v>153632.514</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>39</v>
@@ -904,8 +902,8 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>6758+677</f>
-        <v>7435</v>
+        <f>4931+782</f>
+        <v>5713</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>75</v>
@@ -919,8 +917,8 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>6155</f>
-        <v>6155</v>
+        <f>6166</f>
+        <v>6166</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>75</v>
@@ -935,7 +933,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>1280</v>
+        <v>-453</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -944,7 +942,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>178522.04</v>
+        <v>154085.514</v>
       </c>
     </row>
   </sheetData>
@@ -954,7 +952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DC7478-B38A-4395-A8F9-36F32763DA56}">
-  <dimension ref="B1:FW44"/>
+  <dimension ref="B1:FW40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
@@ -1101,64 +1099,64 @@
         <v>22</v>
       </c>
       <c r="O2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="Q2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="S2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="V2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="W2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="X2" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="Y2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" s="7" t="s">
+      <c r="Z2" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="AA2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AB2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="AC2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" s="7" t="s">
+      <c r="AD2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" s="7" t="s">
+      <c r="AE2" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" s="7" t="s">
+      <c r="AF2" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" s="7" t="s">
+      <c r="AG2" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="AH2" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="AH2" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="AI2" s="7"/>
       <c r="AJ2">
@@ -1218,7 +1216,7 @@
     </row>
     <row r="3" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -1284,16 +1282,15 @@
         <v>5483</v>
       </c>
       <c r="AF3" s="14">
-        <f>AB3*1.12</f>
-        <v>5667.2000000000007</v>
+        <v>5641</v>
       </c>
       <c r="AG3" s="14">
-        <f t="shared" ref="AG3:AH3" si="0">AC3*1.12</f>
-        <v>5801.6</v>
+        <f>AC3*1.11</f>
+        <v>5749.8</v>
       </c>
       <c r="AH3" s="14">
-        <f t="shared" si="0"/>
-        <v>6008.8</v>
+        <f>AD3*1.1</f>
+        <v>5901.5000000000009</v>
       </c>
       <c r="AI3" s="7"/>
       <c r="AM3" s="5">
@@ -1314,12 +1311,12 @@
       </c>
       <c r="AQ3" s="5">
         <f>SUM(AE3:AH3)</f>
-        <v>22960.600000000002</v>
+        <v>22775.3</v>
       </c>
     </row>
     <row r="4" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -1385,8 +1382,7 @@
         <v>95</v>
       </c>
       <c r="AF4" s="14">
-        <f>AB4*0.8</f>
-        <v>83.2</v>
+        <v>88</v>
       </c>
       <c r="AG4" s="14">
         <f>AC4*1.02</f>
@@ -1415,12 +1411,12 @@
       </c>
       <c r="AQ4" s="5">
         <f>SUM(AE4:AH4)</f>
-        <v>344.46</v>
+        <v>349.26</v>
       </c>
     </row>
     <row r="5" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -1486,15 +1482,14 @@
         <v>136</v>
       </c>
       <c r="AF5" s="14">
-        <f>AB5*0.95</f>
-        <v>137.75</v>
+        <v>144</v>
       </c>
       <c r="AG5" s="14">
-        <f t="shared" ref="AG5:AH5" si="1">AC5*0.95</f>
+        <f t="shared" ref="AG5:AH5" si="0">AC5*0.95</f>
         <v>138.69999999999999</v>
       </c>
       <c r="AH5" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>152</v>
       </c>
       <c r="AI5" s="7"/>
@@ -1516,7 +1511,7 @@
       </c>
       <c r="AQ5" s="5">
         <f>SUM(AE5:AH5)</f>
-        <v>564.45000000000005</v>
+        <v>570.70000000000005</v>
       </c>
     </row>
     <row r="6" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1560,84 +1555,84 @@
         <v>3424</v>
       </c>
       <c r="O6" s="9">
-        <f t="shared" ref="O6:AE6" si="2">SUM(O3:O5)</f>
+        <f t="shared" ref="O6:AE6" si="1">SUM(O3:O5)</f>
         <v>3905</v>
       </c>
       <c r="P6" s="9">
+        <f t="shared" si="1"/>
+        <v>3835</v>
+      </c>
+      <c r="Q6" s="9">
+        <f t="shared" si="1"/>
+        <v>3935</v>
+      </c>
+      <c r="R6" s="9">
+        <f t="shared" si="1"/>
+        <v>4110</v>
+      </c>
+      <c r="S6" s="9">
+        <f t="shared" si="1"/>
+        <v>4262</v>
+      </c>
+      <c r="T6" s="9">
+        <f t="shared" si="1"/>
+        <v>4386</v>
+      </c>
+      <c r="U6" s="9">
+        <f t="shared" si="1"/>
+        <v>4433</v>
+      </c>
+      <c r="V6" s="9">
+        <f t="shared" si="1"/>
+        <v>4525</v>
+      </c>
+      <c r="W6" s="9">
+        <f t="shared" si="1"/>
+        <v>4655</v>
+      </c>
+      <c r="X6" s="9">
+        <f t="shared" si="1"/>
+        <v>4816</v>
+      </c>
+      <c r="Y6" s="9">
+        <f t="shared" si="1"/>
+        <v>4890</v>
+      </c>
+      <c r="Z6" s="9">
+        <f t="shared" si="1"/>
+        <v>5048</v>
+      </c>
+      <c r="AA6" s="9">
+        <f t="shared" si="1"/>
+        <v>5182</v>
+      </c>
+      <c r="AB6" s="9">
+        <f t="shared" si="1"/>
+        <v>5309</v>
+      </c>
+      <c r="AC6" s="9">
+        <f t="shared" si="1"/>
+        <v>5408</v>
+      </c>
+      <c r="AD6" s="9">
+        <f t="shared" si="1"/>
+        <v>5606</v>
+      </c>
+      <c r="AE6" s="9">
+        <f t="shared" si="1"/>
+        <v>5714</v>
+      </c>
+      <c r="AF6" s="9">
+        <f t="shared" ref="AF6:AH6" si="2">SUM(AF3:AF5)</f>
+        <v>5873</v>
+      </c>
+      <c r="AG6" s="9">
         <f t="shared" si="2"/>
-        <v>3835</v>
-      </c>
-      <c r="Q6" s="9">
+        <v>5972.14</v>
+      </c>
+      <c r="AH6" s="9">
         <f t="shared" si="2"/>
-        <v>3935</v>
-      </c>
-      <c r="R6" s="9">
-        <f t="shared" si="2"/>
-        <v>4110</v>
-      </c>
-      <c r="S6" s="9">
-        <f t="shared" si="2"/>
-        <v>4262</v>
-      </c>
-      <c r="T6" s="9">
-        <f t="shared" si="2"/>
-        <v>4386</v>
-      </c>
-      <c r="U6" s="9">
-        <f t="shared" si="2"/>
-        <v>4433</v>
-      </c>
-      <c r="V6" s="9">
-        <f t="shared" si="2"/>
-        <v>4525</v>
-      </c>
-      <c r="W6" s="9">
-        <f t="shared" si="2"/>
-        <v>4655</v>
-      </c>
-      <c r="X6" s="9">
-        <f t="shared" si="2"/>
-        <v>4816</v>
-      </c>
-      <c r="Y6" s="9">
-        <f t="shared" si="2"/>
-        <v>4890</v>
-      </c>
-      <c r="Z6" s="9">
-        <f t="shared" si="2"/>
-        <v>5048</v>
-      </c>
-      <c r="AA6" s="9">
-        <f t="shared" si="2"/>
-        <v>5182</v>
-      </c>
-      <c r="AB6" s="9">
-        <f t="shared" si="2"/>
-        <v>5309</v>
-      </c>
-      <c r="AC6" s="9">
-        <f t="shared" si="2"/>
-        <v>5408</v>
-      </c>
-      <c r="AD6" s="9">
-        <f t="shared" si="2"/>
-        <v>5606</v>
-      </c>
-      <c r="AE6" s="9">
-        <f t="shared" si="2"/>
-        <v>5714</v>
-      </c>
-      <c r="AF6" s="9">
-        <f t="shared" ref="AF6:AH6" si="3">SUM(AF3:AF5)</f>
-        <v>5888.1500000000005</v>
-      </c>
-      <c r="AG6" s="9">
-        <f t="shared" si="3"/>
-        <v>6023.9400000000005</v>
-      </c>
-      <c r="AH6" s="9">
-        <f t="shared" si="3"/>
-        <v>6243.42</v>
+        <v>6136.1200000000008</v>
       </c>
       <c r="AJ6" s="9">
         <f>SUM(C6:F6)</f>
@@ -1669,52 +1664,52 @@
       </c>
       <c r="AQ6" s="9">
         <f>SUM(AQ3:AQ5)</f>
-        <v>23869.510000000002</v>
+        <v>23695.26</v>
       </c>
       <c r="AR6" s="9">
         <f>AQ6*1.08</f>
-        <v>25779.070800000005</v>
+        <v>25590.880799999999</v>
       </c>
       <c r="AS6" s="9">
         <f>AR6*1.05</f>
-        <v>27068.024340000007</v>
+        <v>26870.42484</v>
       </c>
       <c r="AT6" s="9">
         <f>AS6*1.04</f>
-        <v>28150.745313600008</v>
+        <v>27945.241833600001</v>
       </c>
       <c r="AU6" s="9">
         <f>AT6*1.03</f>
-        <v>28995.267673008009</v>
+        <v>28783.599088608004</v>
       </c>
       <c r="AV6" s="9">
         <f>AU6*1.03</f>
-        <v>29865.12570319825</v>
+        <v>29647.107061266244</v>
       </c>
       <c r="AW6" s="9">
-        <f t="shared" ref="AW6" si="4">AV6*1.02</f>
-        <v>30462.428217262215</v>
+        <f t="shared" ref="AW6" si="3">AV6*1.02</f>
+        <v>30240.049202491569</v>
       </c>
       <c r="AX6" s="9">
-        <f t="shared" ref="AX6" si="5">AW6*1.02</f>
-        <v>31071.676781607461</v>
+        <f t="shared" ref="AX6" si="4">AW6*1.02</f>
+        <v>30844.8501865414</v>
       </c>
       <c r="AY6" s="9">
-        <f t="shared" ref="AY6" si="6">AX6*1.02</f>
-        <v>31693.110317239611</v>
+        <f t="shared" ref="AY6" si="5">AX6*1.02</f>
+        <v>31461.747190272228</v>
       </c>
       <c r="AZ6" s="9">
-        <f t="shared" ref="AZ6" si="7">AY6*1.02</f>
-        <v>32326.972523584402</v>
+        <f t="shared" ref="AZ6" si="6">AY6*1.02</f>
+        <v>32090.982134077673</v>
       </c>
       <c r="BA6" s="9">
-        <f t="shared" ref="BA6" si="8">AZ6*1.02</f>
-        <v>32973.511974056091</v>
+        <f t="shared" ref="BA6" si="7">AZ6*1.02</f>
+        <v>32732.801776759228</v>
       </c>
     </row>
     <row r="7" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -1779,9 +1774,11 @@
       <c r="AE7" s="5">
         <v>490</v>
       </c>
-      <c r="AF7" s="9"/>
-      <c r="AG7" s="9"/>
-      <c r="AH7" s="9"/>
+      <c r="AF7" s="5">
+        <v>505</v>
+      </c>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
       <c r="AJ7" s="9"/>
       <c r="AK7" s="9"/>
       <c r="AL7" s="9"/>
@@ -1803,7 +1800,7 @@
       </c>
       <c r="AQ7" s="5">
         <f>SUM(AE7:AH7)</f>
-        <v>490</v>
+        <v>995</v>
       </c>
       <c r="AR7" s="9"/>
       <c r="AS7" s="9"/>
@@ -1818,7 +1815,7 @@
     </row>
     <row r="8" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -1883,9 +1880,11 @@
       <c r="AE8" s="5">
         <v>6</v>
       </c>
-      <c r="AF8" s="9"/>
-      <c r="AG8" s="9"/>
-      <c r="AH8" s="9"/>
+      <c r="AF8" s="5">
+        <v>6</v>
+      </c>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
       <c r="AJ8" s="9"/>
       <c r="AK8" s="9"/>
       <c r="AL8" s="9"/>
@@ -1907,7 +1906,7 @@
       </c>
       <c r="AQ8" s="5">
         <f>SUM(AE8:AH8)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AR8" s="9"/>
       <c r="AS8" s="9"/>
@@ -1922,7 +1921,7 @@
     </row>
     <row r="9" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1987,9 +1986,11 @@
       <c r="AE9" s="5">
         <v>126</v>
       </c>
-      <c r="AF9" s="9"/>
-      <c r="AG9" s="9"/>
-      <c r="AH9" s="9"/>
+      <c r="AF9" s="5">
+        <v>127</v>
+      </c>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
       <c r="AJ9" s="9"/>
       <c r="AK9" s="9"/>
       <c r="AL9" s="9"/>
@@ -2011,7 +2012,7 @@
       </c>
       <c r="AQ9" s="5">
         <f>SUM(AE9:AH9)</f>
-        <v>126</v>
+        <v>253</v>
       </c>
       <c r="AR9" s="9"/>
       <c r="AS9" s="9"/>
@@ -2065,84 +2066,84 @@
         <v>428</v>
       </c>
       <c r="O10" s="5">
-        <f t="shared" ref="O10:AE10" si="9">SUM(O7:O9)</f>
+        <f t="shared" ref="O10:AF10" si="8">SUM(O7:O9)</f>
         <v>447</v>
       </c>
       <c r="P10" s="5">
+        <f t="shared" si="8"/>
+        <v>444</v>
+      </c>
+      <c r="Q10" s="5">
+        <f t="shared" si="8"/>
+        <v>467</v>
+      </c>
+      <c r="R10" s="5">
+        <f t="shared" si="8"/>
+        <v>507</v>
+      </c>
+      <c r="S10" s="5">
+        <f t="shared" si="8"/>
+        <v>512</v>
+      </c>
+      <c r="T10" s="5">
+        <f t="shared" si="8"/>
+        <v>539</v>
+      </c>
+      <c r="U10" s="5">
+        <f t="shared" si="8"/>
+        <v>546</v>
+      </c>
+      <c r="V10" s="5">
+        <f t="shared" si="8"/>
+        <v>568</v>
+      </c>
+      <c r="W10" s="5">
+        <f t="shared" si="8"/>
+        <v>568</v>
+      </c>
+      <c r="X10" s="5">
+        <f t="shared" si="8"/>
+        <v>572</v>
+      </c>
+      <c r="Y10" s="5">
+        <f t="shared" si="8"/>
+        <v>580</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" si="8"/>
+        <v>634</v>
+      </c>
+      <c r="AA10" s="5">
+        <f t="shared" si="8"/>
+        <v>590</v>
+      </c>
+      <c r="AB10" s="5">
+        <f t="shared" si="8"/>
+        <v>598</v>
+      </c>
+      <c r="AC10" s="5">
+        <f t="shared" si="8"/>
+        <v>554</v>
+      </c>
+      <c r="AD10" s="5">
+        <f t="shared" si="8"/>
+        <v>616</v>
+      </c>
+      <c r="AE10" s="5">
+        <f t="shared" si="8"/>
+        <v>622</v>
+      </c>
+      <c r="AF10" s="5">
+        <f t="shared" si="8"/>
+        <v>638</v>
+      </c>
+      <c r="AG10" s="5">
+        <f t="shared" ref="AG10:AH10" si="9">AG6-AG11</f>
+        <v>656.9354000000003</v>
+      </c>
+      <c r="AH10" s="5">
         <f t="shared" si="9"/>
-        <v>444</v>
-      </c>
-      <c r="Q10" s="5">
-        <f t="shared" si="9"/>
-        <v>467</v>
-      </c>
-      <c r="R10" s="5">
-        <f t="shared" si="9"/>
-        <v>507</v>
-      </c>
-      <c r="S10" s="5">
-        <f t="shared" si="9"/>
-        <v>512</v>
-      </c>
-      <c r="T10" s="5">
-        <f t="shared" si="9"/>
-        <v>539</v>
-      </c>
-      <c r="U10" s="5">
-        <f t="shared" si="9"/>
-        <v>546</v>
-      </c>
-      <c r="V10" s="5">
-        <f t="shared" si="9"/>
-        <v>568</v>
-      </c>
-      <c r="W10" s="5">
-        <f t="shared" si="9"/>
-        <v>568</v>
-      </c>
-      <c r="X10" s="5">
-        <f t="shared" si="9"/>
-        <v>572</v>
-      </c>
-      <c r="Y10" s="5">
-        <f t="shared" si="9"/>
-        <v>580</v>
-      </c>
-      <c r="Z10" s="5">
-        <f t="shared" si="9"/>
-        <v>634</v>
-      </c>
-      <c r="AA10" s="5">
-        <f t="shared" si="9"/>
-        <v>590</v>
-      </c>
-      <c r="AB10" s="5">
-        <f t="shared" si="9"/>
-        <v>598</v>
-      </c>
-      <c r="AC10" s="5">
-        <f t="shared" si="9"/>
-        <v>554</v>
-      </c>
-      <c r="AD10" s="5">
-        <f t="shared" si="9"/>
-        <v>616</v>
-      </c>
-      <c r="AE10" s="5">
-        <f t="shared" si="9"/>
-        <v>622</v>
-      </c>
-      <c r="AF10" s="5">
-        <f>AF6-AF11</f>
-        <v>647.69650000000001</v>
-      </c>
-      <c r="AG10" s="5">
-        <f t="shared" ref="AG10:AH10" si="10">AG6-AG11</f>
-        <v>662.63339999999971</v>
-      </c>
-      <c r="AH10" s="5">
-        <f t="shared" si="10"/>
-        <v>686.77620000000024</v>
+        <v>674.97320000000036</v>
       </c>
       <c r="AJ10" s="5">
         <f>SUM(C10:F10)</f>
@@ -2174,47 +2175,47 @@
       </c>
       <c r="AQ10" s="5">
         <f>SUM(AQ7:AQ9)</f>
-        <v>622</v>
+        <v>1260</v>
       </c>
       <c r="AR10" s="5">
-        <f t="shared" ref="AR10:AV10" si="11">AR6-AR11</f>
-        <v>2835.6977880000013</v>
+        <f t="shared" ref="AR10:AV10" si="10">AR6-AR11</f>
+        <v>2814.9968879999979</v>
       </c>
       <c r="AS10" s="5">
+        <f t="shared" si="10"/>
+        <v>2955.746732399999</v>
+      </c>
+      <c r="AT10" s="5">
+        <f t="shared" si="10"/>
+        <v>3073.9766016959984</v>
+      </c>
+      <c r="AU10" s="5">
+        <f t="shared" si="10"/>
+        <v>3166.1958997468791</v>
+      </c>
+      <c r="AV10" s="5">
+        <f t="shared" si="10"/>
+        <v>3261.1817767392859</v>
+      </c>
+      <c r="AW10" s="5">
+        <f t="shared" ref="AW10:BA10" si="11">AW6-AW11</f>
+        <v>3326.4054122740708</v>
+      </c>
+      <c r="AX10" s="5">
         <f t="shared" si="11"/>
-        <v>2977.4826773999994</v>
-      </c>
-      <c r="AT10" s="5">
+        <v>3392.933520519553</v>
+      </c>
+      <c r="AY10" s="5">
         <f t="shared" si="11"/>
-        <v>3096.5819844959988</v>
-      </c>
-      <c r="AU10" s="5">
+        <v>3460.7921909299439</v>
+      </c>
+      <c r="AZ10" s="5">
         <f t="shared" si="11"/>
-        <v>3189.4794440308797</v>
-      </c>
-      <c r="AV10" s="5">
+        <v>3530.0080347485418</v>
+      </c>
+      <c r="BA10" s="5">
         <f t="shared" si="11"/>
-        <v>3285.1638273518074</v>
-      </c>
-      <c r="AW10" s="5">
-        <f t="shared" ref="AW10:BA10" si="12">AW6-AW11</f>
-        <v>3350.8671038988432</v>
-      </c>
-      <c r="AX10" s="5">
-        <f t="shared" si="12"/>
-        <v>3417.8844459768188</v>
-      </c>
-      <c r="AY10" s="5">
-        <f t="shared" si="12"/>
-        <v>3486.242134896358</v>
-      </c>
-      <c r="AZ10" s="5">
-        <f t="shared" si="12"/>
-        <v>3555.9669775942821</v>
-      </c>
-      <c r="BA10" s="5">
-        <f t="shared" si="12"/>
-        <v>3627.0863171461679</v>
+        <v>3600.608195443514</v>
       </c>
     </row>
     <row r="11" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2222,204 +2223,204 @@
         <v>24</v>
       </c>
       <c r="C11" s="9">
-        <f t="shared" ref="C11:O11" si="13">C6-C10</f>
+        <f t="shared" ref="C11:O11" si="12">C6-C10</f>
         <v>1820.0499999999997</v>
       </c>
       <c r="D11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1914.0200000000002</v>
       </c>
       <c r="E11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1995.59</v>
       </c>
       <c r="F11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1824.8999999999999</v>
       </c>
       <c r="G11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2204</v>
       </c>
       <c r="H11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2337</v>
       </c>
       <c r="I11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2418</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2539.96</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2639</v>
       </c>
       <c r="L11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2713</v>
       </c>
       <c r="M11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2798</v>
       </c>
       <c r="N11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2996</v>
       </c>
       <c r="O11" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>3458</v>
       </c>
       <c r="P11" s="9">
-        <f t="shared" ref="P11" si="14">P6-P10</f>
+        <f t="shared" ref="P11" si="13">P6-P10</f>
         <v>3391</v>
       </c>
       <c r="Q11" s="9">
-        <f t="shared" ref="Q11" si="15">Q6-Q10</f>
+        <f t="shared" ref="Q11" si="14">Q6-Q10</f>
         <v>3468</v>
       </c>
       <c r="R11" s="9">
-        <f t="shared" ref="R11" si="16">R6-R10</f>
+        <f t="shared" ref="R11" si="15">R6-R10</f>
         <v>3603</v>
       </c>
       <c r="S11" s="9">
-        <f t="shared" ref="S11:U11" si="17">S6-S10</f>
+        <f t="shared" ref="S11:U11" si="16">S6-S10</f>
         <v>3750</v>
       </c>
       <c r="T11" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3847</v>
       </c>
       <c r="U11" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>3887</v>
       </c>
       <c r="V11" s="9">
-        <f t="shared" ref="V11" si="18">V6-V10</f>
+        <f t="shared" ref="V11" si="17">V6-V10</f>
         <v>3957</v>
       </c>
       <c r="W11" s="9">
-        <f t="shared" ref="W11:X11" si="19">W6-W10</f>
+        <f t="shared" ref="W11:X11" si="18">W6-W10</f>
         <v>4087</v>
       </c>
       <c r="X11" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>4244</v>
       </c>
       <c r="Y11" s="9">
-        <f t="shared" ref="Y11" si="20">Y6-Y10</f>
+        <f t="shared" ref="Y11" si="19">Y6-Y10</f>
         <v>4310</v>
       </c>
       <c r="Z11" s="9">
-        <f t="shared" ref="Z11" si="21">Z6-Z10</f>
+        <f t="shared" ref="Z11" si="20">Z6-Z10</f>
         <v>4414</v>
       </c>
       <c r="AA11" s="9">
-        <f t="shared" ref="AA11:AB11" si="22">AA6-AA10</f>
+        <f t="shared" ref="AA11:AB11" si="21">AA6-AA10</f>
         <v>4592</v>
       </c>
       <c r="AB11" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>4711</v>
       </c>
       <c r="AC11" s="9">
-        <f t="shared" ref="AC11" si="23">AC6-AC10</f>
+        <f t="shared" ref="AC11" si="22">AC6-AC10</f>
         <v>4854</v>
       </c>
       <c r="AD11" s="9">
-        <f t="shared" ref="AD11" si="24">AD6-AD10</f>
+        <f t="shared" ref="AD11" si="23">AD6-AD10</f>
         <v>4990</v>
       </c>
       <c r="AE11" s="9">
-        <f t="shared" ref="AE11" si="25">AE6-AE10</f>
+        <f t="shared" ref="AE11:AF11" si="24">AE6-AE10</f>
         <v>5092</v>
       </c>
       <c r="AF11" s="9">
-        <f>AF6*0.89</f>
-        <v>5240.4535000000005</v>
+        <f t="shared" si="24"/>
+        <v>5235</v>
       </c>
       <c r="AG11" s="9">
-        <f t="shared" ref="AG11:AH11" si="26">AG6*0.89</f>
-        <v>5361.3066000000008</v>
+        <f t="shared" ref="AG11:AH11" si="25">AG6*0.89</f>
+        <v>5315.2046</v>
       </c>
       <c r="AH11" s="9">
+        <f t="shared" si="25"/>
+        <v>5461.1468000000004</v>
+      </c>
+      <c r="AJ11" s="9">
+        <f t="shared" ref="AJ11:AP11" si="26">AJ6-AJ10</f>
+        <v>7554.5599999999995</v>
+      </c>
+      <c r="AK11" s="9">
         <f t="shared" si="26"/>
-        <v>5556.6437999999998</v>
-      </c>
-      <c r="AJ11" s="9">
-        <f t="shared" ref="AJ11:AP11" si="27">AJ6-AJ10</f>
-        <v>7554.5599999999995</v>
-      </c>
-      <c r="AK11" s="9">
-        <f t="shared" si="27"/>
         <v>9498.9600000000009</v>
       </c>
       <c r="AL11" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>11146</v>
       </c>
       <c r="AM11" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>13920</v>
       </c>
       <c r="AN11" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>15441</v>
       </c>
       <c r="AO11" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>17055</v>
       </c>
       <c r="AP11" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>19147</v>
       </c>
       <c r="AQ11" s="9">
-        <f t="shared" ref="AQ11" si="28">AQ6*0.88</f>
-        <v>21005.168800000003</v>
+        <f>AQ6*0.89</f>
+        <v>21088.7814</v>
       </c>
       <c r="AR11" s="9">
         <f>AR6*0.89</f>
-        <v>22943.373012000004</v>
+        <v>22775.883912000001</v>
       </c>
       <c r="AS11" s="9">
-        <f t="shared" ref="AS11:BA11" si="29">AS6*0.89</f>
-        <v>24090.541662600008</v>
+        <f t="shared" ref="AS11:BA11" si="27">AS6*0.89</f>
+        <v>23914.678107600001</v>
       </c>
       <c r="AT11" s="9">
-        <f t="shared" si="29"/>
-        <v>25054.163329104009</v>
+        <f t="shared" si="27"/>
+        <v>24871.265231904003</v>
       </c>
       <c r="AU11" s="9">
-        <f t="shared" si="29"/>
-        <v>25805.78822897713</v>
+        <f t="shared" si="27"/>
+        <v>25617.403188861124</v>
       </c>
       <c r="AV11" s="9">
-        <f t="shared" si="29"/>
-        <v>26579.961875846442</v>
+        <f t="shared" si="27"/>
+        <v>26385.925284526958</v>
       </c>
       <c r="AW11" s="9">
-        <f t="shared" si="29"/>
-        <v>27111.561113363372</v>
+        <f t="shared" si="27"/>
+        <v>26913.643790217498</v>
       </c>
       <c r="AX11" s="9">
-        <f t="shared" si="29"/>
-        <v>27653.792335630642</v>
+        <f t="shared" si="27"/>
+        <v>27451.916666021847</v>
       </c>
       <c r="AY11" s="9">
-        <f t="shared" si="29"/>
-        <v>28206.868182343253</v>
+        <f t="shared" si="27"/>
+        <v>28000.954999342284</v>
       </c>
       <c r="AZ11" s="9">
-        <f t="shared" si="29"/>
-        <v>28771.00554599012</v>
+        <f t="shared" si="27"/>
+        <v>28560.974099329131</v>
       </c>
       <c r="BA11" s="9">
-        <f t="shared" si="29"/>
-        <v>29346.425656909923</v>
+        <f t="shared" si="27"/>
+        <v>29132.193581315714</v>
       </c>
     </row>
     <row r="12" spans="2:53" x14ac:dyDescent="0.3">
@@ -2514,8 +2515,7 @@
         <v>1026</v>
       </c>
       <c r="AF12" s="5">
-        <f>AB12*1.09</f>
-        <v>1072.5600000000002</v>
+        <v>1082</v>
       </c>
       <c r="AG12" s="5">
         <f>AC12*1.07</f>
@@ -2555,47 +2555,47 @@
       </c>
       <c r="AQ12" s="5">
         <f>SUM(AE12:AH12)</f>
-        <v>4291</v>
+        <v>4300.4400000000005</v>
       </c>
       <c r="AR12" s="5">
         <f>AQ12*1.07</f>
-        <v>4591.37</v>
+        <v>4601.470800000001</v>
       </c>
       <c r="AS12" s="5">
         <f>AR12*1.05</f>
-        <v>4820.9385000000002</v>
+        <v>4831.5443400000013</v>
       </c>
       <c r="AT12" s="5">
         <f>AS12*1.04</f>
-        <v>5013.7760400000006</v>
+        <v>5024.8061136000015</v>
       </c>
       <c r="AU12" s="5">
         <f>AT12*1.03</f>
-        <v>5164.1893212000004</v>
+        <v>5175.5502970080015</v>
       </c>
       <c r="AV12" s="5">
-        <f t="shared" ref="AV12" si="30">AU12*1.02</f>
-        <v>5267.4731076240005</v>
+        <f t="shared" ref="AV12" si="28">AU12*1.02</f>
+        <v>5279.0613029481619</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" ref="AW12" si="31">AV12*1.02</f>
-        <v>5372.822569776481</v>
+        <f t="shared" ref="AW12" si="29">AV12*1.02</f>
+        <v>5384.6425290071256</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" ref="AX12" si="32">AW12*1.02</f>
-        <v>5480.2790211720112</v>
+        <f t="shared" ref="AX12" si="30">AW12*1.02</f>
+        <v>5492.3353795872681</v>
       </c>
       <c r="AY12" s="5">
-        <f t="shared" ref="AY12" si="33">AX12*1.02</f>
-        <v>5589.8846015954514</v>
+        <f t="shared" ref="AY12" si="31">AX12*1.02</f>
+        <v>5602.1820871790133</v>
       </c>
       <c r="AZ12" s="5">
-        <f t="shared" ref="AZ12" si="34">AY12*1.02</f>
-        <v>5701.6822936273602</v>
+        <f t="shared" ref="AZ12" si="32">AY12*1.02</f>
+        <v>5714.2257289225936</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" ref="BA12" si="35">AZ12*1.02</f>
-        <v>5815.7159394999071</v>
+        <f t="shared" ref="BA12" si="33">AZ12*1.02</f>
+        <v>5828.5102435010458</v>
       </c>
     </row>
     <row r="13" spans="2:53" x14ac:dyDescent="0.3">
@@ -2690,16 +2690,15 @@
         <v>1495</v>
       </c>
       <c r="AF13" s="5">
-        <f>AF6*0.26</f>
-        <v>1530.9190000000001</v>
+        <v>1626</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" ref="AG13:AH13" si="36">AG6*0.26</f>
-        <v>1566.2244000000003</v>
+        <f t="shared" ref="AG13:AH13" si="34">AG6*0.26</f>
+        <v>1552.7564000000002</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="36"/>
-        <v>1623.2892000000002</v>
+        <f t="shared" si="34"/>
+        <v>1595.3912000000003</v>
       </c>
       <c r="AJ13" s="5">
         <f>SUM(C13:F13)</f>
@@ -2731,47 +2730,47 @@
       </c>
       <c r="AQ13" s="5">
         <f>SUM(AE13:AH13)</f>
-        <v>6215.4326000000001</v>
+        <v>6269.1476000000002</v>
       </c>
       <c r="AR13" s="5">
         <f>AQ13*1.02</f>
-        <v>6339.7412519999998</v>
+        <v>6394.5305520000002</v>
       </c>
       <c r="AS13" s="5">
-        <f t="shared" ref="AS13:AV13" si="37">AR13*1.01</f>
-        <v>6403.13866452</v>
+        <f t="shared" ref="AS13:AV13" si="35">AR13*1.01</f>
+        <v>6458.4758575200003</v>
       </c>
       <c r="AT13" s="5">
-        <f t="shared" si="37"/>
-        <v>6467.1700511651998</v>
+        <f t="shared" si="35"/>
+        <v>6523.0606160952002</v>
       </c>
       <c r="AU13" s="5">
-        <f t="shared" si="37"/>
-        <v>6531.8417516768523</v>
+        <f t="shared" si="35"/>
+        <v>6588.2912222561527</v>
       </c>
       <c r="AV13" s="5">
-        <f t="shared" si="37"/>
-        <v>6597.1601691936212</v>
+        <f t="shared" si="35"/>
+        <v>6654.1741344787142</v>
       </c>
       <c r="AW13" s="5">
-        <f t="shared" ref="AW13:AW14" si="38">AV13*1.01</f>
-        <v>6663.1317708855577</v>
+        <f t="shared" ref="AW13:AW14" si="36">AV13*1.01</f>
+        <v>6720.7158758235018</v>
       </c>
       <c r="AX13" s="5">
-        <f t="shared" ref="AX13:AX14" si="39">AW13*1.01</f>
-        <v>6729.7630885944136</v>
+        <f t="shared" ref="AX13:AX14" si="37">AW13*1.01</f>
+        <v>6787.9230345817368</v>
       </c>
       <c r="AY13" s="5">
-        <f t="shared" ref="AY13:AY14" si="40">AX13*1.01</f>
-        <v>6797.0607194803579</v>
+        <f t="shared" ref="AY13:AY14" si="38">AX13*1.01</f>
+        <v>6855.8022649275545</v>
       </c>
       <c r="AZ13" s="5">
-        <f t="shared" ref="AZ13:AZ14" si="41">AY13*1.01</f>
-        <v>6865.0313266751618</v>
+        <f t="shared" ref="AZ13:AZ14" si="39">AY13*1.01</f>
+        <v>6924.3602875768302</v>
       </c>
       <c r="BA13" s="5">
-        <f t="shared" ref="BA13:BA14" si="42">AZ13*1.01</f>
-        <v>6933.6816399419131</v>
+        <f t="shared" ref="BA13:BA14" si="40">AZ13*1.01</f>
+        <v>6993.6038904525985</v>
       </c>
     </row>
     <row r="14" spans="2:53" x14ac:dyDescent="0.3">
@@ -2866,16 +2865,15 @@
         <v>367</v>
       </c>
       <c r="AF14" s="5">
-        <f>AB14*1.03</f>
-        <v>365.65000000000003</v>
+        <v>377</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" ref="AG14" si="43">AC14*1.03</f>
+        <f t="shared" ref="AG14" si="41">AC14*1.03</f>
         <v>376.98</v>
       </c>
       <c r="AH14" s="5">
-        <f>AD14*0.84</f>
-        <v>383.03999999999996</v>
+        <f>AD14*0.87</f>
+        <v>396.71999999999997</v>
       </c>
       <c r="AJ14" s="5">
         <f>SUM(C14:F14)</f>
@@ -2907,47 +2905,47 @@
       </c>
       <c r="AQ14" s="5">
         <f>SUM(AE14:AH14)</f>
-        <v>1492.67</v>
+        <v>1517.7</v>
       </c>
       <c r="AR14" s="5">
         <f>AQ14*1.02</f>
-        <v>1522.5234</v>
+        <v>1548.0540000000001</v>
       </c>
       <c r="AS14" s="5">
         <f>AR14*1.02</f>
-        <v>1552.973868</v>
+        <v>1579.0150800000001</v>
       </c>
       <c r="AT14" s="5">
-        <f t="shared" ref="AT14:AV14" si="44">AS14*1.01</f>
-        <v>1568.5036066800001</v>
+        <f t="shared" ref="AT14:AV14" si="42">AS14*1.01</f>
+        <v>1594.8052308000001</v>
       </c>
       <c r="AU14" s="5">
-        <f t="shared" si="44"/>
-        <v>1584.1886427468</v>
+        <f t="shared" si="42"/>
+        <v>1610.7532831080002</v>
       </c>
       <c r="AV14" s="5">
-        <f t="shared" si="44"/>
-        <v>1600.0305291742682</v>
+        <f t="shared" si="42"/>
+        <v>1626.8608159390803</v>
       </c>
       <c r="AW14" s="5">
+        <f t="shared" si="36"/>
+        <v>1643.1294240984712</v>
+      </c>
+      <c r="AX14" s="5">
+        <f t="shared" si="37"/>
+        <v>1659.5607183394559</v>
+      </c>
+      <c r="AY14" s="5">
         <f t="shared" si="38"/>
-        <v>1616.0308344660109</v>
-      </c>
-      <c r="AX14" s="5">
+        <v>1676.1563255228505</v>
+      </c>
+      <c r="AZ14" s="5">
         <f t="shared" si="39"/>
-        <v>1632.191142810671</v>
-      </c>
-      <c r="AY14" s="5">
+        <v>1692.917888778079</v>
+      </c>
+      <c r="BA14" s="5">
         <f t="shared" si="40"/>
-        <v>1648.5130542387776</v>
-      </c>
-      <c r="AZ14" s="5">
-        <f t="shared" si="41"/>
-        <v>1664.9981847811655</v>
-      </c>
-      <c r="BA14" s="5">
-        <f t="shared" si="42"/>
-        <v>1681.6481666289772</v>
+        <v>1709.8470676658599</v>
       </c>
     </row>
     <row r="15" spans="2:53" x14ac:dyDescent="0.3">
@@ -3043,7 +3041,7 @@
         <v>41</v>
       </c>
       <c r="AF15" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AG15" s="5">
         <v>42</v>
@@ -3081,47 +3079,47 @@
       </c>
       <c r="AQ15" s="5">
         <f>SUM(AE15:AH15)</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AR15" s="5">
-        <f t="shared" ref="AR15:AV15" si="45">AQ15*1.04</f>
-        <v>173.68</v>
+        <f t="shared" ref="AR15:AV15" si="43">AQ15*1.04</f>
+        <v>172.64000000000001</v>
       </c>
       <c r="AS15" s="5">
-        <f t="shared" si="45"/>
-        <v>180.62720000000002</v>
+        <f t="shared" si="43"/>
+        <v>179.54560000000001</v>
       </c>
       <c r="AT15" s="5">
-        <f t="shared" si="45"/>
-        <v>187.85228800000002</v>
+        <f t="shared" si="43"/>
+        <v>186.72742400000001</v>
       </c>
       <c r="AU15" s="5">
-        <f t="shared" si="45"/>
-        <v>195.36637952000001</v>
+        <f t="shared" si="43"/>
+        <v>194.19652096000002</v>
       </c>
       <c r="AV15" s="5">
-        <f t="shared" si="45"/>
-        <v>203.18103470080001</v>
+        <f t="shared" si="43"/>
+        <v>201.96438179840001</v>
       </c>
       <c r="AW15" s="5">
-        <f t="shared" ref="AW15" si="46">AV15*1.04</f>
-        <v>211.30827608883203</v>
+        <f t="shared" ref="AW15" si="44">AV15*1.04</f>
+        <v>210.04295707033603</v>
       </c>
       <c r="AX15" s="5">
-        <f t="shared" ref="AX15" si="47">AW15*1.04</f>
-        <v>219.76060713238533</v>
+        <f t="shared" ref="AX15" si="45">AW15*1.04</f>
+        <v>218.44467535314948</v>
       </c>
       <c r="AY15" s="5">
-        <f t="shared" ref="AY15" si="48">AX15*1.04</f>
-        <v>228.55103141768075</v>
+        <f t="shared" ref="AY15" si="46">AX15*1.04</f>
+        <v>227.18246236727546</v>
       </c>
       <c r="AZ15" s="5">
-        <f t="shared" ref="AZ15" si="49">AY15*1.04</f>
-        <v>237.69307267438799</v>
+        <f t="shared" ref="AZ15" si="47">AY15*1.04</f>
+        <v>236.26976086196649</v>
       </c>
       <c r="BA15" s="5">
-        <f t="shared" ref="BA15" si="50">AZ15*1.04</f>
-        <v>247.20079558136351</v>
+        <f t="shared" ref="BA15" si="48">AZ15*1.04</f>
+        <v>245.72055129644517</v>
       </c>
     </row>
     <row r="16" spans="2:53" x14ac:dyDescent="0.3">
@@ -3129,204 +3127,204 @@
         <v>29</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16:M16" si="51">SUM(C12:C15)</f>
+        <f t="shared" ref="C16:M16" si="49">SUM(C12:C15)</f>
         <v>1117.3100000000002</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1215.5400000000002</v>
       </c>
       <c r="E16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1276.9699999999998</v>
       </c>
       <c r="F16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1384.81</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1509</v>
       </c>
       <c r="H16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1587</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1564</v>
       </c>
       <c r="J16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1570.0100000000002</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1702</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1697</v>
       </c>
       <c r="M16" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1729</v>
       </c>
       <c r="N16" s="5">
-        <f t="shared" ref="N16:P16" si="52">SUM(N12:N15)</f>
+        <f t="shared" ref="N16:P16" si="50">SUM(N12:N15)</f>
         <v>1781</v>
       </c>
       <c r="O16" s="5">
-        <f t="shared" ref="O16" si="53">SUM(O12:O15)</f>
+        <f t="shared" ref="O16" si="51">SUM(O12:O15)</f>
         <v>2004</v>
       </c>
       <c r="P16" s="5">
+        <f t="shared" si="50"/>
+        <v>1985</v>
+      </c>
+      <c r="Q16" s="5">
+        <f t="shared" ref="Q16:T16" si="52">SUM(Q12:Q15)</f>
+        <v>2027</v>
+      </c>
+      <c r="R16" s="5">
         <f t="shared" si="52"/>
-        <v>1985</v>
-      </c>
-      <c r="Q16" s="5">
-        <f t="shared" ref="Q16:T16" si="54">SUM(Q12:Q15)</f>
-        <v>2027</v>
-      </c>
-      <c r="R16" s="5">
-        <f t="shared" si="54"/>
         <v>2102</v>
       </c>
       <c r="S16" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>2170</v>
       </c>
       <c r="T16" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>2318</v>
       </c>
       <c r="U16" s="5">
-        <f t="shared" ref="U16" si="55">SUM(U12:U15)</f>
+        <f t="shared" ref="U16" si="53">SUM(U12:U15)</f>
         <v>2403</v>
       </c>
       <c r="V16" s="5">
-        <f t="shared" ref="V16" si="56">SUM(V12:V15)</f>
+        <f t="shared" ref="V16" si="54">SUM(V12:V15)</f>
         <v>2452</v>
       </c>
       <c r="W16" s="5">
-        <f t="shared" ref="W16:X16" si="57">SUM(W12:W15)</f>
+        <f t="shared" ref="W16:X16" si="55">SUM(W12:W15)</f>
         <v>2501</v>
       </c>
       <c r="X16" s="5">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>2620</v>
       </c>
       <c r="Y16" s="5">
-        <f t="shared" ref="Y16" si="58">SUM(Y12:Y15)</f>
+        <f t="shared" ref="Y16" si="56">SUM(Y12:Y15)</f>
         <v>2613</v>
       </c>
       <c r="Z16" s="5">
-        <f t="shared" ref="Z16" si="59">SUM(Z12:Z15)</f>
+        <f t="shared" ref="Z16" si="57">SUM(Z12:Z15)</f>
         <v>2671</v>
       </c>
       <c r="AA16" s="5">
-        <f t="shared" ref="AA16:AB16" si="60">SUM(AA12:AA15)</f>
+        <f t="shared" ref="AA16:AB16" si="58">SUM(AA12:AA15)</f>
         <v>3685</v>
       </c>
       <c r="AB16" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2826</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" ref="AC16" si="61">SUM(AC12:AC15)</f>
+        <f t="shared" ref="AC16" si="59">SUM(AC12:AC15)</f>
         <v>2862</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" ref="AD16" si="62">SUM(AD12:AD15)</f>
+        <f t="shared" ref="AD16" si="60">SUM(AD12:AD15)</f>
         <v>3033</v>
       </c>
       <c r="AE16" s="5">
-        <f t="shared" ref="AE16:AH16" si="63">SUM(AE12:AE15)</f>
+        <f t="shared" ref="AE16:AH16" si="61">SUM(AE12:AE15)</f>
         <v>2929</v>
       </c>
       <c r="AF16" s="5">
-        <f t="shared" si="63"/>
-        <v>3011.1290000000004</v>
+        <f t="shared" si="61"/>
+        <v>3126</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="63"/>
-        <v>3078.7444</v>
+        <f t="shared" si="61"/>
+        <v>3065.2764000000002</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="63"/>
-        <v>3147.2292000000002</v>
+        <f t="shared" si="61"/>
+        <v>3133.0112000000004</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" ref="AJ16:AL16" si="64">SUM(AJ12:AJ15)</f>
+        <f t="shared" ref="AJ16:AL16" si="62">SUM(AJ12:AJ15)</f>
         <v>4994.630000000001</v>
       </c>
       <c r="AK16" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>6230.01</v>
       </c>
       <c r="AL16" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>6909</v>
       </c>
       <c r="AM16" s="5">
-        <f t="shared" ref="AM16" si="65">SUM(AM12:AM15)</f>
+        <f t="shared" ref="AM16" si="63">SUM(AM12:AM15)</f>
         <v>8118</v>
       </c>
       <c r="AN16" s="5">
-        <f t="shared" ref="AN16" si="66">SUM(AN12:AN15)</f>
+        <f t="shared" ref="AN16" si="64">SUM(AN12:AN15)</f>
         <v>9343</v>
       </c>
       <c r="AO16" s="5">
-        <f t="shared" ref="AO16" si="67">SUM(AO12:AO15)</f>
+        <f t="shared" ref="AO16" si="65">SUM(AO12:AO15)</f>
         <v>10405</v>
       </c>
       <c r="AP16" s="5">
-        <f t="shared" ref="AP16" si="68">SUM(AP12:AP15)</f>
+        <f t="shared" ref="AP16" si="66">SUM(AP12:AP15)</f>
         <v>12406</v>
       </c>
       <c r="AQ16" s="5">
-        <f t="shared" ref="AQ16" si="69">SUM(AQ12:AQ15)</f>
-        <v>12166.1026</v>
+        <f t="shared" ref="AQ16" si="67">SUM(AQ12:AQ15)</f>
+        <v>12253.287600000001</v>
       </c>
       <c r="AR16" s="5">
-        <f t="shared" ref="AR16" si="70">SUM(AR12:AR15)</f>
-        <v>12627.314651999999</v>
+        <f t="shared" ref="AR16" si="68">SUM(AR12:AR15)</f>
+        <v>12716.695352000001</v>
       </c>
       <c r="AS16" s="5">
-        <f t="shared" ref="AS16" si="71">SUM(AS12:AS15)</f>
-        <v>12957.678232520002</v>
+        <f t="shared" ref="AS16" si="69">SUM(AS12:AS15)</f>
+        <v>13048.58087752</v>
       </c>
       <c r="AT16" s="5">
-        <f t="shared" ref="AT16" si="72">SUM(AT12:AT15)</f>
-        <v>13237.301985845201</v>
+        <f t="shared" ref="AT16" si="70">SUM(AT12:AT15)</f>
+        <v>13329.399384495202</v>
       </c>
       <c r="AU16" s="5">
-        <f t="shared" ref="AU16" si="73">SUM(AU12:AU15)</f>
-        <v>13475.586095143652</v>
+        <f t="shared" ref="AU16" si="71">SUM(AU12:AU15)</f>
+        <v>13568.791323332156</v>
       </c>
       <c r="AV16" s="5">
-        <f t="shared" ref="AV16:BA16" si="74">SUM(AV12:AV15)</f>
-        <v>13667.844840692689</v>
+        <f t="shared" ref="AV16:BA16" si="72">SUM(AV12:AV15)</f>
+        <v>13762.060635164356</v>
       </c>
       <c r="AW16" s="5">
-        <f t="shared" si="74"/>
-        <v>13863.293451216883</v>
+        <f t="shared" si="72"/>
+        <v>13958.530785999435</v>
       </c>
       <c r="AX16" s="5">
-        <f t="shared" si="74"/>
-        <v>14061.993859709482</v>
+        <f t="shared" si="72"/>
+        <v>14158.263807861613</v>
       </c>
       <c r="AY16" s="5">
-        <f t="shared" si="74"/>
-        <v>14264.009406732268</v>
+        <f t="shared" si="72"/>
+        <v>14361.323139996692</v>
       </c>
       <c r="AZ16" s="5">
-        <f t="shared" si="74"/>
-        <v>14469.404877758076</v>
+        <f t="shared" si="72"/>
+        <v>14567.77366613947</v>
       </c>
       <c r="BA16" s="5">
-        <f t="shared" si="74"/>
-        <v>14678.246541652161</v>
+        <f t="shared" si="72"/>
+        <v>14777.681752915949</v>
       </c>
     </row>
     <row r="17" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3334,209 +3332,209 @@
         <v>30</v>
       </c>
       <c r="C17" s="9">
-        <f t="shared" ref="C17:M17" si="75">C11-C16</f>
+        <f t="shared" ref="C17:M17" si="73">C11-C16</f>
         <v>702.73999999999955</v>
       </c>
       <c r="D17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>698.48</v>
       </c>
       <c r="E17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>718.62000000000012</v>
       </c>
       <c r="F17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>440.08999999999992</v>
       </c>
       <c r="G17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>695</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>750</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>854</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>969.94999999999982</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>937</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1016</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1069</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" ref="N17:P17" si="76">N11-N16</f>
+        <f t="shared" ref="N17:P17" si="74">N11-N16</f>
         <v>1215</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" ref="O17" si="77">O11-O16</f>
+        <f t="shared" ref="O17" si="75">O11-O16</f>
         <v>1454</v>
       </c>
       <c r="P17" s="9">
+        <f t="shared" si="74"/>
+        <v>1406</v>
+      </c>
+      <c r="Q17" s="9">
+        <f t="shared" ref="Q17:T17" si="76">Q11-Q16</f>
+        <v>1441</v>
+      </c>
+      <c r="R17" s="9">
         <f t="shared" si="76"/>
-        <v>1406</v>
-      </c>
-      <c r="Q17" s="9">
-        <f t="shared" ref="Q17:T17" si="78">Q11-Q16</f>
-        <v>1441</v>
-      </c>
-      <c r="R17" s="9">
-        <f t="shared" si="78"/>
         <v>1501</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>1580</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>1529</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="79">U11-U16</f>
+        <f t="shared" ref="U17" si="77">U11-U16</f>
         <v>1484</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" ref="V17" si="80">V11-V16</f>
+        <f t="shared" ref="V17" si="78">V11-V16</f>
         <v>1505</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" ref="W17:X17" si="81">W11-W16</f>
+        <f t="shared" ref="W17:X17" si="79">W11-W16</f>
         <v>1586</v>
       </c>
       <c r="X17" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>1624</v>
       </c>
       <c r="Y17" s="9">
-        <f t="shared" ref="Y17" si="82">Y11-Y16</f>
+        <f t="shared" ref="Y17" si="80">Y11-Y16</f>
         <v>1697</v>
       </c>
       <c r="Z17" s="9">
-        <f t="shared" ref="Z17" si="83">Z11-Z16</f>
+        <f t="shared" ref="Z17" si="81">Z11-Z16</f>
         <v>1743</v>
       </c>
       <c r="AA17" s="9">
-        <f t="shared" ref="AA17:AB17" si="84">AA11-AA16</f>
+        <f t="shared" ref="AA17:AB17" si="82">AA11-AA16</f>
         <v>907</v>
       </c>
       <c r="AB17" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>1885</v>
       </c>
       <c r="AC17" s="9">
-        <f t="shared" ref="AC17" si="85">AC11-AC16</f>
+        <f t="shared" ref="AC17" si="83">AC11-AC16</f>
         <v>1992</v>
       </c>
       <c r="AD17" s="9">
-        <f t="shared" ref="AD17" si="86">AD11-AD16</f>
+        <f t="shared" ref="AD17" si="84">AD11-AD16</f>
         <v>1957</v>
       </c>
       <c r="AE17" s="9">
-        <f t="shared" ref="AE17:AH17" si="87">AE11-AE16</f>
+        <f t="shared" ref="AE17:AH17" si="85">AE11-AE16</f>
         <v>2163</v>
       </c>
       <c r="AF17" s="9">
-        <f t="shared" si="87"/>
-        <v>2229.3245000000002</v>
+        <f t="shared" si="85"/>
+        <v>2109</v>
       </c>
       <c r="AG17" s="9">
-        <f t="shared" si="87"/>
-        <v>2282.5622000000008</v>
+        <f t="shared" si="85"/>
+        <v>2249.9281999999998</v>
       </c>
       <c r="AH17" s="9">
-        <f t="shared" si="87"/>
-        <v>2409.4145999999996</v>
+        <f t="shared" si="85"/>
+        <v>2328.1356000000001</v>
       </c>
       <c r="AJ17" s="9">
-        <f t="shared" ref="AJ17:AL17" si="88">AJ11-AJ16</f>
+        <f t="shared" ref="AJ17:AL17" si="86">AJ11-AJ16</f>
         <v>2559.9299999999985</v>
       </c>
       <c r="AK17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>3268.9500000000007</v>
       </c>
       <c r="AL17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>4237</v>
       </c>
       <c r="AM17" s="9">
-        <f t="shared" ref="AM17" si="89">AM11-AM16</f>
+        <f t="shared" ref="AM17" si="87">AM11-AM16</f>
         <v>5802</v>
       </c>
       <c r="AN17" s="9">
-        <f t="shared" ref="AN17" si="90">AN11-AN16</f>
+        <f t="shared" ref="AN17" si="88">AN11-AN16</f>
         <v>6098</v>
       </c>
       <c r="AO17" s="9">
-        <f t="shared" ref="AO17" si="91">AO11-AO16</f>
+        <f t="shared" ref="AO17" si="89">AO11-AO16</f>
         <v>6650</v>
       </c>
       <c r="AP17" s="9">
-        <f t="shared" ref="AP17" si="92">AP11-AP16</f>
+        <f t="shared" ref="AP17" si="90">AP11-AP16</f>
         <v>6741</v>
       </c>
       <c r="AQ17" s="9">
-        <f t="shared" ref="AQ17" si="93">AQ11-AQ16</f>
-        <v>8839.0662000000029</v>
+        <f t="shared" ref="AQ17" si="91">AQ11-AQ16</f>
+        <v>8835.4937999999984</v>
       </c>
       <c r="AR17" s="9">
-        <f t="shared" ref="AR17" si="94">AR11-AR16</f>
-        <v>10316.058360000005</v>
+        <f t="shared" ref="AR17" si="92">AR11-AR16</f>
+        <v>10059.188560000001</v>
       </c>
       <c r="AS17" s="9">
-        <f t="shared" ref="AS17" si="95">AS11-AS16</f>
-        <v>11132.863430080006</v>
+        <f t="shared" ref="AS17" si="93">AS11-AS16</f>
+        <v>10866.09723008</v>
       </c>
       <c r="AT17" s="9">
-        <f t="shared" ref="AT17" si="96">AT11-AT16</f>
-        <v>11816.861343258808</v>
+        <f t="shared" ref="AT17" si="94">AT11-AT16</f>
+        <v>11541.865847408801</v>
       </c>
       <c r="AU17" s="9">
-        <f t="shared" ref="AU17" si="97">AU11-AU16</f>
-        <v>12330.202133833478</v>
+        <f t="shared" ref="AU17" si="95">AU11-AU16</f>
+        <v>12048.611865528968</v>
       </c>
       <c r="AV17" s="9">
-        <f t="shared" ref="AV17:BA17" si="98">AV11-AV16</f>
-        <v>12912.117035153753</v>
+        <f t="shared" ref="AV17:BA17" si="96">AV11-AV16</f>
+        <v>12623.864649362602</v>
       </c>
       <c r="AW17" s="9">
-        <f t="shared" si="98"/>
-        <v>13248.267662146489</v>
+        <f t="shared" si="96"/>
+        <v>12955.113004218063</v>
       </c>
       <c r="AX17" s="9">
-        <f t="shared" si="98"/>
-        <v>13591.798475921159</v>
+        <f t="shared" si="96"/>
+        <v>13293.652858160234</v>
       </c>
       <c r="AY17" s="9">
-        <f t="shared" si="98"/>
-        <v>13942.858775610985</v>
+        <f t="shared" si="96"/>
+        <v>13639.631859345593</v>
       </c>
       <c r="AZ17" s="9">
-        <f t="shared" si="98"/>
-        <v>14301.600668232044</v>
+        <f t="shared" si="96"/>
+        <v>13993.200433189661</v>
       </c>
       <c r="BA17" s="9">
-        <f t="shared" si="98"/>
-        <v>14668.179115257763</v>
+        <f t="shared" si="96"/>
+        <v>14354.511828399765</v>
       </c>
     </row>
     <row r="18" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -3602,16 +3600,13 @@
         <v>62</v>
       </c>
       <c r="AF18" s="5">
-        <f>AB18*1.03</f>
-        <v>42.230000000000004</v>
+        <v>68</v>
       </c>
       <c r="AG18" s="5">
-        <f t="shared" ref="AG18:AH18" si="99">AC18*1.03</f>
-        <v>52.53</v>
+        <v>60</v>
       </c>
       <c r="AH18" s="5">
-        <f t="shared" si="99"/>
-        <v>51.5</v>
+        <v>60</v>
       </c>
       <c r="AJ18" s="9"/>
       <c r="AK18" s="9"/>
@@ -3634,7 +3629,7 @@
       </c>
       <c r="AQ18" s="5">
         <f>SUM(AE18:AH18)</f>
-        <v>208.26</v>
+        <v>250</v>
       </c>
       <c r="AR18" s="9"/>
       <c r="AS18" s="9"/>
@@ -3649,7 +3644,7 @@
     </row>
     <row r="19" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -3715,7 +3710,7 @@
         <v>-6</v>
       </c>
       <c r="AF19" s="5">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="AG19" s="5">
         <v>-10</v>
@@ -3744,7 +3739,7 @@
       </c>
       <c r="AQ19" s="5">
         <f>SUM(AE19:AH19)</f>
-        <v>-36</v>
+        <v>-28</v>
       </c>
       <c r="AR19" s="9"/>
       <c r="AS19" s="9"/>
@@ -3825,15 +3820,14 @@
         <v>-75</v>
       </c>
       <c r="AF20" s="5">
-        <f>AB20*1.03</f>
-        <v>-84.460000000000008</v>
+        <v>-58</v>
       </c>
       <c r="AG20" s="5">
-        <f t="shared" ref="AG20:AH20" si="100">AC20*1.03</f>
+        <f t="shared" ref="AG20:AH20" si="97">AC20*1.03</f>
         <v>-91.67</v>
       </c>
       <c r="AH20" s="5">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>-72.100000000000009</v>
       </c>
       <c r="AJ20" s="9"/>
@@ -3857,7 +3851,7 @@
       </c>
       <c r="AQ20" s="5">
         <f>SUM(AE20:AH20)</f>
-        <v>-323.23</v>
+        <v>-296.77000000000004</v>
       </c>
       <c r="AR20" s="9"/>
       <c r="AS20" s="9"/>
@@ -3872,7 +3866,7 @@
     </row>
     <row r="21" spans="2:179" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" s="5">
         <v>0.23</v>
@@ -3911,84 +3905,84 @@
         <v>18</v>
       </c>
       <c r="O21" s="5">
-        <f t="shared" ref="O21:AE21" si="101">SUM(O18:O20)</f>
+        <f t="shared" ref="O21:AE21" si="98">SUM(O18:O20)</f>
         <v>21</v>
       </c>
       <c r="P21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>20</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>23</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>33</v>
       </c>
       <c r="S21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>37</v>
       </c>
       <c r="T21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>37</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>28</v>
       </c>
       <c r="V21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-12</v>
       </c>
       <c r="W21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-12</v>
       </c>
       <c r="X21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-26</v>
       </c>
       <c r="Y21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-46</v>
       </c>
       <c r="Z21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-65</v>
       </c>
       <c r="AA21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-61</v>
       </c>
       <c r="AB21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-45</v>
       </c>
       <c r="AC21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-50</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-34</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>-19</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" ref="AF21:AH21" si="102">SUM(AF18:AF20)</f>
-        <v>-52.230000000000004</v>
+        <f t="shared" ref="AF21:AH21" si="99">SUM(AF18:AF20)</f>
+        <v>8</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" si="102"/>
-        <v>-49.14</v>
+        <f t="shared" si="99"/>
+        <v>-41.67</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" si="102"/>
-        <v>-30.600000000000009</v>
+        <f t="shared" si="99"/>
+        <v>-22.100000000000009</v>
       </c>
       <c r="AJ21" s="5">
         <f>SUM(C21:F21)</f>
@@ -4007,60 +4001,60 @@
         <v>97</v>
       </c>
       <c r="AN21" s="5">
-        <f t="shared" ref="AN21:AQ21" si="103">SUM(AN18:AN20)</f>
+        <f t="shared" ref="AN21:AQ21" si="100">SUM(AN18:AN20)</f>
         <v>90</v>
       </c>
       <c r="AO21" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-149</v>
       </c>
       <c r="AP21" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>-190</v>
       </c>
       <c r="AQ21" s="5">
-        <f t="shared" si="103"/>
-        <v>-150.97000000000003</v>
+        <f t="shared" si="100"/>
+        <v>-74.770000000000039</v>
       </c>
       <c r="AR21" s="5">
-        <f t="shared" ref="AR21:AV21" si="104">AQ21*1.01</f>
-        <v>-152.47970000000004</v>
+        <f t="shared" ref="AR21:AV21" si="101">AQ21*1.01</f>
+        <v>-75.517700000000033</v>
       </c>
       <c r="AS21" s="5">
-        <f t="shared" si="104"/>
-        <v>-154.00449700000004</v>
+        <f t="shared" si="101"/>
+        <v>-76.272877000000037</v>
       </c>
       <c r="AT21" s="5">
-        <f t="shared" si="104"/>
-        <v>-155.54454197000004</v>
+        <f t="shared" si="101"/>
+        <v>-77.035605770000032</v>
       </c>
       <c r="AU21" s="5">
-        <f t="shared" si="104"/>
-        <v>-157.09998738970003</v>
+        <f t="shared" si="101"/>
+        <v>-77.805961827700031</v>
       </c>
       <c r="AV21" s="5">
-        <f t="shared" si="104"/>
-        <v>-158.67098726359703</v>
+        <f t="shared" si="101"/>
+        <v>-78.584021445977029</v>
       </c>
       <c r="AW21" s="5">
-        <f t="shared" ref="AW21" si="105">AV21*1.01</f>
-        <v>-160.25769713623299</v>
+        <f t="shared" ref="AW21" si="102">AV21*1.01</f>
+        <v>-79.369861660436797</v>
       </c>
       <c r="AX21" s="5">
-        <f t="shared" ref="AX21" si="106">AW21*1.01</f>
-        <v>-161.86027410759533</v>
+        <f t="shared" ref="AX21" si="103">AW21*1.01</f>
+        <v>-80.163560277041171</v>
       </c>
       <c r="AY21" s="5">
-        <f t="shared" ref="AY21" si="107">AX21*1.01</f>
-        <v>-163.47887684867129</v>
+        <f t="shared" ref="AY21" si="104">AX21*1.01</f>
+        <v>-80.965195879811588</v>
       </c>
       <c r="AZ21" s="5">
-        <f t="shared" ref="AZ21" si="108">AY21*1.01</f>
-        <v>-165.11366561715801</v>
+        <f t="shared" ref="AZ21" si="105">AY21*1.01</f>
+        <v>-81.774847838609702</v>
       </c>
       <c r="BA21" s="5">
-        <f t="shared" ref="BA21" si="109">AZ21*1.01</f>
-        <v>-166.76480227332959</v>
+        <f t="shared" ref="BA21" si="106">AZ21*1.01</f>
+        <v>-82.592596316995795</v>
       </c>
     </row>
     <row r="22" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4068,204 +4062,204 @@
         <v>32</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:AE22" si="110">C17-C21</f>
+        <f t="shared" ref="C22:AE22" si="107">C17-C21</f>
         <v>702.50999999999954</v>
       </c>
       <c r="D22" s="9">
+        <f t="shared" si="107"/>
+        <v>690.78</v>
+      </c>
+      <c r="E22" s="9">
+        <f t="shared" si="107"/>
+        <v>701.37000000000012</v>
+      </c>
+      <c r="F22" s="9">
+        <f t="shared" si="107"/>
+        <v>418.78999999999991</v>
+      </c>
+      <c r="G22" s="9">
+        <f t="shared" si="107"/>
+        <v>702</v>
+      </c>
+      <c r="H22" s="9">
+        <f t="shared" si="107"/>
+        <v>711</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="107"/>
+        <v>835</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="107"/>
+        <v>957.16999999999985</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="107"/>
+        <v>919</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="107"/>
+        <v>1000</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="107"/>
+        <v>1060</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="107"/>
+        <v>1197</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" si="107"/>
+        <v>1433</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="107"/>
+        <v>1386</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" si="107"/>
+        <v>1418</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="107"/>
+        <v>1468</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" si="107"/>
+        <v>1543</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" si="107"/>
+        <v>1492</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" si="107"/>
+        <v>1456</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="107"/>
+        <v>1517</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="107"/>
+        <v>1598</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" si="107"/>
+        <v>1650</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="107"/>
+        <v>1743</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" si="107"/>
+        <v>1808</v>
+      </c>
+      <c r="AA22" s="9">
+        <f t="shared" si="107"/>
+        <v>968</v>
+      </c>
+      <c r="AB22" s="9">
+        <f t="shared" si="107"/>
+        <v>1930</v>
+      </c>
+      <c r="AC22" s="9">
+        <f t="shared" si="107"/>
+        <v>2042</v>
+      </c>
+      <c r="AD22" s="9">
+        <f t="shared" si="107"/>
+        <v>1991</v>
+      </c>
+      <c r="AE22" s="9">
+        <f t="shared" si="107"/>
+        <v>2182</v>
+      </c>
+      <c r="AF22" s="9">
+        <f t="shared" ref="AF22:AH22" si="108">AF17-AF21</f>
+        <v>2101</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" si="108"/>
+        <v>2291.5981999999999</v>
+      </c>
+      <c r="AH22" s="9">
+        <f t="shared" si="108"/>
+        <v>2350.2356</v>
+      </c>
+      <c r="AJ22" s="9">
+        <f t="shared" ref="AJ22:AV22" si="109">AJ17-AJ21</f>
+        <v>2513.4499999999985</v>
+      </c>
+      <c r="AK22" s="9">
+        <f t="shared" si="109"/>
+        <v>3205.1700000000005</v>
+      </c>
+      <c r="AL22" s="9">
+        <f t="shared" si="109"/>
+        <v>4176</v>
+      </c>
+      <c r="AM22" s="9">
+        <f t="shared" si="109"/>
+        <v>5705</v>
+      </c>
+      <c r="AN22" s="9">
+        <f t="shared" si="109"/>
+        <v>6008</v>
+      </c>
+      <c r="AO22" s="9">
+        <f t="shared" si="109"/>
+        <v>6799</v>
+      </c>
+      <c r="AP22" s="9">
+        <f t="shared" si="109"/>
+        <v>6931</v>
+      </c>
+      <c r="AQ22" s="9">
+        <f t="shared" si="109"/>
+        <v>8910.2637999999988</v>
+      </c>
+      <c r="AR22" s="9">
+        <f t="shared" si="109"/>
+        <v>10134.706260000001</v>
+      </c>
+      <c r="AS22" s="9">
+        <f t="shared" si="109"/>
+        <v>10942.37010708</v>
+      </c>
+      <c r="AT22" s="9">
+        <f t="shared" si="109"/>
+        <v>11618.9014531788</v>
+      </c>
+      <c r="AU22" s="9">
+        <f t="shared" si="109"/>
+        <v>12126.417827356669</v>
+      </c>
+      <c r="AV22" s="9">
+        <f t="shared" si="109"/>
+        <v>12702.448670808579</v>
+      </c>
+      <c r="AW22" s="9">
+        <f t="shared" ref="AW22:BA22" si="110">AW17-AW21</f>
+        <v>13034.482865878499</v>
+      </c>
+      <c r="AX22" s="9">
         <f t="shared" si="110"/>
-        <v>690.78</v>
-      </c>
-      <c r="E22" s="9">
+        <v>13373.816418437276</v>
+      </c>
+      <c r="AY22" s="9">
         <f t="shared" si="110"/>
-        <v>701.37000000000012</v>
-      </c>
-      <c r="F22" s="9">
+        <v>13720.597055225404</v>
+      </c>
+      <c r="AZ22" s="9">
         <f t="shared" si="110"/>
-        <v>418.78999999999991</v>
-      </c>
-      <c r="G22" s="9">
+        <v>14074.97528102827</v>
+      </c>
+      <c r="BA22" s="9">
         <f t="shared" si="110"/>
-        <v>702</v>
-      </c>
-      <c r="H22" s="9">
-        <f t="shared" si="110"/>
-        <v>711</v>
-      </c>
-      <c r="I22" s="9">
-        <f t="shared" si="110"/>
-        <v>835</v>
-      </c>
-      <c r="J22" s="9">
-        <f t="shared" si="110"/>
-        <v>957.16999999999985</v>
-      </c>
-      <c r="K22" s="9">
-        <f t="shared" si="110"/>
-        <v>919</v>
-      </c>
-      <c r="L22" s="9">
-        <f t="shared" si="110"/>
-        <v>1000</v>
-      </c>
-      <c r="M22" s="9">
-        <f t="shared" si="110"/>
-        <v>1060</v>
-      </c>
-      <c r="N22" s="9">
-        <f t="shared" si="110"/>
-        <v>1197</v>
-      </c>
-      <c r="O22" s="9">
-        <f t="shared" si="110"/>
-        <v>1433</v>
-      </c>
-      <c r="P22" s="9">
-        <f t="shared" si="110"/>
-        <v>1386</v>
-      </c>
-      <c r="Q22" s="9">
-        <f t="shared" si="110"/>
-        <v>1418</v>
-      </c>
-      <c r="R22" s="9">
-        <f t="shared" si="110"/>
-        <v>1468</v>
-      </c>
-      <c r="S22" s="9">
-        <f t="shared" si="110"/>
-        <v>1543</v>
-      </c>
-      <c r="T22" s="9">
-        <f t="shared" si="110"/>
-        <v>1492</v>
-      </c>
-      <c r="U22" s="9">
-        <f t="shared" si="110"/>
-        <v>1456</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" si="110"/>
-        <v>1517</v>
-      </c>
-      <c r="W22" s="9">
-        <f t="shared" si="110"/>
-        <v>1598</v>
-      </c>
-      <c r="X22" s="9">
-        <f t="shared" si="110"/>
-        <v>1650</v>
-      </c>
-      <c r="Y22" s="9">
-        <f t="shared" si="110"/>
-        <v>1743</v>
-      </c>
-      <c r="Z22" s="9">
-        <f t="shared" si="110"/>
-        <v>1808</v>
-      </c>
-      <c r="AA22" s="9">
-        <f t="shared" si="110"/>
-        <v>968</v>
-      </c>
-      <c r="AB22" s="9">
-        <f t="shared" si="110"/>
-        <v>1930</v>
-      </c>
-      <c r="AC22" s="9">
-        <f t="shared" si="110"/>
-        <v>2042</v>
-      </c>
-      <c r="AD22" s="9">
-        <f t="shared" si="110"/>
-        <v>1991</v>
-      </c>
-      <c r="AE22" s="9">
-        <f t="shared" si="110"/>
-        <v>2182</v>
-      </c>
-      <c r="AF22" s="9">
-        <f t="shared" ref="AF22:AH22" si="111">AF17-AF21</f>
-        <v>2281.5545000000002</v>
-      </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="111"/>
-        <v>2331.7022000000006</v>
-      </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="111"/>
-        <v>2440.0145999999995</v>
-      </c>
-      <c r="AJ22" s="9">
-        <f t="shared" ref="AJ22:AV22" si="112">AJ17-AJ21</f>
-        <v>2513.4499999999985</v>
-      </c>
-      <c r="AK22" s="9">
-        <f t="shared" si="112"/>
-        <v>3205.1700000000005</v>
-      </c>
-      <c r="AL22" s="9">
-        <f t="shared" si="112"/>
-        <v>4176</v>
-      </c>
-      <c r="AM22" s="9">
-        <f t="shared" si="112"/>
-        <v>5705</v>
-      </c>
-      <c r="AN22" s="9">
-        <f t="shared" si="112"/>
-        <v>6008</v>
-      </c>
-      <c r="AO22" s="9">
-        <f t="shared" si="112"/>
-        <v>6799</v>
-      </c>
-      <c r="AP22" s="9">
-        <f t="shared" si="112"/>
-        <v>6931</v>
-      </c>
-      <c r="AQ22" s="9">
-        <f t="shared" si="112"/>
-        <v>8990.0362000000023</v>
-      </c>
-      <c r="AR22" s="9">
-        <f t="shared" si="112"/>
-        <v>10468.538060000004</v>
-      </c>
-      <c r="AS22" s="9">
-        <f t="shared" si="112"/>
-        <v>11286.867927080006</v>
-      </c>
-      <c r="AT22" s="9">
-        <f t="shared" si="112"/>
-        <v>11972.405885228809</v>
-      </c>
-      <c r="AU22" s="9">
-        <f t="shared" si="112"/>
-        <v>12487.302121223178</v>
-      </c>
-      <c r="AV22" s="9">
-        <f t="shared" si="112"/>
-        <v>13070.78802241735</v>
-      </c>
-      <c r="AW22" s="9">
-        <f t="shared" ref="AW22:BA22" si="113">AW17-AW21</f>
-        <v>13408.525359282721</v>
-      </c>
-      <c r="AX22" s="9">
-        <f t="shared" si="113"/>
-        <v>13753.658750028755</v>
-      </c>
-      <c r="AY22" s="9">
-        <f t="shared" si="113"/>
-        <v>14106.337652459655</v>
-      </c>
-      <c r="AZ22" s="9">
-        <f t="shared" si="113"/>
-        <v>14466.714333849202</v>
-      </c>
-      <c r="BA22" s="9">
-        <f t="shared" si="113"/>
-        <v>14834.943917531093</v>
+        <v>14437.104424716761</v>
       </c>
     </row>
     <row r="23" spans="2:179" x14ac:dyDescent="0.3">
@@ -4360,16 +4354,15 @@
         <v>371</v>
       </c>
       <c r="AF23" s="5">
-        <f>AF22*0.17</f>
-        <v>387.86426500000005</v>
+        <v>410</v>
       </c>
       <c r="AG23" s="5">
-        <f t="shared" ref="AG23:AH23" si="114">AG22*0.17</f>
-        <v>396.38937400000015</v>
+        <f t="shared" ref="AG23:AH23" si="111">AG22*0.17</f>
+        <v>389.57169400000004</v>
       </c>
       <c r="AH23" s="5">
-        <f t="shared" si="114"/>
-        <v>414.80248199999994</v>
+        <f t="shared" si="111"/>
+        <v>399.540052</v>
       </c>
       <c r="AJ23" s="5">
         <f>SUM(C23:F23)</f>
@@ -4401,47 +4394,47 @@
       </c>
       <c r="AQ23" s="5">
         <f>SUM(AE23:AH23)</f>
-        <v>1570.0561210000001</v>
+        <v>1570.111746</v>
       </c>
       <c r="AR23" s="5">
         <f>AR22*0.18</f>
-        <v>1884.3368508000008</v>
+        <v>1824.2471268000002</v>
       </c>
       <c r="AS23" s="5">
-        <f t="shared" ref="AS23:BA23" si="115">AS22*0.18</f>
-        <v>2031.636226874401</v>
+        <f t="shared" ref="AS23:BA23" si="112">AS22*0.18</f>
+        <v>1969.6266192743999</v>
       </c>
       <c r="AT23" s="5">
-        <f t="shared" si="115"/>
-        <v>2155.0330593411854</v>
+        <f t="shared" si="112"/>
+        <v>2091.4022615721838</v>
       </c>
       <c r="AU23" s="5">
-        <f t="shared" si="115"/>
-        <v>2247.7143818201721</v>
+        <f t="shared" si="112"/>
+        <v>2182.7552089242004</v>
       </c>
       <c r="AV23" s="5">
-        <f t="shared" si="115"/>
-        <v>2352.741844035123</v>
+        <f t="shared" si="112"/>
+        <v>2286.4407607455441</v>
       </c>
       <c r="AW23" s="5">
-        <f t="shared" si="115"/>
-        <v>2413.5345646708897</v>
+        <f t="shared" si="112"/>
+        <v>2346.2069158581298</v>
       </c>
       <c r="AX23" s="5">
-        <f t="shared" si="115"/>
-        <v>2475.6585750051759</v>
+        <f t="shared" si="112"/>
+        <v>2407.2869553187097</v>
       </c>
       <c r="AY23" s="5">
-        <f t="shared" si="115"/>
-        <v>2539.140777442738</v>
+        <f t="shared" si="112"/>
+        <v>2469.7074699405725</v>
       </c>
       <c r="AZ23" s="5">
-        <f t="shared" si="115"/>
-        <v>2604.0085800928564</v>
+        <f t="shared" si="112"/>
+        <v>2533.4955505850885</v>
       </c>
       <c r="BA23" s="5">
-        <f t="shared" si="115"/>
-        <v>2670.2899051555964</v>
+        <f t="shared" si="112"/>
+        <v>2598.6787964490168</v>
       </c>
     </row>
     <row r="24" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4449,708 +4442,708 @@
         <v>34</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:M24" si="116">C22-C23</f>
+        <f t="shared" ref="C24:M24" si="113">C22-C23</f>
         <v>583.07999999999947</v>
       </c>
       <c r="D24" s="9">
+        <f t="shared" si="113"/>
+        <v>663.15</v>
+      </c>
+      <c r="E24" s="9">
+        <f t="shared" si="113"/>
+        <v>666.30000000000007</v>
+      </c>
+      <c r="F24" s="9">
+        <f t="shared" si="113"/>
+        <v>397.80999999999989</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="113"/>
+        <v>674</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="113"/>
+        <v>633</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="113"/>
+        <v>793</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="113"/>
+        <v>851.88999999999987</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="113"/>
+        <v>955</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="113"/>
+        <v>1100</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="113"/>
+        <v>955</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" ref="N24:P24" si="114">N22-N23</f>
+        <v>2250</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" ref="O24" si="115">O22-O23</f>
+        <v>1261</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="114"/>
+        <v>1116</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" ref="Q24:T24" si="116">Q22-Q23</f>
+        <v>1212</v>
+      </c>
+      <c r="R24" s="9">
         <f t="shared" si="116"/>
-        <v>663.15</v>
-      </c>
-      <c r="E24" s="9">
+        <v>1233</v>
+      </c>
+      <c r="S24" s="9">
         <f t="shared" si="116"/>
-        <v>666.30000000000007</v>
-      </c>
-      <c r="F24" s="9">
+        <v>1266</v>
+      </c>
+      <c r="T24" s="9">
         <f t="shared" si="116"/>
-        <v>397.80999999999989</v>
-      </c>
-      <c r="G24" s="9">
-        <f t="shared" si="116"/>
-        <v>674</v>
-      </c>
-      <c r="H24" s="9">
-        <f t="shared" si="116"/>
-        <v>633</v>
-      </c>
-      <c r="I24" s="9">
-        <f t="shared" si="116"/>
-        <v>793</v>
-      </c>
-      <c r="J24" s="9">
-        <f t="shared" si="116"/>
-        <v>851.88999999999987</v>
-      </c>
-      <c r="K24" s="9">
-        <f t="shared" si="116"/>
-        <v>955</v>
-      </c>
-      <c r="L24" s="9">
-        <f t="shared" si="116"/>
-        <v>1100</v>
-      </c>
-      <c r="M24" s="9">
-        <f t="shared" si="116"/>
-        <v>955</v>
-      </c>
-      <c r="N24" s="9">
-        <f t="shared" ref="N24:P24" si="117">N22-N23</f>
-        <v>2250</v>
-      </c>
-      <c r="O24" s="9">
-        <f t="shared" ref="O24" si="118">O22-O23</f>
-        <v>1261</v>
-      </c>
-      <c r="P24" s="9">
-        <f t="shared" si="117"/>
-        <v>1116</v>
-      </c>
-      <c r="Q24" s="9">
-        <f t="shared" ref="Q24:T24" si="119">Q22-Q23</f>
-        <v>1212</v>
-      </c>
-      <c r="R24" s="9">
+        <v>1178</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" ref="U24" si="117">U22-U23</f>
+        <v>1136</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" ref="V24" si="118">V22-V23</f>
+        <v>1176</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" ref="W24:X24" si="119">W22-W23</f>
+        <v>1247</v>
+      </c>
+      <c r="X24" s="9">
         <f t="shared" si="119"/>
-        <v>1233</v>
-      </c>
-      <c r="S24" s="9">
-        <f t="shared" si="119"/>
-        <v>1266</v>
-      </c>
-      <c r="T24" s="9">
-        <f t="shared" si="119"/>
-        <v>1178</v>
-      </c>
-      <c r="U24" s="9">
-        <f t="shared" ref="U24" si="120">U22-U23</f>
-        <v>1136</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" ref="V24" si="121">V22-V23</f>
-        <v>1176</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" ref="W24:X24" si="122">W22-W23</f>
-        <v>1247</v>
-      </c>
-      <c r="X24" s="9">
+        <v>1295</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" ref="Y24" si="120">Y22-Y23</f>
+        <v>1403</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" ref="Z24" si="121">Z22-Z23</f>
+        <v>1483</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" ref="AA24:AB24" si="122">AA22-AA23</f>
+        <v>620</v>
+      </c>
+      <c r="AB24" s="9">
         <f t="shared" si="122"/>
-        <v>1295</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" ref="Y24" si="123">Y22-Y23</f>
-        <v>1403</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" ref="Z24" si="124">Z22-Z23</f>
-        <v>1483</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" ref="AA24:AB24" si="125">AA22-AA23</f>
-        <v>620</v>
-      </c>
-      <c r="AB24" s="9">
+        <v>1573</v>
+      </c>
+      <c r="AC24" s="9">
+        <f t="shared" ref="AC24" si="123">AC22-AC23</f>
+        <v>1684</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" ref="AD24" si="124">AD22-AD23</f>
+        <v>1683</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" ref="AE24:AH24" si="125">AE22-AE23</f>
+        <v>1811</v>
+      </c>
+      <c r="AF24" s="9">
         <f t="shared" si="125"/>
-        <v>1573</v>
-      </c>
-      <c r="AC24" s="9">
-        <f t="shared" ref="AC24" si="126">AC22-AC23</f>
-        <v>1684</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" ref="AD24" si="127">AD22-AD23</f>
-        <v>1683</v>
-      </c>
-      <c r="AE24" s="9">
-        <f t="shared" ref="AE24:AH24" si="128">AE22-AE23</f>
-        <v>1811</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="128"/>
-        <v>1893.690235</v>
+        <v>1691</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="128"/>
-        <v>1935.3128260000005</v>
+        <f t="shared" si="125"/>
+        <v>1902.0265059999999</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="128"/>
-        <v>2025.2121179999995</v>
+        <f t="shared" si="125"/>
+        <v>1950.6955479999999</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" ref="AJ24:AL24" si="129">AJ22-AJ23</f>
+        <f t="shared" ref="AJ24:AL24" si="126">AJ22-AJ23</f>
         <v>2310.3399999999983</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="126"/>
         <v>2951.8900000000003</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="126"/>
         <v>5260</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" ref="AM24" si="130">AM22-AM23</f>
+        <f t="shared" ref="AM24" si="127">AM22-AM23</f>
         <v>4822</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" ref="AN24" si="131">AN22-AN23</f>
+        <f t="shared" ref="AN24" si="128">AN22-AN23</f>
         <v>4756</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" ref="AO24" si="132">AO22-AO23</f>
+        <f t="shared" ref="AO24" si="129">AO22-AO23</f>
         <v>5428</v>
       </c>
       <c r="AP24" s="9">
-        <f t="shared" ref="AP24" si="133">AP22-AP23</f>
+        <f t="shared" ref="AP24" si="130">AP22-AP23</f>
         <v>5560</v>
       </c>
       <c r="AQ24" s="9">
-        <f t="shared" ref="AQ24" si="134">AQ22-AQ23</f>
-        <v>7419.9800790000027</v>
+        <f t="shared" ref="AQ24" si="131">AQ22-AQ23</f>
+        <v>7340.1520539999983</v>
       </c>
       <c r="AR24" s="9">
-        <f t="shared" ref="AR24" si="135">AR22-AR23</f>
-        <v>8584.2012092000041</v>
+        <f t="shared" ref="AR24" si="132">AR22-AR23</f>
+        <v>8310.4591332</v>
       </c>
       <c r="AS24" s="9">
-        <f t="shared" ref="AS24" si="136">AS22-AS23</f>
-        <v>9255.2317002056043</v>
+        <f t="shared" ref="AS24" si="133">AS22-AS23</f>
+        <v>8972.7434878055992</v>
       </c>
       <c r="AT24" s="9">
-        <f t="shared" ref="AT24" si="137">AT22-AT23</f>
-        <v>9817.3728258876235</v>
+        <f t="shared" ref="AT24" si="134">AT22-AT23</f>
+        <v>9527.4991916066156</v>
       </c>
       <c r="AU24" s="9">
-        <f t="shared" ref="AU24" si="138">AU22-AU23</f>
-        <v>10239.587739403007</v>
+        <f t="shared" ref="AU24" si="135">AU22-AU23</f>
+        <v>9943.6626184324687</v>
       </c>
       <c r="AV24" s="9">
-        <f t="shared" ref="AV24:BA24" si="139">AV22-AV23</f>
-        <v>10718.046178382227</v>
+        <f t="shared" ref="AV24:BA24" si="136">AV22-AV23</f>
+        <v>10416.007910063036</v>
       </c>
       <c r="AW24" s="9">
-        <f t="shared" si="139"/>
-        <v>10994.990794611831</v>
+        <f t="shared" si="136"/>
+        <v>10688.275950020368</v>
       </c>
       <c r="AX24" s="9">
-        <f t="shared" si="139"/>
-        <v>11278.000175023579</v>
+        <f t="shared" si="136"/>
+        <v>10966.529463118566</v>
       </c>
       <c r="AY24" s="9">
-        <f t="shared" si="139"/>
-        <v>11567.196875016918</v>
+        <f t="shared" si="136"/>
+        <v>11250.889585284831</v>
       </c>
       <c r="AZ24" s="9">
-        <f t="shared" si="139"/>
-        <v>11862.705753756345</v>
+        <f t="shared" si="136"/>
+        <v>11541.479730443181</v>
       </c>
       <c r="BA24" s="9">
-        <f t="shared" si="139"/>
-        <v>12164.654012375497</v>
+        <f t="shared" si="136"/>
+        <v>11838.425628267745</v>
       </c>
       <c r="BB24" s="1">
         <f>BA24*(1+$BD$32)</f>
-        <v>12043.007472251742</v>
+        <v>11720.041371985068</v>
       </c>
       <c r="BC24" s="1">
-        <f t="shared" ref="BC24:DN24" si="140">BB24*(1+$BD$32)</f>
-        <v>11922.577397529225</v>
+        <f t="shared" ref="BC24:DN24" si="137">BB24*(1+$BD$32)</f>
+        <v>11602.840958265217</v>
       </c>
       <c r="BD24" s="1">
-        <f t="shared" si="140"/>
-        <v>11803.351623553932</v>
+        <f t="shared" si="137"/>
+        <v>11486.812548682565</v>
       </c>
       <c r="BE24" s="1">
-        <f t="shared" si="140"/>
-        <v>11685.318107318393</v>
+        <f t="shared" si="137"/>
+        <v>11371.944423195739</v>
       </c>
       <c r="BF24" s="1">
-        <f t="shared" si="140"/>
-        <v>11568.464926245209</v>
+        <f t="shared" si="137"/>
+        <v>11258.224978963781</v>
       </c>
       <c r="BG24" s="1">
-        <f t="shared" si="140"/>
-        <v>11452.780276982758</v>
+        <f t="shared" si="137"/>
+        <v>11145.642729174142</v>
       </c>
       <c r="BH24" s="1">
-        <f t="shared" si="140"/>
-        <v>11338.25247421293</v>
+        <f t="shared" si="137"/>
+        <v>11034.186301882401</v>
       </c>
       <c r="BI24" s="1">
-        <f t="shared" si="140"/>
-        <v>11224.8699494708</v>
+        <f t="shared" si="137"/>
+        <v>10923.844438863576</v>
       </c>
       <c r="BJ24" s="1">
-        <f t="shared" si="140"/>
-        <v>11112.621249976091</v>
+        <f t="shared" si="137"/>
+        <v>10814.60599447494</v>
       </c>
       <c r="BK24" s="1">
-        <f t="shared" si="140"/>
-        <v>11001.49503747633</v>
+        <f t="shared" si="137"/>
+        <v>10706.45993453019</v>
       </c>
       <c r="BL24" s="1">
-        <f t="shared" si="140"/>
-        <v>10891.480087101567</v>
+        <f t="shared" si="137"/>
+        <v>10599.395335184889</v>
       </c>
       <c r="BM24" s="1">
-        <f t="shared" si="140"/>
-        <v>10782.565286230551</v>
+        <f t="shared" si="137"/>
+        <v>10493.40138183304</v>
       </c>
       <c r="BN24" s="1">
-        <f t="shared" si="140"/>
-        <v>10674.739633368245</v>
+        <f t="shared" si="137"/>
+        <v>10388.46736801471</v>
       </c>
       <c r="BO24" s="1">
-        <f t="shared" si="140"/>
-        <v>10567.992237034561</v>
+        <f t="shared" si="137"/>
+        <v>10284.582694334562</v>
       </c>
       <c r="BP24" s="1">
-        <f t="shared" si="140"/>
-        <v>10462.312314664216</v>
+        <f t="shared" si="137"/>
+        <v>10181.736867391217</v>
       </c>
       <c r="BQ24" s="1">
-        <f t="shared" si="140"/>
-        <v>10357.689191517573</v>
+        <f t="shared" si="137"/>
+        <v>10079.919498717305</v>
       </c>
       <c r="BR24" s="1">
-        <f t="shared" si="140"/>
-        <v>10254.112299602397</v>
+        <f t="shared" si="137"/>
+        <v>9979.1203037301311</v>
       </c>
       <c r="BS24" s="1">
-        <f t="shared" si="140"/>
-        <v>10151.571176606372</v>
+        <f t="shared" si="137"/>
+        <v>9879.3291006928303</v>
       </c>
       <c r="BT24" s="1">
-        <f t="shared" si="140"/>
-        <v>10050.055464840309</v>
+        <f t="shared" si="137"/>
+        <v>9780.5358096859018</v>
       </c>
       <c r="BU24" s="1">
-        <f t="shared" si="140"/>
-        <v>9949.5549101919059</v>
+        <f t="shared" si="137"/>
+        <v>9682.7304515890428</v>
       </c>
       <c r="BV24" s="1">
-        <f t="shared" si="140"/>
-        <v>9850.0593610899869</v>
+        <f t="shared" si="137"/>
+        <v>9585.9031470731516</v>
       </c>
       <c r="BW24" s="1">
-        <f t="shared" si="140"/>
-        <v>9751.5587674790877</v>
+        <f t="shared" si="137"/>
+        <v>9490.0441156024208</v>
       </c>
       <c r="BX24" s="1">
-        <f t="shared" si="140"/>
-        <v>9654.0431798042973</v>
+        <f t="shared" si="137"/>
+        <v>9395.1436744463972</v>
       </c>
       <c r="BY24" s="1">
-        <f t="shared" si="140"/>
-        <v>9557.5027480062545</v>
+        <f t="shared" si="137"/>
+        <v>9301.1922377019328</v>
       </c>
       <c r="BZ24" s="1">
-        <f t="shared" si="140"/>
-        <v>9461.9277205261915</v>
+        <f t="shared" si="137"/>
+        <v>9208.180315324913</v>
       </c>
       <c r="CA24" s="1">
-        <f t="shared" si="140"/>
-        <v>9367.3084433209297</v>
+        <f t="shared" si="137"/>
+        <v>9116.098512171664</v>
       </c>
       <c r="CB24" s="1">
-        <f t="shared" si="140"/>
-        <v>9273.6353588877209</v>
+        <f t="shared" si="137"/>
+        <v>9024.9375270499477</v>
       </c>
       <c r="CC24" s="1">
-        <f t="shared" si="140"/>
-        <v>9180.8990052988429</v>
+        <f t="shared" si="137"/>
+        <v>8934.6881517794482</v>
       </c>
       <c r="CD24" s="1">
-        <f t="shared" si="140"/>
-        <v>9089.0900152458544</v>
+        <f t="shared" si="137"/>
+        <v>8845.3412702616533</v>
       </c>
       <c r="CE24" s="1">
-        <f t="shared" si="140"/>
-        <v>8998.1991150933954</v>
+        <f t="shared" si="137"/>
+        <v>8756.887857559037</v>
       </c>
       <c r="CF24" s="1">
-        <f t="shared" si="140"/>
-        <v>8908.2171239424606</v>
+        <f t="shared" si="137"/>
+        <v>8669.3189789834469</v>
       </c>
       <c r="CG24" s="1">
-        <f t="shared" si="140"/>
-        <v>8819.1349527030361</v>
+        <f t="shared" si="137"/>
+        <v>8582.6257891936129</v>
       </c>
       <c r="CH24" s="1">
-        <f t="shared" si="140"/>
-        <v>8730.9436031760051</v>
+        <f t="shared" si="137"/>
+        <v>8496.7995313016763</v>
       </c>
       <c r="CI24" s="1">
-        <f t="shared" si="140"/>
-        <v>8643.6341671442442</v>
+        <f t="shared" si="137"/>
+        <v>8411.8315359886601</v>
       </c>
       <c r="CJ24" s="1">
-        <f t="shared" si="140"/>
-        <v>8557.1978254728019</v>
+        <f t="shared" si="137"/>
+        <v>8327.7132206287733</v>
       </c>
       <c r="CK24" s="1">
-        <f t="shared" si="140"/>
-        <v>8471.6258472180743</v>
+        <f t="shared" si="137"/>
+        <v>8244.4360884224861</v>
       </c>
       <c r="CL24" s="1">
-        <f t="shared" si="140"/>
-        <v>8386.9095887458934</v>
+        <f t="shared" si="137"/>
+        <v>8161.9917275382613</v>
       </c>
       <c r="CM24" s="1">
-        <f t="shared" si="140"/>
-        <v>8303.0404928584339</v>
+        <f t="shared" si="137"/>
+        <v>8080.3718102628791</v>
       </c>
       <c r="CN24" s="1">
-        <f t="shared" si="140"/>
-        <v>8220.0100879298498</v>
+        <f t="shared" si="137"/>
+        <v>7999.5680921602507</v>
       </c>
       <c r="CO24" s="1">
-        <f t="shared" si="140"/>
-        <v>8137.8099870505512</v>
+        <f t="shared" si="137"/>
+        <v>7919.5724112386479</v>
       </c>
       <c r="CP24" s="1">
-        <f t="shared" si="140"/>
-        <v>8056.431887180046</v>
+        <f t="shared" si="137"/>
+        <v>7840.3766871262615</v>
       </c>
       <c r="CQ24" s="1">
-        <f t="shared" si="140"/>
-        <v>7975.8675683082456</v>
+        <f t="shared" si="137"/>
+        <v>7761.9729202549988</v>
       </c>
       <c r="CR24" s="1">
-        <f t="shared" si="140"/>
-        <v>7896.1088926251632</v>
+        <f t="shared" si="137"/>
+        <v>7684.3531910524489</v>
       </c>
       <c r="CS24" s="1">
-        <f t="shared" si="140"/>
-        <v>7817.147803698912</v>
+        <f t="shared" si="137"/>
+        <v>7607.5096591419242</v>
       </c>
       <c r="CT24" s="1">
-        <f t="shared" si="140"/>
-        <v>7738.9763256619226</v>
+        <f t="shared" si="137"/>
+        <v>7531.4345625505048</v>
       </c>
       <c r="CU24" s="1">
-        <f t="shared" si="140"/>
-        <v>7661.5865624053031</v>
+        <f t="shared" si="137"/>
+        <v>7456.120216925</v>
       </c>
       <c r="CV24" s="1">
-        <f t="shared" si="140"/>
-        <v>7584.9706967812499</v>
+        <f t="shared" si="137"/>
+        <v>7381.5590147557496</v>
       </c>
       <c r="CW24" s="1">
-        <f t="shared" si="140"/>
-        <v>7509.1209898134375</v>
+        <f t="shared" si="137"/>
+        <v>7307.7434246081921</v>
       </c>
       <c r="CX24" s="1">
-        <f t="shared" si="140"/>
-        <v>7434.0297799153032</v>
+        <f t="shared" si="137"/>
+        <v>7234.6659903621103</v>
       </c>
       <c r="CY24" s="1">
-        <f t="shared" si="140"/>
-        <v>7359.6894821161504</v>
+        <f t="shared" si="137"/>
+        <v>7162.3193304584893</v>
       </c>
       <c r="CZ24" s="1">
-        <f t="shared" si="140"/>
-        <v>7286.0925872949892</v>
+        <f t="shared" si="137"/>
+        <v>7090.6961371539046</v>
       </c>
       <c r="DA24" s="1">
-        <f t="shared" si="140"/>
-        <v>7213.231661422039</v>
+        <f t="shared" si="137"/>
+        <v>7019.7891757823654</v>
       </c>
       <c r="DB24" s="1">
-        <f t="shared" si="140"/>
-        <v>7141.0993448078189</v>
+        <f t="shared" si="137"/>
+        <v>6949.5912840245419</v>
       </c>
       <c r="DC24" s="1">
-        <f t="shared" si="140"/>
-        <v>7069.6883513597404</v>
+        <f t="shared" si="137"/>
+        <v>6880.0953711842967</v>
       </c>
       <c r="DD24" s="1">
-        <f t="shared" si="140"/>
-        <v>6998.9914678461428</v>
+        <f t="shared" si="137"/>
+        <v>6811.2944174724535</v>
       </c>
       <c r="DE24" s="1">
-        <f t="shared" si="140"/>
-        <v>6929.0015531676809</v>
+        <f t="shared" si="137"/>
+        <v>6743.1814732977291</v>
       </c>
       <c r="DF24" s="1">
-        <f t="shared" si="140"/>
-        <v>6859.7115376360043</v>
+        <f t="shared" si="137"/>
+        <v>6675.7496585647514</v>
       </c>
       <c r="DG24" s="1">
-        <f t="shared" si="140"/>
-        <v>6791.114422259644</v>
+        <f t="shared" si="137"/>
+        <v>6608.9921619791039</v>
       </c>
       <c r="DH24" s="1">
-        <f t="shared" si="140"/>
-        <v>6723.2032780370473</v>
+        <f t="shared" si="137"/>
+        <v>6542.9022403593126</v>
       </c>
       <c r="DI24" s="1">
-        <f t="shared" si="140"/>
-        <v>6655.9712452566764</v>
+        <f t="shared" si="137"/>
+        <v>6477.4732179557195</v>
       </c>
       <c r="DJ24" s="1">
-        <f t="shared" si="140"/>
-        <v>6589.4115328041098</v>
+        <f t="shared" si="137"/>
+        <v>6412.6984857761627</v>
       </c>
       <c r="DK24" s="1">
-        <f t="shared" si="140"/>
-        <v>6523.5174174760687</v>
+        <f t="shared" si="137"/>
+        <v>6348.5715009184014</v>
       </c>
       <c r="DL24" s="1">
-        <f t="shared" si="140"/>
-        <v>6458.282243301308</v>
+        <f t="shared" si="137"/>
+        <v>6285.0857859092175</v>
       </c>
       <c r="DM24" s="1">
-        <f t="shared" si="140"/>
-        <v>6393.6994208682945</v>
+        <f t="shared" si="137"/>
+        <v>6222.2349280501248</v>
       </c>
       <c r="DN24" s="1">
-        <f t="shared" si="140"/>
-        <v>6329.7624266596113</v>
+        <f t="shared" si="137"/>
+        <v>6160.0125787696234</v>
       </c>
       <c r="DO24" s="1">
-        <f t="shared" ref="DO24:FW24" si="141">DN24*(1+$BD$32)</f>
-        <v>6266.4648023930149</v>
+        <f t="shared" ref="DO24:FW24" si="138">DN24*(1+$BD$32)</f>
+        <v>6098.4124529819273</v>
       </c>
       <c r="DP24" s="1">
-        <f t="shared" si="141"/>
-        <v>6203.8001543690843</v>
+        <f t="shared" si="138"/>
+        <v>6037.428328452108</v>
       </c>
       <c r="DQ24" s="1">
-        <f t="shared" si="141"/>
-        <v>6141.7621528253931</v>
+        <f t="shared" si="138"/>
+        <v>5977.054045167587</v>
       </c>
       <c r="DR24" s="1">
-        <f t="shared" si="141"/>
-        <v>6080.3445312971389</v>
+        <f t="shared" si="138"/>
+        <v>5917.2835047159115</v>
       </c>
       <c r="DS24" s="1">
-        <f t="shared" si="141"/>
-        <v>6019.5410859841677</v>
+        <f t="shared" si="138"/>
+        <v>5858.1106696687521</v>
       </c>
       <c r="DT24" s="1">
-        <f t="shared" si="141"/>
-        <v>5959.3456751243257</v>
+        <f t="shared" si="138"/>
+        <v>5799.5295629720649</v>
       </c>
       <c r="DU24" s="1">
-        <f t="shared" si="141"/>
-        <v>5899.7522183730825</v>
+        <f t="shared" si="138"/>
+        <v>5741.5342673423438</v>
       </c>
       <c r="DV24" s="1">
-        <f t="shared" si="141"/>
-        <v>5840.7546961893513</v>
+        <f t="shared" si="138"/>
+        <v>5684.11892466892</v>
       </c>
       <c r="DW24" s="1">
-        <f t="shared" si="141"/>
-        <v>5782.3471492274575</v>
+        <f t="shared" si="138"/>
+        <v>5627.2777354222308</v>
       </c>
       <c r="DX24" s="1">
-        <f t="shared" si="141"/>
-        <v>5724.5236777351829</v>
+        <f t="shared" si="138"/>
+        <v>5571.0049580680088</v>
       </c>
       <c r="DY24" s="1">
-        <f t="shared" si="141"/>
-        <v>5667.2784409578308</v>
+        <f t="shared" si="138"/>
+        <v>5515.2949084873289</v>
       </c>
       <c r="DZ24" s="1">
-        <f t="shared" si="141"/>
-        <v>5610.6056565482522</v>
+        <f t="shared" si="138"/>
+        <v>5460.1419594024555</v>
       </c>
       <c r="EA24" s="1">
-        <f t="shared" si="141"/>
-        <v>5554.4995999827697</v>
+        <f t="shared" si="138"/>
+        <v>5405.5405398084313</v>
       </c>
       <c r="EB24" s="1">
-        <f t="shared" si="141"/>
-        <v>5498.954603982942</v>
+        <f t="shared" si="138"/>
+        <v>5351.4851344103472</v>
       </c>
       <c r="EC24" s="1">
-        <f t="shared" si="141"/>
-        <v>5443.9650579431127</v>
+        <f t="shared" si="138"/>
+        <v>5297.9702830662436</v>
       </c>
       <c r="ED24" s="1">
-        <f t="shared" si="141"/>
-        <v>5389.5254073636816</v>
+        <f t="shared" si="138"/>
+        <v>5244.9905802355815</v>
       </c>
       <c r="EE24" s="1">
-        <f t="shared" si="141"/>
-        <v>5335.6301532900443</v>
+        <f t="shared" si="138"/>
+        <v>5192.5406744332258</v>
       </c>
       <c r="EF24" s="1">
-        <f t="shared" si="141"/>
-        <v>5282.2738517571433</v>
+        <f t="shared" si="138"/>
+        <v>5140.6152676888933</v>
       </c>
       <c r="EG24" s="1">
-        <f t="shared" si="141"/>
-        <v>5229.4511132395719</v>
+        <f t="shared" si="138"/>
+        <v>5089.2091150120041</v>
       </c>
       <c r="EH24" s="1">
-        <f t="shared" si="141"/>
-        <v>5177.1566021071758</v>
+        <f t="shared" si="138"/>
+        <v>5038.3170238618841</v>
       </c>
       <c r="EI24" s="1">
-        <f t="shared" si="141"/>
-        <v>5125.3850360861043</v>
+        <f t="shared" si="138"/>
+        <v>4987.9338536232653</v>
       </c>
       <c r="EJ24" s="1">
-        <f t="shared" si="141"/>
-        <v>5074.1311857252431</v>
+        <f t="shared" si="138"/>
+        <v>4938.054515087033</v>
       </c>
       <c r="EK24" s="1">
-        <f t="shared" si="141"/>
-        <v>5023.3898738679909</v>
+        <f t="shared" si="138"/>
+        <v>4888.6739699361624</v>
       </c>
       <c r="EL24" s="1">
-        <f t="shared" si="141"/>
-        <v>4973.1559751293107</v>
+        <f t="shared" si="138"/>
+        <v>4839.7872302368005</v>
       </c>
       <c r="EM24" s="1">
-        <f t="shared" si="141"/>
-        <v>4923.4244153780173</v>
+        <f t="shared" si="138"/>
+        <v>4791.3893579344322</v>
       </c>
       <c r="EN24" s="1">
-        <f t="shared" si="141"/>
-        <v>4874.190171224237</v>
+        <f t="shared" si="138"/>
+        <v>4743.4754643550878</v>
       </c>
       <c r="EO24" s="1">
-        <f t="shared" si="141"/>
-        <v>4825.448269511995</v>
+        <f t="shared" si="138"/>
+        <v>4696.0407097115367</v>
       </c>
       <c r="EP24" s="1">
-        <f t="shared" si="141"/>
-        <v>4777.1937868168752</v>
+        <f t="shared" si="138"/>
+        <v>4649.0803026144213</v>
       </c>
       <c r="EQ24" s="1">
-        <f t="shared" si="141"/>
-        <v>4729.4218489487066</v>
+        <f t="shared" si="138"/>
+        <v>4602.5894995882772</v>
       </c>
       <c r="ER24" s="1">
-        <f t="shared" si="141"/>
-        <v>4682.1276304592193</v>
+        <f t="shared" si="138"/>
+        <v>4556.5636045923948</v>
       </c>
       <c r="ES24" s="1">
-        <f t="shared" si="141"/>
-        <v>4635.3063541546271</v>
+        <f t="shared" si="138"/>
+        <v>4510.9979685464705</v>
       </c>
       <c r="ET24" s="1">
-        <f t="shared" si="141"/>
-        <v>4588.9532906130808</v>
+        <f t="shared" si="138"/>
+        <v>4465.8879888610054</v>
       </c>
       <c r="EU24" s="1">
-        <f t="shared" si="141"/>
-        <v>4543.0637577069501</v>
+        <f t="shared" si="138"/>
+        <v>4421.2291089723949</v>
       </c>
       <c r="EV24" s="1">
-        <f t="shared" si="141"/>
-        <v>4497.6331201298808</v>
+        <f t="shared" si="138"/>
+        <v>4377.0168178826707</v>
       </c>
       <c r="EW24" s="1">
-        <f t="shared" si="141"/>
-        <v>4452.6567889285816</v>
+        <f t="shared" si="138"/>
+        <v>4333.246649703844</v>
       </c>
       <c r="EX24" s="1">
-        <f t="shared" si="141"/>
-        <v>4408.130221039296</v>
+        <f t="shared" si="138"/>
+        <v>4289.9141832068053</v>
       </c>
       <c r="EY24" s="1">
-        <f t="shared" si="141"/>
-        <v>4364.048918828903</v>
+        <f t="shared" si="138"/>
+        <v>4247.0150413747369</v>
       </c>
       <c r="EZ24" s="1">
-        <f t="shared" si="141"/>
-        <v>4320.4084296406136</v>
+        <f t="shared" si="138"/>
+        <v>4204.5448909609895</v>
       </c>
       <c r="FA24" s="1">
-        <f t="shared" si="141"/>
-        <v>4277.2043453442075</v>
+        <f t="shared" si="138"/>
+        <v>4162.4994420513794</v>
       </c>
       <c r="FB24" s="1">
-        <f t="shared" si="141"/>
-        <v>4234.4323018907653</v>
+        <f t="shared" si="138"/>
+        <v>4120.8744476308657</v>
       </c>
       <c r="FC24" s="1">
-        <f t="shared" si="141"/>
-        <v>4192.0879788718576</v>
+        <f t="shared" si="138"/>
+        <v>4079.6657031545569</v>
       </c>
       <c r="FD24" s="1">
-        <f t="shared" si="141"/>
-        <v>4150.167099083139</v>
+        <f t="shared" si="138"/>
+        <v>4038.8690461230112</v>
       </c>
       <c r="FE24" s="1">
-        <f t="shared" si="141"/>
-        <v>4108.6654280923076</v>
+        <f t="shared" si="138"/>
+        <v>3998.4803556617812</v>
       </c>
       <c r="FF24" s="1">
-        <f t="shared" si="141"/>
-        <v>4067.5787738113845</v>
+        <f t="shared" si="138"/>
+        <v>3958.4955521051634</v>
       </c>
       <c r="FG24" s="1">
-        <f t="shared" si="141"/>
-        <v>4026.9029860732708</v>
+        <f t="shared" si="138"/>
+        <v>3918.9105965841118</v>
       </c>
       <c r="FH24" s="1">
-        <f t="shared" si="141"/>
-        <v>3986.6339562125381</v>
+        <f t="shared" si="138"/>
+        <v>3879.7214906182708</v>
       </c>
       <c r="FI24" s="1">
-        <f t="shared" si="141"/>
-        <v>3946.7676166504125</v>
+        <f t="shared" si="138"/>
+        <v>3840.9242757120878</v>
       </c>
       <c r="FJ24" s="1">
-        <f t="shared" si="141"/>
-        <v>3907.2999404839084</v>
+        <f t="shared" si="138"/>
+        <v>3802.515032954967</v>
       </c>
       <c r="FK24" s="1">
-        <f t="shared" si="141"/>
-        <v>3868.2269410790691</v>
+        <f t="shared" si="138"/>
+        <v>3764.4898826254171</v>
       </c>
       <c r="FL24" s="1">
-        <f t="shared" si="141"/>
-        <v>3829.5446716682782</v>
+        <f t="shared" si="138"/>
+        <v>3726.8449837991629</v>
       </c>
       <c r="FM24" s="1">
-        <f t="shared" si="141"/>
-        <v>3791.2492249515954</v>
+        <f t="shared" si="138"/>
+        <v>3689.5765339611712</v>
       </c>
       <c r="FN24" s="1">
-        <f t="shared" si="141"/>
-        <v>3753.3367327020792</v>
+        <f t="shared" si="138"/>
+        <v>3652.6807686215593</v>
       </c>
       <c r="FO24" s="1">
-        <f t="shared" si="141"/>
-        <v>3715.8033653750585</v>
+        <f t="shared" si="138"/>
+        <v>3616.1539609353435</v>
       </c>
       <c r="FP24" s="1">
-        <f t="shared" si="141"/>
-        <v>3678.6453317213081</v>
+        <f t="shared" si="138"/>
+        <v>3579.9924213259901</v>
       </c>
       <c r="FQ24" s="1">
-        <f t="shared" si="141"/>
-        <v>3641.8588784040949</v>
+        <f t="shared" si="138"/>
+        <v>3544.1924971127301</v>
       </c>
       <c r="FR24" s="1">
-        <f t="shared" si="141"/>
-        <v>3605.440289620054</v>
+        <f t="shared" si="138"/>
+        <v>3508.7505721416028</v>
       </c>
       <c r="FS24" s="1">
-        <f t="shared" si="141"/>
-        <v>3569.3858867238537</v>
+        <f t="shared" si="138"/>
+        <v>3473.6630664201866</v>
       </c>
       <c r="FT24" s="1">
-        <f t="shared" si="141"/>
-        <v>3533.6920278566149</v>
+        <f t="shared" si="138"/>
+        <v>3438.9264357559846</v>
       </c>
       <c r="FU24" s="1">
-        <f t="shared" si="141"/>
-        <v>3498.3551075780488</v>
+        <f t="shared" si="138"/>
+        <v>3404.5371713984246</v>
       </c>
       <c r="FV24" s="1">
-        <f t="shared" si="141"/>
-        <v>3463.371556502268</v>
+        <f t="shared" si="138"/>
+        <v>3370.4917996844401</v>
       </c>
       <c r="FW24" s="1">
-        <f t="shared" si="141"/>
-        <v>3428.7378409372454</v>
+        <f t="shared" si="138"/>
+        <v>3336.7868816875957</v>
       </c>
     </row>
     <row r="25" spans="2:179" x14ac:dyDescent="0.3">
@@ -5245,13 +5238,16 @@
         <v>436</v>
       </c>
       <c r="AF25" s="5">
-        <v>436</v>
+        <f>424.2</f>
+        <v>424.2</v>
       </c>
       <c r="AG25" s="5">
-        <v>436</v>
+        <f>424.2</f>
+        <v>424.2</v>
       </c>
       <c r="AH25" s="5">
-        <v>436</v>
+        <f>424.2</f>
+        <v>424.2</v>
       </c>
       <c r="AJ25" s="5">
         <v>480</v>
@@ -5275,37 +5271,48 @@
         <v>478</v>
       </c>
       <c r="AQ25" s="5">
-        <v>436</v>
+        <f t="shared" ref="AQ25:BA25" si="139">424.2</f>
+        <v>424.2</v>
       </c>
       <c r="AR25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
       <c r="AS25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
       <c r="AT25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
       <c r="AU25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
       <c r="AV25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
       <c r="AW25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
       <c r="AX25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
       <c r="AY25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
       <c r="AZ25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
       <c r="BA25" s="5">
-        <v>436</v>
+        <f t="shared" si="139"/>
+        <v>424.2</v>
       </c>
     </row>
     <row r="26" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5313,289 +5320,289 @@
         <v>35</v>
       </c>
       <c r="C26" s="8">
-        <f t="shared" ref="C26:M26" si="142">C24/C25</f>
+        <f t="shared" ref="C26:M26" si="140">C24/C25</f>
         <v>1.2147499999999989</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.3815625</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.3881250000000001</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>0.82877083333333312</v>
       </c>
       <c r="G26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.4041666666666666</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.3187500000000001</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.6520833333333333</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.774770833333333</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.9895833333333333</v>
       </c>
       <c r="L26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>2.2916666666666665</v>
       </c>
       <c r="M26" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.9895833333333333</v>
       </c>
       <c r="N26" s="8">
-        <f t="shared" ref="N26:S26" si="143">N24/N25</f>
+        <f t="shared" ref="N26:S26" si="141">N24/N25</f>
         <v>4.6875</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" ref="O26" si="144">O24/O25</f>
+        <f t="shared" ref="O26" si="142">O24/O25</f>
         <v>2.8922018348623855</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>2.5596330275229358</v>
       </c>
       <c r="Q26" s="8">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>2.7798165137614679</v>
       </c>
       <c r="R26" s="8">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>2.8279816513761467</v>
       </c>
       <c r="S26" s="8">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>2.903669724770642</v>
       </c>
       <c r="T26" s="8">
-        <f t="shared" ref="T26" si="145">T24/T25</f>
+        <f t="shared" ref="T26" si="143">T24/T25</f>
         <v>2.7018348623853212</v>
       </c>
       <c r="U26" s="8">
-        <f t="shared" ref="U26" si="146">U24/U25</f>
+        <f t="shared" ref="U26" si="144">U24/U25</f>
         <v>2.6055045871559632</v>
       </c>
       <c r="V26" s="8">
-        <f t="shared" ref="V26" si="147">V24/V25</f>
+        <f t="shared" ref="V26" si="145">V24/V25</f>
         <v>2.6972477064220182</v>
       </c>
       <c r="W26" s="8">
-        <f t="shared" ref="W26:X26" si="148">W24/W25</f>
+        <f t="shared" ref="W26:X26" si="146">W24/W25</f>
         <v>2.8600917431192658</v>
       </c>
       <c r="X26" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="146"/>
         <v>2.9701834862385321</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" ref="Y26" si="149">Y24/Y25</f>
+        <f t="shared" ref="Y26" si="147">Y24/Y25</f>
         <v>3.2178899082568808</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" ref="Z26" si="150">Z24/Z25</f>
+        <f t="shared" ref="Z26" si="148">Z24/Z25</f>
         <v>3.4013761467889907</v>
       </c>
       <c r="AA26" s="8">
-        <f t="shared" ref="AA26:AB26" si="151">AA24/AA25</f>
+        <f t="shared" ref="AA26:AB26" si="149">AA24/AA25</f>
         <v>1.4220183486238531</v>
       </c>
       <c r="AB26" s="8">
-        <f t="shared" si="151"/>
+        <f t="shared" si="149"/>
         <v>3.6077981651376145</v>
       </c>
       <c r="AC26" s="8">
-        <f t="shared" ref="AC26" si="152">AC24/AC25</f>
+        <f t="shared" ref="AC26" si="150">AC24/AC25</f>
         <v>3.8623853211009176</v>
       </c>
       <c r="AD26" s="8">
-        <f t="shared" ref="AD26" si="153">AD24/AD25</f>
+        <f t="shared" ref="AD26" si="151">AD24/AD25</f>
         <v>3.8600917431192658</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" ref="AE26:AH26" si="154">AE24/AE25</f>
+        <f t="shared" ref="AE26:AH26" si="152">AE24/AE25</f>
         <v>4.1536697247706424</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" si="154"/>
-        <v>4.3433262270642201</v>
+        <f t="shared" si="152"/>
+        <v>3.9863272041489863</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" si="154"/>
-        <v>4.4387908853211018</v>
+        <f t="shared" si="152"/>
+        <v>4.4837965723715225</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="154"/>
-        <v>4.6449819220183475</v>
+        <f t="shared" si="152"/>
+        <v>4.5985279302215938</v>
       </c>
       <c r="AJ26" s="8">
-        <f t="shared" ref="AJ26:AL26" si="155">AJ24/AJ25</f>
+        <f t="shared" ref="AJ26:AL26" si="153">AJ24/AJ25</f>
         <v>4.8132083333333302</v>
       </c>
       <c r="AK26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="153"/>
         <v>6.1497708333333341</v>
       </c>
       <c r="AL26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="153"/>
         <v>10.958333333333334</v>
       </c>
       <c r="AM26" s="8">
-        <f t="shared" ref="AM26" si="156">AM24/AM25</f>
+        <f t="shared" ref="AM26" si="154">AM24/AM25</f>
         <v>10.087866108786612</v>
       </c>
       <c r="AN26" s="8">
-        <f t="shared" ref="AN26" si="157">AN24/AN25</f>
+        <f t="shared" ref="AN26" si="155">AN24/AN25</f>
         <v>9.94979079497908</v>
       </c>
       <c r="AO26" s="8">
-        <f t="shared" ref="AO26" si="158">AO24/AO25</f>
+        <f t="shared" ref="AO26" si="156">AO24/AO25</f>
         <v>11.355648535564853</v>
       </c>
       <c r="AP26" s="8">
-        <f t="shared" ref="AP26" si="159">AP24/AP25</f>
+        <f t="shared" ref="AP26" si="157">AP24/AP25</f>
         <v>11.631799163179917</v>
       </c>
       <c r="AQ26" s="8">
-        <f t="shared" ref="AQ26" si="160">AQ24/AQ25</f>
-        <v>17.018302933486243</v>
+        <f t="shared" ref="AQ26" si="158">AQ24/AQ25</f>
+        <v>17.303517336162184</v>
       </c>
       <c r="AR26" s="8">
-        <f t="shared" ref="AR26" si="161">AR24/AR25</f>
-        <v>19.688534883486248</v>
+        <f t="shared" ref="AR26" si="159">AR24/AR25</f>
+        <v>19.590898475247524</v>
       </c>
       <c r="AS26" s="8">
-        <f t="shared" ref="AS26" si="162">AS24/AS25</f>
-        <v>21.227595642673403</v>
+        <f t="shared" ref="AS26" si="160">AS24/AS25</f>
+        <v>21.152153436599715</v>
       </c>
       <c r="AT26" s="8">
-        <f t="shared" ref="AT26" si="163">AT24/AT25</f>
-        <v>22.516910151118402</v>
+        <f t="shared" ref="AT26" si="161">AT24/AT25</f>
+        <v>22.459922658195701</v>
       </c>
       <c r="AU26" s="8">
-        <f t="shared" ref="AU26" si="164">AU24/AU25</f>
-        <v>23.485292980282125</v>
+        <f t="shared" ref="AU26" si="162">AU24/AU25</f>
+        <v>23.440977412617794</v>
       </c>
       <c r="AV26" s="8">
-        <f t="shared" ref="AV26:BA26" si="165">AV24/AV25</f>
-        <v>24.582674721060151</v>
+        <f t="shared" ref="AV26:BA26" si="163">AV24/AV25</f>
+        <v>24.55447409255784</v>
       </c>
       <c r="AW26" s="8">
-        <f t="shared" si="165"/>
-        <v>25.217868794981264</v>
+        <f t="shared" si="163"/>
+        <v>25.196312942056505</v>
       </c>
       <c r="AX26" s="8">
-        <f t="shared" si="165"/>
-        <v>25.866972878494447</v>
+        <f t="shared" si="163"/>
+        <v>25.852261817818402</v>
       </c>
       <c r="AY26" s="8">
-        <f t="shared" si="165"/>
-        <v>26.530268061965408</v>
+        <f t="shared" si="163"/>
+        <v>26.522606283085409</v>
       </c>
       <c r="AZ26" s="8">
-        <f t="shared" si="165"/>
-        <v>27.208040719624645</v>
+        <f t="shared" si="163"/>
+        <v>27.207637271200333</v>
       </c>
       <c r="BA26" s="8">
-        <f t="shared" si="165"/>
-        <v>27.900582597191505</v>
+        <f t="shared" si="163"/>
+        <v>27.907651174605718</v>
       </c>
     </row>
     <row r="28" spans="2:179" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="S28" s="12">
-        <f t="shared" ref="S28:AH28" si="166">S3/O3-1</f>
+        <f t="shared" ref="S28:AH28" si="164">S3/O3-1</f>
         <v>0.1043526785714286</v>
       </c>
       <c r="T28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.15625</v>
       </c>
       <c r="U28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.12879409351927817</v>
       </c>
       <c r="V28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.11017838405036717</v>
       </c>
       <c r="W28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.10485093481556351</v>
       </c>
       <c r="X28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.10982800982800978</v>
       </c>
       <c r="Y28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.1218507751937985</v>
       </c>
       <c r="Z28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.12547258979206055</v>
       </c>
       <c r="AA28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.12417104962268466</v>
       </c>
       <c r="AB28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.12021253044055791</v>
       </c>
       <c r="AC28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.11854890952278119</v>
       </c>
       <c r="AD28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.12639093008608016</v>
       </c>
       <c r="AE28" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="164"/>
         <v>0.11533767290480057</v>
       </c>
       <c r="AF28" s="12">
-        <f t="shared" si="166"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="164"/>
+        <v>0.11482213438735167</v>
       </c>
       <c r="AG28" s="12">
-        <f t="shared" si="166"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="164"/>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AH28" s="12">
-        <f t="shared" si="166"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="164"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AN28" s="12">
-        <f t="shared" ref="AN28:AP30" si="167">AN3/AM3-1</f>
+        <f t="shared" ref="AN28:AP30" si="165">AN3/AM3-1</f>
         <v>0.12454539216359017</v>
       </c>
       <c r="AO28" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>0.11569441054430074</v>
       </c>
       <c r="AP28" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>0.12234740756945972</v>
       </c>
       <c r="AQ28" s="12">
-        <f t="shared" ref="AQ28:AQ30" si="168">AQ3/AP3-1</f>
-        <v>0.11888309536572295</v>
+        <f t="shared" ref="AQ28:AQ30" si="166">AQ3/AP3-1</f>
+        <v>0.10985332098825595</v>
       </c>
       <c r="AR28" s="12"/>
       <c r="AS28" s="12"/>
@@ -5610,87 +5617,87 @@
     </row>
     <row r="29" spans="2:179" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S29" s="12">
-        <f t="shared" ref="S29:AH29" si="169">S4/O4-1</f>
+        <f t="shared" ref="S29:AH29" si="167">S4/O4-1</f>
         <v>-6.4516129032258118E-2</v>
       </c>
       <c r="T29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-4.5751633986928053E-2</v>
       </c>
       <c r="U29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>5.8823529411764719E-2</v>
       </c>
       <c r="V29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-0.1015625</v>
       </c>
       <c r="W29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-0.17241379310344829</v>
       </c>
       <c r="X29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-0.1095890410958904</v>
       </c>
       <c r="Y29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-0.23809523809523814</v>
       </c>
       <c r="Z29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-8.6956521739129933E-3</v>
       </c>
       <c r="AA29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-8.3333333333333037E-3</v>
       </c>
       <c r="AB29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-0.19999999999999996</v>
       </c>
       <c r="AC29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-0.14583333333333337</v>
       </c>
       <c r="AD29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-0.28947368421052633</v>
       </c>
       <c r="AE29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-0.20168067226890751</v>
       </c>
       <c r="AF29" s="12">
-        <f t="shared" si="169"/>
-        <v>-0.19999999999999996</v>
+        <f t="shared" si="167"/>
+        <v>-0.15384615384615385</v>
       </c>
       <c r="AG29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH29" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>-4.1441441441441462E-2</v>
       </c>
       <c r="AO29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>-0.13533834586466165</v>
       </c>
       <c r="AP29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>-0.16086956521739126</v>
       </c>
       <c r="AQ29" s="12">
-        <f t="shared" si="168"/>
-        <v>-0.10761658031088084</v>
+        <f t="shared" si="166"/>
+        <v>-9.5181347150259055E-2</v>
       </c>
       <c r="AR29" s="12"/>
       <c r="AS29" s="12"/>
@@ -5705,87 +5712,87 @@
     </row>
     <row r="30" spans="2:179" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S30" s="12">
-        <f t="shared" ref="S30:AH30" si="170">S5/O5-1</f>
+        <f t="shared" ref="S30:AH30" si="168">S5/O5-1</f>
         <v>-4.216867469879515E-2</v>
       </c>
       <c r="T30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>4.9382716049382713E-2</v>
       </c>
       <c r="U30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>0.12578616352201255</v>
       </c>
       <c r="V30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>4.705882352941182E-2</v>
       </c>
       <c r="W30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>1.8867924528301883E-2</v>
       </c>
       <c r="X30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>-5.8823529411764497E-3</v>
       </c>
       <c r="Y30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>-8.9385474860335212E-2</v>
       </c>
       <c r="Z30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>-3.9325842696629199E-2</v>
       </c>
       <c r="AA30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>-9.259259259259256E-2</v>
       </c>
       <c r="AB30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>-0.14201183431952658</v>
       </c>
       <c r="AC30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>-0.10429447852760731</v>
       </c>
       <c r="AD30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>-6.4327485380117011E-2</v>
       </c>
       <c r="AE30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
         <v>-7.4829931972789088E-2</v>
       </c>
       <c r="AF30" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="168"/>
+        <v>-6.8965517241379448E-3</v>
+      </c>
+      <c r="AG30" s="12">
+        <f t="shared" si="168"/>
         <v>-5.0000000000000044E-2</v>
       </c>
-      <c r="AG30" s="12">
-        <f t="shared" si="170"/>
+      <c r="AH30" s="12">
+        <f t="shared" si="168"/>
         <v>-5.0000000000000044E-2</v>
       </c>
-      <c r="AH30" s="12">
-        <f t="shared" si="170"/>
-        <v>-5.0000000000000044E-2</v>
-      </c>
       <c r="AN30" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>4.4140030441400357E-2</v>
       </c>
       <c r="AO30" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>-3.0612244897959218E-2</v>
       </c>
       <c r="AP30" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>-0.10075187969924815</v>
       </c>
       <c r="AQ30" s="12">
-        <f t="shared" si="168"/>
-        <v>-5.6103678929765866E-2</v>
+        <f t="shared" si="166"/>
+        <v>-4.5652173913043437E-2</v>
       </c>
       <c r="AR30" s="12"/>
       <c r="AS30" s="12"/>
@@ -5803,183 +5810,183 @@
         <v>44</v>
       </c>
       <c r="G31" s="12">
-        <f t="shared" ref="G31:R31" si="171">G6/C6-1</f>
+        <f t="shared" ref="G31:R31" si="169">G6/C6-1</f>
         <v>0.25111234036412622</v>
       </c>
       <c r="H31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.24990889876831135</v>
+      </c>
+      <c r="I31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.23697121008432709</v>
+      </c>
+      <c r="J31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.36983554318364975</v>
+      </c>
+      <c r="K31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.18838908112264519</v>
+      </c>
+      <c r="L31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.13994169096209919</v>
+      </c>
+      <c r="M31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.13796753705010589</v>
+      </c>
+      <c r="N31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.14440797609577727</v>
+      </c>
+      <c r="O31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.26334519572953741</v>
+      </c>
+      <c r="P31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.22602301790281332</v>
+      </c>
+      <c r="Q31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.22015503875969</v>
+      </c>
+      <c r="R31" s="12">
+        <f t="shared" si="169"/>
+        <v>0.20035046728971961</v>
+      </c>
+      <c r="S31" s="12">
+        <f t="shared" ref="S31:AH31" si="170">S6/O6-1</f>
+        <v>9.1421254801536511E-2</v>
+      </c>
+      <c r="T31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.14367666232073018</v>
+      </c>
+      <c r="U31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.12655654383735704</v>
+      </c>
+      <c r="V31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.1009732360097324</v>
+      </c>
+      <c r="W31" s="12">
+        <f t="shared" si="170"/>
+        <v>9.2210229938995747E-2</v>
+      </c>
+      <c r="X31" s="12">
+        <f t="shared" si="170"/>
+        <v>9.8039215686274606E-2</v>
+      </c>
+      <c r="Y31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.1030904579291676</v>
+      </c>
+      <c r="Z31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.1155801104972376</v>
+      </c>
+      <c r="AA31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.11321160042964551</v>
+      </c>
+      <c r="AB31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.10236710963455153</v>
+      </c>
+      <c r="AC31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.10593047034764824</v>
+      </c>
+      <c r="AD31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.11053882725832009</v>
+      </c>
+      <c r="AE31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.10266306445387885</v>
+      </c>
+      <c r="AF31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.10623469579958567</v>
+      </c>
+      <c r="AG31" s="12">
+        <f t="shared" si="170"/>
+        <v>0.10431582840236686</v>
+      </c>
+      <c r="AH31" s="12">
+        <f t="shared" si="170"/>
+        <v>9.4562968248305568E-2</v>
+      </c>
+      <c r="AK31" s="12">
+        <f t="shared" ref="AK31:AV31" si="171">AK6/AJ6-1</f>
+        <v>0.2767445182895123</v>
+      </c>
+      <c r="AL31" s="12">
         <f t="shared" si="171"/>
-        <v>0.24990889876831135</v>
-      </c>
-      <c r="I31" s="12">
+        <v>0.15191738564525448</v>
+      </c>
+      <c r="AM31" s="12">
         <f t="shared" si="171"/>
-        <v>0.23697121008432709</v>
-      </c>
-      <c r="J31" s="12">
+        <v>0.22668635374572577</v>
+      </c>
+      <c r="AN31" s="12">
         <f t="shared" si="171"/>
-        <v>0.36983554318364975</v>
-      </c>
-      <c r="K31" s="12">
+        <v>0.11536268609439349</v>
+      </c>
+      <c r="AO31" s="12">
         <f t="shared" si="171"/>
-        <v>0.18838908112264519</v>
-      </c>
-      <c r="L31" s="12">
+        <v>0.10240826990798602</v>
+      </c>
+      <c r="AP31" s="12">
         <f t="shared" si="171"/>
-        <v>0.13994169096209919</v>
-      </c>
-      <c r="M31" s="12">
+        <v>0.10799113813179462</v>
+      </c>
+      <c r="AQ31" s="12">
         <f t="shared" si="171"/>
-        <v>0.13796753705010589</v>
-      </c>
-      <c r="N31" s="12">
+        <v>0.10184887235526618</v>
+      </c>
+      <c r="AR31" s="12">
         <f t="shared" si="171"/>
-        <v>0.14440797609577727</v>
-      </c>
-      <c r="O31" s="12">
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AS31" s="12">
         <f t="shared" si="171"/>
-        <v>0.26334519572953741</v>
-      </c>
-      <c r="P31" s="12">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AT31" s="12">
         <f t="shared" si="171"/>
-        <v>0.22602301790281332</v>
-      </c>
-      <c r="Q31" s="12">
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AU31" s="12">
         <f t="shared" si="171"/>
-        <v>0.22015503875969</v>
-      </c>
-      <c r="R31" s="12">
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AV31" s="12">
         <f t="shared" si="171"/>
-        <v>0.20035046728971961</v>
-      </c>
-      <c r="S31" s="12">
-        <f t="shared" ref="S31:AH31" si="172">S6/O6-1</f>
-        <v>9.1421254801536511E-2</v>
-      </c>
-      <c r="T31" s="12">
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AW31" s="12">
+        <f t="shared" ref="AW31:BA31" si="172">AW6/AV6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AX31" s="12">
         <f t="shared" si="172"/>
-        <v>0.14367666232073018</v>
-      </c>
-      <c r="U31" s="12">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AY31" s="12">
         <f t="shared" si="172"/>
-        <v>0.12655654383735704</v>
-      </c>
-      <c r="V31" s="12">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AZ31" s="12">
         <f t="shared" si="172"/>
-        <v>0.1009732360097324</v>
-      </c>
-      <c r="W31" s="12">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BA31" s="12">
         <f t="shared" si="172"/>
-        <v>9.2210229938995747E-2</v>
-      </c>
-      <c r="X31" s="12">
-        <f t="shared" si="172"/>
-        <v>9.8039215686274606E-2</v>
-      </c>
-      <c r="Y31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.1030904579291676</v>
-      </c>
-      <c r="Z31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.1155801104972376</v>
-      </c>
-      <c r="AA31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.11321160042964551</v>
-      </c>
-      <c r="AB31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.10236710963455153</v>
-      </c>
-      <c r="AC31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.10593047034764824</v>
-      </c>
-      <c r="AD31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.11053882725832009</v>
-      </c>
-      <c r="AE31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.10266306445387885</v>
-      </c>
-      <c r="AF31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.10908834055377681</v>
-      </c>
-      <c r="AG31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.11389423076923078</v>
-      </c>
-      <c r="AH31" s="12">
-        <f t="shared" si="172"/>
-        <v>0.11370317516946127</v>
-      </c>
-      <c r="AK31" s="12">
-        <f t="shared" ref="AK31:AV31" si="173">AK6/AJ6-1</f>
-        <v>0.2767445182895123</v>
-      </c>
-      <c r="AL31" s="12">
-        <f t="shared" si="173"/>
-        <v>0.15191738564525448</v>
-      </c>
-      <c r="AM31" s="12">
-        <f t="shared" si="173"/>
-        <v>0.22668635374572577</v>
-      </c>
-      <c r="AN31" s="12">
-        <f t="shared" si="173"/>
-        <v>0.11536268609439349</v>
-      </c>
-      <c r="AO31" s="12">
-        <f t="shared" si="173"/>
-        <v>0.10240826990798602</v>
-      </c>
-      <c r="AP31" s="12">
-        <f t="shared" si="173"/>
-        <v>0.10799113813179462</v>
-      </c>
-      <c r="AQ31" s="12">
-        <f t="shared" si="173"/>
-        <v>0.10995163915368522</v>
-      </c>
-      <c r="AR31" s="12">
-        <f t="shared" si="173"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AS31" s="12">
-        <f t="shared" si="173"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AT31" s="12">
-        <f t="shared" si="173"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AU31" s="12">
-        <f t="shared" si="173"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AV31" s="12">
-        <f t="shared" si="173"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AW31" s="12">
-        <f t="shared" ref="AW31:BA31" si="174">AW6/AV6-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AX31" s="12">
-        <f t="shared" si="174"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AY31" s="12">
-        <f t="shared" si="174"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AZ31" s="12">
-        <f t="shared" si="174"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BA31" s="12">
-        <f t="shared" si="174"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5988,203 +5995,203 @@
         <v>41</v>
       </c>
       <c r="C32" s="12">
-        <f t="shared" ref="C32:R32" si="175">C11/C6</f>
+        <f t="shared" ref="C32:R32" si="173">C11/C6</f>
         <v>0.87546598042280954</v>
       </c>
       <c r="D32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.87184789738357271</v>
+      </c>
+      <c r="E32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.8710258917191892</v>
+      </c>
+      <c r="F32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.83551571313456885</v>
+      </c>
+      <c r="G32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.8473663975394079</v>
+      </c>
+      <c r="H32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.85167638483965014</v>
+      </c>
+      <c r="I32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.85321100917431192</v>
+      </c>
+      <c r="J32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.84893413637974025</v>
+      </c>
+      <c r="K32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.85376900679391787</v>
+      </c>
+      <c r="L32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.86732736572890023</v>
+      </c>
+      <c r="M32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.86759689922480621</v>
+      </c>
+      <c r="N32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.875</v>
+      </c>
+      <c r="O32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.88553137003841231</v>
+      </c>
+      <c r="P32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.8842242503259452</v>
+      </c>
+      <c r="Q32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.88132147395171534</v>
+      </c>
+      <c r="R32" s="12">
+        <f t="shared" si="173"/>
+        <v>0.87664233576642336</v>
+      </c>
+      <c r="S32" s="12">
+        <f t="shared" ref="S32:AH32" si="174">S11/S6</f>
+        <v>0.87986860628812769</v>
+      </c>
+      <c r="T32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.87710898312813501</v>
+      </c>
+      <c r="U32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.87683284457478006</v>
+      </c>
+      <c r="V32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.87447513812154698</v>
+      </c>
+      <c r="W32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.87798066595059077</v>
+      </c>
+      <c r="X32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.8812292358803987</v>
+      </c>
+      <c r="Y32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.88139059304703471</v>
+      </c>
+      <c r="Z32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.87440570522979399</v>
+      </c>
+      <c r="AA32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.88614434581242763</v>
+      </c>
+      <c r="AB32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.88736108495008481</v>
+      </c>
+      <c r="AC32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.8975591715976331</v>
+      </c>
+      <c r="AD32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.89011773100249736</v>
+      </c>
+      <c r="AE32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.89114455722786134</v>
+      </c>
+      <c r="AF32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.89136727396560533</v>
+      </c>
+      <c r="AG32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="AH32" s="12">
+        <f t="shared" si="174"/>
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="AJ32" s="12">
+        <f t="shared" ref="AJ32:AV32" si="175">AJ11/AJ6</f>
+        <v>0.86342269030978736</v>
+      </c>
+      <c r="AK32" s="12">
         <f t="shared" si="175"/>
-        <v>0.87184789738357271</v>
-      </c>
-      <c r="E32" s="12">
+        <v>0.85032772533018708</v>
+      </c>
+      <c r="AL32" s="12">
         <f t="shared" si="175"/>
-        <v>0.8710258917191892</v>
-      </c>
-      <c r="F32" s="12">
+        <v>0.86617967050046629</v>
+      </c>
+      <c r="AM32" s="12">
         <f t="shared" si="175"/>
-        <v>0.83551571313456885</v>
-      </c>
-      <c r="G32" s="12">
+        <v>0.88184985745961353</v>
+      </c>
+      <c r="AN32" s="12">
         <f t="shared" si="175"/>
-        <v>0.8473663975394079</v>
-      </c>
-      <c r="H32" s="12">
+        <v>0.87703055776439853</v>
+      </c>
+      <c r="AO32" s="12">
         <f t="shared" si="175"/>
-        <v>0.85167638483965014</v>
-      </c>
-      <c r="I32" s="12">
+        <v>0.87871605955999799</v>
+      </c>
+      <c r="AP32" s="12">
         <f t="shared" si="175"/>
-        <v>0.85321100917431192</v>
-      </c>
-      <c r="J32" s="12">
+        <v>0.89035108114392003</v>
+      </c>
+      <c r="AQ32" s="12">
         <f t="shared" si="175"/>
-        <v>0.84893413637974025</v>
-      </c>
-      <c r="K32" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="AR32" s="12">
         <f t="shared" si="175"/>
-        <v>0.85376900679391787</v>
-      </c>
-      <c r="L32" s="12">
+        <v>0.89000000000000012</v>
+      </c>
+      <c r="AS32" s="12">
         <f t="shared" si="175"/>
-        <v>0.86732736572890023</v>
-      </c>
-      <c r="M32" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="AT32" s="12">
         <f t="shared" si="175"/>
-        <v>0.86759689922480621</v>
-      </c>
-      <c r="N32" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="AU32" s="12">
         <f t="shared" si="175"/>
-        <v>0.875</v>
-      </c>
-      <c r="O32" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="AV32" s="12">
         <f t="shared" si="175"/>
-        <v>0.88553137003841231</v>
-      </c>
-      <c r="P32" s="12">
-        <f t="shared" si="175"/>
-        <v>0.8842242503259452</v>
-      </c>
-      <c r="Q32" s="12">
-        <f t="shared" si="175"/>
-        <v>0.88132147395171534</v>
-      </c>
-      <c r="R32" s="12">
-        <f t="shared" si="175"/>
-        <v>0.87664233576642336</v>
-      </c>
-      <c r="S32" s="12">
-        <f t="shared" ref="S32:AH32" si="176">S11/S6</f>
-        <v>0.87986860628812769</v>
-      </c>
-      <c r="T32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.87710898312813501</v>
-      </c>
-      <c r="U32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.87683284457478006</v>
-      </c>
-      <c r="V32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.87447513812154698</v>
-      </c>
-      <c r="W32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.87798066595059077</v>
-      </c>
-      <c r="X32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.8812292358803987</v>
-      </c>
-      <c r="Y32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.88139059304703471</v>
-      </c>
-      <c r="Z32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.87440570522979399</v>
-      </c>
-      <c r="AA32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.88614434581242763</v>
-      </c>
-      <c r="AB32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.88736108495008481</v>
-      </c>
-      <c r="AC32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.8975591715976331</v>
-      </c>
-      <c r="AD32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.89011773100249736</v>
-      </c>
-      <c r="AE32" s="12">
-        <f t="shared" si="176"/>
-        <v>0.89114455722786134</v>
-      </c>
-      <c r="AF32" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="AW32" s="12">
+        <f t="shared" ref="AW32:BA32" si="176">AW11/AW6</f>
+        <v>0.89</v>
+      </c>
+      <c r="AX32" s="12">
         <f t="shared" si="176"/>
         <v>0.89</v>
       </c>
-      <c r="AG32" s="12">
+      <c r="AY32" s="12">
         <f t="shared" si="176"/>
         <v>0.89</v>
       </c>
-      <c r="AH32" s="12">
+      <c r="AZ32" s="12">
         <f t="shared" si="176"/>
         <v>0.89</v>
       </c>
-      <c r="AJ32" s="12">
-        <f t="shared" ref="AJ32:AV32" si="177">AJ11/AJ6</f>
-        <v>0.86342269030978736</v>
-      </c>
-      <c r="AK32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.85032772533018708</v>
-      </c>
-      <c r="AL32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.86617967050046629</v>
-      </c>
-      <c r="AM32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.88184985745961353</v>
-      </c>
-      <c r="AN32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.87703055776439853</v>
-      </c>
-      <c r="AO32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.87871605955999799</v>
-      </c>
-      <c r="AP32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.89035108114392003</v>
-      </c>
-      <c r="AQ32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.88</v>
-      </c>
-      <c r="AR32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.89</v>
-      </c>
-      <c r="AS32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.89</v>
-      </c>
-      <c r="AT32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.89000000000000012</v>
-      </c>
-      <c r="AU32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.89</v>
-      </c>
-      <c r="AV32" s="12">
-        <f t="shared" si="177"/>
-        <v>0.89</v>
-      </c>
-      <c r="AW32" s="12">
-        <f t="shared" ref="AW32:BA32" si="178">AW11/AW6</f>
-        <v>0.89</v>
-      </c>
-      <c r="AX32" s="12">
-        <f t="shared" si="178"/>
-        <v>0.89</v>
-      </c>
-      <c r="AY32" s="12">
-        <f t="shared" si="178"/>
-        <v>0.89</v>
-      </c>
-      <c r="AZ32" s="12">
-        <f t="shared" si="178"/>
-        <v>0.89</v>
-      </c>
       <c r="BA32" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="176"/>
         <v>0.89</v>
       </c>
       <c r="BC32" t="s">
@@ -6194,813 +6201,813 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="33" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:56" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="12">
-        <f t="shared" ref="C33:R33" si="179">C17/C6</f>
+        <f t="shared" ref="C33:R33" si="177">C17/C6</f>
         <v>0.33802640756150926</v>
       </c>
       <c r="D33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.31816194154944971</v>
+      </c>
+      <c r="E33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.31365993330656289</v>
+      </c>
+      <c r="F33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.20149164896344587</v>
+      </c>
+      <c r="G33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.26720492118415995</v>
+      </c>
+      <c r="H33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.27332361516034986</v>
+      </c>
+      <c r="I33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.30134086097388851</v>
+      </c>
+      <c r="J33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.32418765082187473</v>
+      </c>
+      <c r="K33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.30313814299579422</v>
+      </c>
+      <c r="L33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.32480818414322249</v>
+      </c>
+      <c r="M33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.33147286821705424</v>
+      </c>
+      <c r="N33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.35484813084112149</v>
+      </c>
+      <c r="O33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.37234314980793853</v>
+      </c>
+      <c r="P33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.36662320730117343</v>
+      </c>
+      <c r="Q33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.36620076238881832</v>
+      </c>
+      <c r="R33" s="12">
+        <f t="shared" si="177"/>
+        <v>0.36520681265206811</v>
+      </c>
+      <c r="S33" s="12">
+        <f t="shared" ref="S33:AH33" si="178">S17/S6</f>
+        <v>0.37071797278273111</v>
+      </c>
+      <c r="T33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.34860921112631099</v>
+      </c>
+      <c r="U33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.33476201218136703</v>
+      </c>
+      <c r="V33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.33259668508287293</v>
+      </c>
+      <c r="W33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.3407089151450054</v>
+      </c>
+      <c r="X33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.33720930232558138</v>
+      </c>
+      <c r="Y33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.34703476482617585</v>
+      </c>
+      <c r="Z33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.3452852614896989</v>
+      </c>
+      <c r="AA33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.17502894635275956</v>
+      </c>
+      <c r="AB33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.35505744961386326</v>
+      </c>
+      <c r="AC33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.36834319526627218</v>
+      </c>
+      <c r="AD33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.34909026043524793</v>
+      </c>
+      <c r="AE33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.37854392719635982</v>
+      </c>
+      <c r="AF33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.35910097054316364</v>
+      </c>
+      <c r="AG33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.37673735043049889</v>
+      </c>
+      <c r="AH33" s="12">
+        <f t="shared" si="178"/>
+        <v>0.37941493973390344</v>
+      </c>
+      <c r="AJ33" s="12">
+        <f t="shared" ref="AJ33:AV33" si="179">AJ17/AJ6</f>
+        <v>0.29257847546445231</v>
+      </c>
+      <c r="AK33" s="12">
         <f t="shared" si="179"/>
-        <v>0.31816194154944971</v>
-      </c>
-      <c r="E33" s="12">
+        <v>0.29262980554904067</v>
+      </c>
+      <c r="AL33" s="12">
         <f t="shared" si="179"/>
-        <v>0.31365993330656289</v>
-      </c>
-      <c r="F33" s="12">
+        <v>0.32926639726453216</v>
+      </c>
+      <c r="AM33" s="12">
         <f t="shared" si="179"/>
-        <v>0.20149164896344587</v>
-      </c>
-      <c r="G33" s="12">
+        <v>0.36756414317389929</v>
+      </c>
+      <c r="AN33" s="12">
         <f t="shared" si="179"/>
-        <v>0.26720492118415995</v>
-      </c>
-      <c r="H33" s="12">
+        <v>0.34635919572872886</v>
+      </c>
+      <c r="AO33" s="12">
         <f t="shared" si="179"/>
-        <v>0.27332361516034986</v>
-      </c>
-      <c r="I33" s="12">
+        <v>0.3426245556185275</v>
+      </c>
+      <c r="AP33" s="12">
         <f t="shared" si="179"/>
-        <v>0.30134086097388851</v>
-      </c>
-      <c r="J33" s="12">
+        <v>0.31346198558474775</v>
+      </c>
+      <c r="AQ33" s="12">
         <f t="shared" si="179"/>
-        <v>0.32418765082187473</v>
-      </c>
-      <c r="K33" s="12">
+        <v>0.37288022161394302</v>
+      </c>
+      <c r="AR33" s="12">
         <f t="shared" si="179"/>
-        <v>0.30313814299579422</v>
-      </c>
-      <c r="L33" s="12">
+        <v>0.39307707454914959</v>
+      </c>
+      <c r="AS33" s="12">
         <f t="shared" si="179"/>
-        <v>0.32480818414322249</v>
-      </c>
-      <c r="M33" s="12">
+        <v>0.40438873947033582</v>
+      </c>
+      <c r="AT33" s="12">
         <f t="shared" si="179"/>
-        <v>0.33147286821705424</v>
-      </c>
-      <c r="N33" s="12">
+        <v>0.41301721116370593</v>
+      </c>
+      <c r="AU33" s="12">
         <f t="shared" si="179"/>
-        <v>0.35484813084112149</v>
-      </c>
-      <c r="O33" s="12">
+        <v>0.41859295734485052</v>
+      </c>
+      <c r="AV33" s="12">
         <f t="shared" si="179"/>
-        <v>0.37234314980793853</v>
-      </c>
-      <c r="P33" s="12">
-        <f t="shared" si="179"/>
-        <v>0.36662320730117343</v>
-      </c>
-      <c r="Q33" s="12">
-        <f t="shared" si="179"/>
-        <v>0.36620076238881832</v>
-      </c>
-      <c r="R33" s="12">
-        <f t="shared" si="179"/>
-        <v>0.36520681265206811</v>
-      </c>
-      <c r="S33" s="12">
-        <f t="shared" ref="S33:AH33" si="180">S17/S6</f>
-        <v>0.37071797278273111</v>
-      </c>
-      <c r="T33" s="12">
+        <v>0.42580426559917545</v>
+      </c>
+      <c r="AW33" s="12">
+        <f t="shared" ref="AW33:BA33" si="180">AW17/AW6</f>
+        <v>0.42840912451791419</v>
+      </c>
+      <c r="AX33" s="12">
         <f t="shared" si="180"/>
-        <v>0.34860921112631099</v>
-      </c>
-      <c r="U33" s="12">
+        <v>0.43098451695384415</v>
+      </c>
+      <c r="AY33" s="12">
         <f t="shared" si="180"/>
-        <v>0.33476201218136703</v>
-      </c>
-      <c r="V33" s="12">
+        <v>0.43353065476169361</v>
+      </c>
+      <c r="AZ33" s="12">
         <f t="shared" si="180"/>
-        <v>0.33259668508287293</v>
-      </c>
-      <c r="W33" s="12">
+        <v>0.4360477462087447</v>
+      </c>
+      <c r="BA33" s="12">
         <f t="shared" si="180"/>
-        <v>0.3407089151450054</v>
-      </c>
-      <c r="X33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.33720930232558138</v>
-      </c>
-      <c r="Y33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.34703476482617585</v>
-      </c>
-      <c r="Z33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.3452852614896989</v>
-      </c>
-      <c r="AA33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.17502894635275956</v>
-      </c>
-      <c r="AB33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.35505744961386326</v>
-      </c>
-      <c r="AC33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.36834319526627218</v>
-      </c>
-      <c r="AD33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.34909026043524793</v>
-      </c>
-      <c r="AE33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.37854392719635982</v>
-      </c>
-      <c r="AF33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.37861204283178929</v>
-      </c>
-      <c r="AG33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.37891516183760138</v>
-      </c>
-      <c r="AH33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.38591262481140137</v>
-      </c>
-      <c r="AJ33" s="12">
-        <f t="shared" ref="AJ33:AV33" si="181">AJ17/AJ6</f>
-        <v>0.29257847546445231</v>
-      </c>
-      <c r="AK33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.29262980554904067</v>
-      </c>
-      <c r="AL33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.32926639726453216</v>
-      </c>
-      <c r="AM33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.36756414317389929</v>
-      </c>
-      <c r="AN33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.34635919572872886</v>
-      </c>
-      <c r="AO33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.3426245556185275</v>
-      </c>
-      <c r="AP33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.31346198558474775</v>
-      </c>
-      <c r="AQ33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.37030781947346225</v>
-      </c>
-      <c r="AR33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.40017184638012643</v>
-      </c>
-      <c r="AS33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.41129205775200667</v>
-      </c>
-      <c r="AT33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.41977081642488245</v>
-      </c>
-      <c r="AU33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.42524877758972335</v>
-      </c>
-      <c r="AV33" s="12">
-        <f t="shared" si="181"/>
-        <v>0.43234765403217429</v>
-      </c>
-      <c r="AW33" s="12">
-        <f t="shared" ref="AW33:BA33" si="182">AW17/AW6</f>
-        <v>0.43490517458615008</v>
-      </c>
-      <c r="AX33" s="12">
-        <f t="shared" si="182"/>
-        <v>0.43743369794470427</v>
-      </c>
-      <c r="AY33" s="12">
-        <f t="shared" si="182"/>
-        <v>0.43993343146338981</v>
-      </c>
-      <c r="AZ33" s="12">
-        <f t="shared" si="182"/>
-        <v>0.44240457895641777</v>
-      </c>
-      <c r="BA33" s="12">
-        <f t="shared" si="182"/>
-        <v>0.44484734070179849</v>
+        <v>0.43853599598038934</v>
       </c>
       <c r="BC33" t="s">
         <v>46</v>
       </c>
       <c r="BD33" s="12">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:56" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12">
-        <f t="shared" ref="G34:R34" si="183">G12/C12-1</f>
+        <f t="shared" ref="G34:R34" si="181">G12/C12-1</f>
         <v>0.33329510264938644</v>
       </c>
       <c r="H34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.27228503461363696</v>
       </c>
       <c r="I34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.22819330258672554</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.201557842100202</v>
       </c>
       <c r="K34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.1440860215053763</v>
       </c>
       <c r="L34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.11764705882352944</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.15510204081632661</v>
       </c>
       <c r="N34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.11644657863145258</v>
       </c>
       <c r="O34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.16541353383458657</v>
       </c>
       <c r="P34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.15037593984962405</v>
       </c>
       <c r="Q34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.15017667844522964</v>
       </c>
       <c r="R34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>0.17741935483870974</v>
       </c>
       <c r="S34" s="12">
-        <f t="shared" ref="S34:AH34" si="184">S12/O12-1</f>
+        <f t="shared" ref="S34:AH34" si="182">S12/O12-1</f>
         <v>0.13064516129032255</v>
       </c>
       <c r="T34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.20588235294117641</v>
       </c>
       <c r="U34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.19047619047619047</v>
       </c>
       <c r="V34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.17656012176560121</v>
       </c>
       <c r="W34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.17974322396576325</v>
       </c>
       <c r="X34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.18699186991869921</v>
       </c>
       <c r="Y34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.13677419354838705</v>
       </c>
       <c r="Z34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.1500646830530401</v>
       </c>
       <c r="AA34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.13542926239419595</v>
       </c>
       <c r="AB34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.12328767123287676</v>
       </c>
       <c r="AC34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.16004540295119174</v>
       </c>
       <c r="AD34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.12373453318335215</v>
       </c>
       <c r="AE34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>9.2651757188498385E-2</v>
       </c>
       <c r="AF34" s="12">
-        <f t="shared" si="184"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="182"/>
+        <v>9.9593495934959364E-2</v>
       </c>
       <c r="AG34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AH34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="182"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ34" s="12"/>
       <c r="AK34" s="12">
-        <f t="shared" ref="AK34:AV34" si="185">AK12/AJ12-1</f>
+        <f t="shared" ref="AK34:AV34" si="183">AK12/AJ12-1</f>
         <v>0.25555172615602717</v>
       </c>
       <c r="AL34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>0.13320903252537808</v>
       </c>
       <c r="AM34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>0.16087751371115178</v>
       </c>
       <c r="AN34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>0.17598425196850398</v>
       </c>
       <c r="AO34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>0.16270505523937051</v>
       </c>
       <c r="AP34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>0.13561762165274982</v>
       </c>
       <c r="AQ34" s="12">
-        <f t="shared" si="185"/>
-        <v>8.7981744421906649E-2</v>
+        <f t="shared" si="183"/>
+        <v>9.0375253549695778E-2</v>
       </c>
       <c r="AR34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AS34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AT34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AU34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AV34" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="183"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW34" s="12">
-        <f t="shared" ref="AW34:BA34" si="186">AW12/AV12-1</f>
+        <f t="shared" ref="AW34:BA34" si="184">AW12/AV12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX34" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="184"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AY34" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="184"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ34" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="184"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA34" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="184"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC34" t="s">
         <v>47</v>
       </c>
       <c r="BD34" s="5">
-        <f>NPV(BD33,AM24:FW24)</f>
-        <v>152617.21254900124</v>
+        <f>NPV(BD33,AQ24:FW24)</f>
+        <v>142989.24752594542</v>
       </c>
     </row>
-    <row r="35" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:56" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="12">
-        <f t="shared" ref="C35:R35" si="187">C13/C6</f>
+        <f t="shared" ref="C35:R35" si="185">C13/C6</f>
         <v>0.27944876019144282</v>
       </c>
       <c r="D35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.29435718970920488</v>
+      </c>
+      <c r="E35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.29247341864971982</v>
+      </c>
+      <c r="F35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.33128067540839501</v>
+      </c>
+      <c r="G35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.30026912725874666</v>
+      </c>
+      <c r="H35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.30940233236151604</v>
+      </c>
+      <c r="I35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.28652081863091039</v>
+      </c>
+      <c r="J35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.26791646891314663</v>
+      </c>
+      <c r="K35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.27725655127790361</v>
+      </c>
+      <c r="L35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.28804347826086957</v>
+      </c>
+      <c r="M35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.27658914728682171</v>
+      </c>
+      <c r="N35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.27482476635514019</v>
+      </c>
+      <c r="O35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.26862996158770808</v>
+      </c>
+      <c r="P35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.27979139504563233</v>
+      </c>
+      <c r="Q35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.27141041931385007</v>
+      </c>
+      <c r="R35" s="12">
+        <f t="shared" si="185"/>
+        <v>0.2751824817518248</v>
+      </c>
+      <c r="S35" s="12">
+        <f t="shared" ref="S35:AH35" si="186">S13/S6</f>
+        <v>0.2717034256217738</v>
+      </c>
+      <c r="T35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.28431372549019607</v>
+      </c>
+      <c r="U35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.28558538235957592</v>
+      </c>
+      <c r="V35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.28662983425414362</v>
+      </c>
+      <c r="W35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.27948442534908702</v>
+      </c>
+      <c r="X35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.27927740863787376</v>
+      </c>
+      <c r="Y35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.27341513292433539</v>
+      </c>
+      <c r="Z35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.27099841521394613</v>
+      </c>
+      <c r="AA35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.26090312620609801</v>
+      </c>
+      <c r="AB35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.27217931813900925</v>
+      </c>
+      <c r="AC35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.26460798816568049</v>
+      </c>
+      <c r="AD35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.27399215126650017</v>
+      </c>
+      <c r="AE35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.26163808190409521</v>
+      </c>
+      <c r="AF35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.27686020773029119</v>
+      </c>
+      <c r="AG35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.26</v>
+      </c>
+      <c r="AH35" s="12">
+        <f t="shared" si="186"/>
+        <v>0.26</v>
+      </c>
+      <c r="AJ35" s="12">
+        <f t="shared" ref="AJ35:AV35" si="187">AJ13/AJ6</f>
+        <v>0.29953883342571913</v>
+      </c>
+      <c r="AK35" s="12">
         <f t="shared" si="187"/>
-        <v>0.29435718970920488</v>
-      </c>
-      <c r="E35" s="12">
+        <v>0.29035962953878547</v>
+      </c>
+      <c r="AL35" s="12">
         <f t="shared" si="187"/>
-        <v>0.29247341864971982</v>
-      </c>
-      <c r="F35" s="12">
+        <v>0.27906434566366178</v>
+      </c>
+      <c r="AM35" s="12">
         <f t="shared" si="187"/>
-        <v>0.33128067540839501</v>
-      </c>
-      <c r="G35" s="12">
+        <v>0.27374089325308837</v>
+      </c>
+      <c r="AN35" s="12">
         <f t="shared" si="187"/>
-        <v>0.30026912725874666</v>
-      </c>
-      <c r="H35" s="12">
+        <v>0.28217653072816085</v>
+      </c>
+      <c r="AO35" s="12">
         <f t="shared" si="187"/>
-        <v>0.30940233236151604</v>
-      </c>
-      <c r="I35" s="12">
+        <v>0.27569684167138958</v>
+      </c>
+      <c r="AP35" s="12">
         <f t="shared" si="187"/>
-        <v>0.28652081863091039</v>
-      </c>
-      <c r="J35" s="12">
+        <v>0.26803069053708439</v>
+      </c>
+      <c r="AQ35" s="12">
         <f t="shared" si="187"/>
-        <v>0.26791646891314663</v>
-      </c>
-      <c r="K35" s="12">
+        <v>0.2645739105627033</v>
+      </c>
+      <c r="AR35" s="12">
         <f t="shared" si="187"/>
-        <v>0.27725655127790361</v>
-      </c>
-      <c r="L35" s="12">
+        <v>0.24987535997588642</v>
+      </c>
+      <c r="AS35" s="12">
         <f t="shared" si="187"/>
-        <v>0.28804347826086957</v>
-      </c>
-      <c r="M35" s="12">
+        <v>0.24035629864347172</v>
+      </c>
+      <c r="AT35" s="12">
         <f t="shared" si="187"/>
-        <v>0.27658914728682171</v>
-      </c>
-      <c r="N35" s="12">
+        <v>0.23342294387491</v>
+      </c>
+      <c r="AU35" s="12">
         <f t="shared" si="187"/>
-        <v>0.27482476635514019</v>
-      </c>
-      <c r="O35" s="12">
+        <v>0.22889045952782436</v>
+      </c>
+      <c r="AV35" s="12">
         <f t="shared" si="187"/>
-        <v>0.26862996158770808</v>
-      </c>
-      <c r="P35" s="12">
-        <f t="shared" si="187"/>
-        <v>0.27979139504563233</v>
-      </c>
-      <c r="Q35" s="12">
-        <f t="shared" si="187"/>
-        <v>0.27141041931385007</v>
-      </c>
-      <c r="R35" s="12">
-        <f t="shared" si="187"/>
-        <v>0.2751824817518248</v>
-      </c>
-      <c r="S35" s="12">
-        <f t="shared" ref="S35:AH35" si="188">S13/S6</f>
-        <v>0.2717034256217738</v>
-      </c>
-      <c r="T35" s="12">
+        <v>0.22444598458553652</v>
+      </c>
+      <c r="AW35" s="12">
+        <f t="shared" ref="AW35:BA35" si="188">AW13/AW6</f>
+        <v>0.22224553375626657</v>
+      </c>
+      <c r="AX35" s="12">
         <f t="shared" si="188"/>
-        <v>0.28431372549019607</v>
-      </c>
-      <c r="U35" s="12">
+        <v>0.22006665597434238</v>
+      </c>
+      <c r="AY35" s="12">
         <f t="shared" si="188"/>
-        <v>0.28558538235957592</v>
-      </c>
-      <c r="V35" s="12">
+        <v>0.21790913973929982</v>
+      </c>
+      <c r="AZ35" s="12">
         <f t="shared" si="188"/>
-        <v>0.28662983425414362</v>
-      </c>
-      <c r="W35" s="12">
+        <v>0.21577277562420866</v>
+      </c>
+      <c r="BA35" s="12">
         <f t="shared" si="188"/>
-        <v>0.27948442534908702</v>
-      </c>
-      <c r="X35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.27927740863787376</v>
-      </c>
-      <c r="Y35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.27341513292433539</v>
-      </c>
-      <c r="Z35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.27099841521394613</v>
-      </c>
-      <c r="AA35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.26090312620609801</v>
-      </c>
-      <c r="AB35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.27217931813900925</v>
-      </c>
-      <c r="AC35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.26460798816568049</v>
-      </c>
-      <c r="AD35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.27399215126650017</v>
-      </c>
-      <c r="AE35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.26163808190409521</v>
-      </c>
-      <c r="AF35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.26</v>
-      </c>
-      <c r="AG35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.26</v>
-      </c>
-      <c r="AH35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.26</v>
-      </c>
-      <c r="AJ35" s="12">
-        <f t="shared" ref="AJ35:AV35" si="189">AJ13/AJ6</f>
-        <v>0.29953883342571913</v>
-      </c>
-      <c r="AK35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.29035962953878547</v>
-      </c>
-      <c r="AL35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.27906434566366178</v>
-      </c>
-      <c r="AM35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.27374089325308837</v>
-      </c>
-      <c r="AN35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.28217653072816085</v>
-      </c>
-      <c r="AO35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.27569684167138958</v>
-      </c>
-      <c r="AP35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.26803069053708439</v>
-      </c>
-      <c r="AQ35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.26039213205465883</v>
-      </c>
-      <c r="AR35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.24592590249606663</v>
-      </c>
-      <c r="AS35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.23655729668669268</v>
-      </c>
-      <c r="AT35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.22973352851303805</v>
-      </c>
-      <c r="AU35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.22527268329919267</v>
-      </c>
-      <c r="AV35" s="12">
-        <f t="shared" si="189"/>
-        <v>0.22089845643901418</v>
-      </c>
-      <c r="AW35" s="12">
-        <f t="shared" ref="AW35:BA35" si="190">AW13/AW6</f>
-        <v>0.21873278529745521</v>
-      </c>
-      <c r="AX35" s="12">
-        <f t="shared" si="190"/>
-        <v>0.21658834622591155</v>
-      </c>
-      <c r="AY35" s="12">
-        <f t="shared" si="190"/>
-        <v>0.21446493106683398</v>
-      </c>
-      <c r="AZ35" s="12">
-        <f t="shared" si="190"/>
-        <v>0.21236233370343366</v>
-      </c>
-      <c r="BA35" s="12">
-        <f t="shared" si="190"/>
-        <v>0.21028035003967449</v>
+        <v>0.21365735625534385</v>
       </c>
       <c r="BC35" t="s">
         <v>48</v>
       </c>
       <c r="BD35" s="5">
         <f>Main!D8</f>
-        <v>1280</v>
+        <v>-453</v>
       </c>
     </row>
-    <row r="36" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:56" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12">
-        <f t="shared" ref="G36:R36" si="191">G14/C14-1</f>
+        <f t="shared" ref="G36:R36" si="189">G14/C14-1</f>
         <v>0.26730814362825628</v>
       </c>
       <c r="H36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>0.23006066052572471</v>
       </c>
       <c r="I36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>0.1898294034553949</v>
       </c>
       <c r="J36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>6.3951024252413502E-2</v>
       </c>
       <c r="K36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>0.25462962962962954</v>
       </c>
       <c r="L36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>2.2831050228310446E-2</v>
       </c>
       <c r="M36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>5.0228310502283158E-2</v>
       </c>
       <c r="N36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>7.5554375248970906E-2</v>
       </c>
       <c r="O36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>7.0110701107011009E-2</v>
       </c>
       <c r="P36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>0.14285714285714279</v>
       </c>
       <c r="Q36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>0.15217391304347827</v>
       </c>
       <c r="R36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="189"/>
         <v>0.12757201646090532</v>
       </c>
       <c r="S36" s="12">
-        <f t="shared" ref="S36:AH36" si="192">S14/O14-1</f>
+        <f t="shared" ref="S36:AH36" si="190">S14/O14-1</f>
         <v>-7.241379310344831E-2</v>
       </c>
       <c r="T36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>0.13671875</v>
       </c>
       <c r="U36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>0.20377358490566033</v>
       </c>
       <c r="V36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>0.24087591240875916</v>
       </c>
       <c r="W36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>0.23048327137546476</v>
       </c>
       <c r="X36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>0.22680412371134029</v>
       </c>
       <c r="Y36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>0.10658307210031337</v>
       </c>
       <c r="Z36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>9.4117647058823639E-2</v>
       </c>
       <c r="AA36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>6.3444108761329332E-2</v>
       </c>
       <c r="AB36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>-5.6022408963585235E-3</v>
       </c>
       <c r="AC36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>3.6827195467422191E-2</v>
       </c>
       <c r="AD36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>0.22580645161290325</v>
       </c>
       <c r="AE36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
         <v>4.2613636363636465E-2</v>
       </c>
       <c r="AF36" s="12">
-        <f t="shared" si="192"/>
+        <f t="shared" si="190"/>
+        <v>6.197183098591541E-2</v>
+      </c>
+      <c r="AG36" s="12">
+        <f t="shared" si="190"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG36" s="12">
-        <f t="shared" si="192"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="AH36" s="12">
-        <f t="shared" si="192"/>
-        <v>-0.16000000000000003</v>
+        <f t="shared" si="190"/>
+        <v>-0.13000000000000012</v>
       </c>
       <c r="AJ36" s="12"/>
       <c r="AK36" s="12">
-        <f t="shared" ref="AK36:AV36" si="193">AK14/AJ14-1</f>
+        <f t="shared" ref="AK36:AV36" si="191">AK14/AJ14-1</f>
         <v>0.18128851239780386</v>
       </c>
       <c r="AL36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>0.10008750696078095</v>
       </c>
       <c r="AM36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>0.12086776859504123</v>
       </c>
       <c r="AN36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>0.12350230414746544</v>
       </c>
       <c r="AO36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>0.1591468416735029</v>
       </c>
       <c r="AP36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>8.2094833687190283E-2</v>
       </c>
       <c r="AQ36" s="12">
-        <f t="shared" si="193"/>
-        <v>-2.376062786134725E-2</v>
+        <f t="shared" si="191"/>
+        <v>-7.3904512753433238E-3</v>
       </c>
       <c r="AR36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV36" s="12">
-        <f t="shared" si="193"/>
+        <f t="shared" si="191"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW36" s="12">
-        <f t="shared" ref="AW36:BA36" si="194">AW14/AV14-1</f>
+        <f t="shared" ref="AW36:BA36" si="192">AW14/AV14-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX36" s="12">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY36" s="12">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ36" s="12">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA36" s="12">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC36" t="s">
@@ -7008,10 +7015,10 @@
       </c>
       <c r="BD36" s="5">
         <f>BD34+BD35</f>
-        <v>153897.21254900124</v>
+        <v>142536.24752594542</v>
       </c>
     </row>
-    <row r="37" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:56" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>33</v>
       </c>
@@ -7020,199 +7027,199 @@
         <v>0.17000469744202942</v>
       </c>
       <c r="D37" s="12">
-        <f t="shared" ref="D37:N37" si="195">D23/D22</f>
+        <f t="shared" ref="D37:N37" si="193">D23/D22</f>
         <v>3.9998262833318858E-2</v>
       </c>
       <c r="E37" s="12">
+        <f t="shared" si="193"/>
+        <v>5.000213867145728E-2</v>
+      </c>
+      <c r="F37" s="12">
+        <f t="shared" si="193"/>
+        <v>5.0096707180209664E-2</v>
+      </c>
+      <c r="G37" s="12">
+        <f t="shared" si="193"/>
+        <v>3.9886039886039885E-2</v>
+      </c>
+      <c r="H37" s="12">
+        <f t="shared" si="193"/>
+        <v>0.10970464135021098</v>
+      </c>
+      <c r="I37" s="12">
+        <f t="shared" si="193"/>
+        <v>5.0299401197604787E-2</v>
+      </c>
+      <c r="J37" s="12">
+        <f t="shared" si="193"/>
+        <v>0.10999091070551732</v>
+      </c>
+      <c r="K37" s="12">
+        <f t="shared" si="193"/>
+        <v>-3.9173014145810661E-2</v>
+      </c>
+      <c r="L37" s="12">
+        <f t="shared" si="193"/>
+        <v>-0.1</v>
+      </c>
+      <c r="M37" s="12">
+        <f t="shared" si="193"/>
+        <v>9.9056603773584911E-2</v>
+      </c>
+      <c r="N37" s="12">
+        <f t="shared" si="193"/>
+        <v>-0.87969924812030076</v>
+      </c>
+      <c r="O37" s="12">
+        <f t="shared" ref="O37:R37" si="194">O23/O22</f>
+        <v>0.12002791346824843</v>
+      </c>
+      <c r="P37" s="12">
+        <f t="shared" si="194"/>
+        <v>0.19480519480519481</v>
+      </c>
+      <c r="Q37" s="12">
+        <f t="shared" si="194"/>
+        <v>0.14527503526093088</v>
+      </c>
+      <c r="R37" s="12">
+        <f t="shared" si="194"/>
+        <v>0.16008174386920981</v>
+      </c>
+      <c r="S37" s="12">
+        <f t="shared" ref="S37:AH37" si="195">S23/S22</f>
+        <v>0.17952041477640959</v>
+      </c>
+      <c r="T37" s="12">
         <f t="shared" si="195"/>
-        <v>5.000213867145728E-2</v>
-      </c>
-      <c r="F37" s="12">
+        <v>0.21045576407506703</v>
+      </c>
+      <c r="U37" s="12">
         <f t="shared" si="195"/>
-        <v>5.0096707180209664E-2</v>
-      </c>
-      <c r="G37" s="12">
+        <v>0.21978021978021978</v>
+      </c>
+      <c r="V37" s="12">
         <f t="shared" si="195"/>
-        <v>3.9886039886039885E-2</v>
-      </c>
-      <c r="H37" s="12">
+        <v>0.22478576137112721</v>
+      </c>
+      <c r="W37" s="12">
         <f t="shared" si="195"/>
-        <v>0.10970464135021098</v>
-      </c>
-      <c r="I37" s="12">
+        <v>0.21964956195244056</v>
+      </c>
+      <c r="X37" s="12">
         <f t="shared" si="195"/>
-        <v>5.0299401197604787E-2</v>
-      </c>
-      <c r="J37" s="12">
+        <v>0.21515151515151515</v>
+      </c>
+      <c r="Y37" s="12">
         <f t="shared" si="195"/>
-        <v>0.10999091070551732</v>
-      </c>
-      <c r="K37" s="12">
+        <v>0.19506597819850832</v>
+      </c>
+      <c r="Z37" s="12">
         <f t="shared" si="195"/>
-        <v>-3.9173014145810661E-2</v>
-      </c>
-      <c r="L37" s="12">
+        <v>0.17975663716814158</v>
+      </c>
+      <c r="AA37" s="12">
         <f t="shared" si="195"/>
-        <v>-0.1</v>
-      </c>
-      <c r="M37" s="12">
+        <v>0.35950413223140498</v>
+      </c>
+      <c r="AB37" s="12">
         <f t="shared" si="195"/>
-        <v>9.9056603773584911E-2</v>
-      </c>
-      <c r="N37" s="12">
+        <v>0.18497409326424871</v>
+      </c>
+      <c r="AC37" s="12">
         <f t="shared" si="195"/>
-        <v>-0.87969924812030076</v>
-      </c>
-      <c r="O37" s="12">
-        <f t="shared" ref="O37:R37" si="196">O23/O22</f>
-        <v>0.12002791346824843</v>
-      </c>
-      <c r="P37" s="12">
+        <v>0.17531831537708129</v>
+      </c>
+      <c r="AD37" s="12">
+        <f t="shared" si="195"/>
+        <v>0.15469613259668508</v>
+      </c>
+      <c r="AE37" s="12">
+        <f t="shared" si="195"/>
+        <v>0.17002749770852429</v>
+      </c>
+      <c r="AF37" s="12">
+        <f t="shared" si="195"/>
+        <v>0.1951451689671585</v>
+      </c>
+      <c r="AG37" s="12">
+        <f t="shared" si="195"/>
+        <v>0.17</v>
+      </c>
+      <c r="AH37" s="12">
+        <f t="shared" si="195"/>
+        <v>0.17</v>
+      </c>
+      <c r="AJ37" s="12">
+        <f t="shared" ref="AJ37:AV37" si="196">AJ23/AJ22</f>
+        <v>8.0809246255147349E-2</v>
+      </c>
+      <c r="AK37" s="12">
         <f t="shared" si="196"/>
-        <v>0.19480519480519481</v>
-      </c>
-      <c r="Q37" s="12">
+        <v>7.902232954882267E-2</v>
+      </c>
+      <c r="AL37" s="12">
         <f t="shared" si="196"/>
-        <v>0.14527503526093088</v>
-      </c>
-      <c r="R37" s="12">
+        <v>-0.25957854406130271</v>
+      </c>
+      <c r="AM37" s="12">
         <f t="shared" si="196"/>
-        <v>0.16008174386920981</v>
-      </c>
-      <c r="S37" s="12">
-        <f t="shared" ref="S37:AH37" si="197">S23/S22</f>
-        <v>0.17952041477640959</v>
-      </c>
-      <c r="T37" s="12">
+        <v>0.15477651183172655</v>
+      </c>
+      <c r="AN37" s="12">
+        <f t="shared" si="196"/>
+        <v>0.20838881491344874</v>
+      </c>
+      <c r="AO37" s="12">
+        <f t="shared" si="196"/>
+        <v>0.20164730107368731</v>
+      </c>
+      <c r="AP37" s="12">
+        <f t="shared" si="196"/>
+        <v>0.19780695426345404</v>
+      </c>
+      <c r="AQ37" s="12">
+        <f t="shared" si="196"/>
+        <v>0.17621383398323182</v>
+      </c>
+      <c r="AR37" s="12">
+        <f t="shared" si="196"/>
+        <v>0.18</v>
+      </c>
+      <c r="AS37" s="12">
+        <f t="shared" si="196"/>
+        <v>0.18</v>
+      </c>
+      <c r="AT37" s="12">
+        <f t="shared" si="196"/>
+        <v>0.18</v>
+      </c>
+      <c r="AU37" s="12">
+        <f t="shared" si="196"/>
+        <v>0.18</v>
+      </c>
+      <c r="AV37" s="12">
+        <f t="shared" si="196"/>
+        <v>0.18</v>
+      </c>
+      <c r="AW37" s="12">
+        <f t="shared" ref="AW37:BA37" si="197">AW23/AW22</f>
+        <v>0.18</v>
+      </c>
+      <c r="AX37" s="12">
         <f t="shared" si="197"/>
-        <v>0.21045576407506703</v>
-      </c>
-      <c r="U37" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="AY37" s="12">
         <f t="shared" si="197"/>
-        <v>0.21978021978021978</v>
-      </c>
-      <c r="V37" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="AZ37" s="12">
         <f t="shared" si="197"/>
-        <v>0.22478576137112721</v>
-      </c>
-      <c r="W37" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="BA37" s="12">
         <f t="shared" si="197"/>
-        <v>0.21964956195244056</v>
-      </c>
-      <c r="X37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.21515151515151515</v>
-      </c>
-      <c r="Y37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.19506597819850832</v>
-      </c>
-      <c r="Z37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.17975663716814158</v>
-      </c>
-      <c r="AA37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.35950413223140498</v>
-      </c>
-      <c r="AB37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.18497409326424871</v>
-      </c>
-      <c r="AC37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.17531831537708129</v>
-      </c>
-      <c r="AD37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.15469613259668508</v>
-      </c>
-      <c r="AE37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.17002749770852429</v>
-      </c>
-      <c r="AF37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.17</v>
-      </c>
-      <c r="AG37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.17</v>
-      </c>
-      <c r="AH37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.17</v>
-      </c>
-      <c r="AJ37" s="12">
-        <f t="shared" ref="AJ37:AV37" si="198">AJ23/AJ22</f>
-        <v>8.0809246255147349E-2</v>
-      </c>
-      <c r="AK37" s="12">
-        <f t="shared" si="198"/>
-        <v>7.902232954882267E-2</v>
-      </c>
-      <c r="AL37" s="12">
-        <f t="shared" si="198"/>
-        <v>-0.25957854406130271</v>
-      </c>
-      <c r="AM37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.15477651183172655</v>
-      </c>
-      <c r="AN37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.20838881491344874</v>
-      </c>
-      <c r="AO37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.20164730107368731</v>
-      </c>
-      <c r="AP37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.19780695426345404</v>
-      </c>
-      <c r="AQ37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.17464402657244024</v>
-      </c>
-      <c r="AR37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.18</v>
-      </c>
-      <c r="AS37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.18</v>
-      </c>
-      <c r="AT37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.18</v>
-      </c>
-      <c r="AU37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.18</v>
-      </c>
-      <c r="AV37" s="12">
-        <f t="shared" si="198"/>
-        <v>0.18</v>
-      </c>
-      <c r="AW37" s="12">
-        <f t="shared" ref="AW37:BA37" si="199">AW23/AW22</f>
-        <v>0.18</v>
-      </c>
-      <c r="AX37" s="12">
-        <f t="shared" si="199"/>
-        <v>0.18</v>
-      </c>
-      <c r="AY37" s="12">
-        <f t="shared" si="199"/>
-        <v>0.18</v>
-      </c>
-      <c r="AZ37" s="12">
-        <f t="shared" si="199"/>
-        <v>0.18</v>
-      </c>
-      <c r="BA37" s="12">
-        <f t="shared" si="199"/>
         <v>0.18</v>
       </c>
       <c r="BC37" t="s">
@@ -7220,241 +7227,236 @@
       </c>
       <c r="BD37" s="6">
         <f>BD36/AV25</f>
-        <v>352.97525813991109</v>
+        <v>336.01189892962145</v>
       </c>
     </row>
-    <row r="38" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:56" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="12">
-        <f t="shared" ref="C38:R38" si="200">C24/C6</f>
+        <f t="shared" ref="C38:R38" si="198">C24/C6</f>
         <v>0.28046850573606846</v>
       </c>
       <c r="D38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.30206890897164929</v>
+      </c>
+      <c r="E38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.29082354173577529</v>
+      </c>
+      <c r="F38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.18213409274045853</v>
+      </c>
+      <c r="G38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.25913110342176088</v>
+      </c>
+      <c r="H38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.23068513119533526</v>
+      </c>
+      <c r="I38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.27981651376146788</v>
+      </c>
+      <c r="J38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.28472830337506766</v>
+      </c>
+      <c r="K38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.30896150113231963</v>
+      </c>
+      <c r="L38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.35166240409207161</v>
+      </c>
+      <c r="M38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.29612403100775192</v>
+      </c>
+      <c r="N38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.65712616822429903</v>
+      </c>
+      <c r="O38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.3229193341869398</v>
+      </c>
+      <c r="P38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.29100391134289438</v>
+      </c>
+      <c r="Q38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.308005082592122</v>
+      </c>
+      <c r="R38" s="12">
+        <f t="shared" si="198"/>
+        <v>0.3</v>
+      </c>
+      <c r="S38" s="12">
+        <f t="shared" ref="S38:AH38" si="199">S24/S6</f>
+        <v>0.29704364148287188</v>
+      </c>
+      <c r="T38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.26858185134518925</v>
+      </c>
+      <c r="U38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.25625986916309496</v>
+      </c>
+      <c r="V38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.25988950276243095</v>
+      </c>
+      <c r="W38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.2678839957035446</v>
+      </c>
+      <c r="X38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.26889534883720928</v>
+      </c>
+      <c r="Y38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.28691206543967279</v>
+      </c>
+      <c r="Z38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.29377971473851028</v>
+      </c>
+      <c r="AA38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.11964492473948282</v>
+      </c>
+      <c r="AB38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.29628932002260311</v>
+      </c>
+      <c r="AC38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.31139053254437871</v>
+      </c>
+      <c r="AD38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.30021405636817694</v>
+      </c>
+      <c r="AE38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.31694084704235209</v>
+      </c>
+      <c r="AF38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.28792780521028433</v>
+      </c>
+      <c r="AG38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.31848324151811575</v>
+      </c>
+      <c r="AH38" s="12">
+        <f t="shared" si="199"/>
+        <v>0.31790374829696938</v>
+      </c>
+      <c r="AJ38" s="12">
+        <f t="shared" ref="AJ38:AV38" si="200">AJ24/AJ6</f>
+        <v>0.26405243698247322</v>
+      </c>
+      <c r="AK38" s="12">
         <f t="shared" si="200"/>
-        <v>0.30206890897164929</v>
-      </c>
-      <c r="E38" s="12">
+        <v>0.26424723434196229</v>
+      </c>
+      <c r="AL38" s="12">
         <f t="shared" si="200"/>
-        <v>0.29082354173577529</v>
-      </c>
-      <c r="F38" s="12">
+        <v>0.40876593099160707</v>
+      </c>
+      <c r="AM38" s="12">
         <f t="shared" si="200"/>
-        <v>0.18213409274045853</v>
-      </c>
-      <c r="G38" s="12">
+        <v>0.30547988596769082</v>
+      </c>
+      <c r="AN38" s="12">
         <f t="shared" si="200"/>
-        <v>0.25913110342176088</v>
-      </c>
-      <c r="H38" s="12">
+        <v>0.27013518118823127</v>
+      </c>
+      <c r="AO38" s="12">
         <f t="shared" si="200"/>
-        <v>0.23068513119533526</v>
-      </c>
-      <c r="I38" s="12">
+        <v>0.27966407336802512</v>
+      </c>
+      <c r="AP38" s="12">
         <f t="shared" si="200"/>
-        <v>0.27981651376146788</v>
-      </c>
-      <c r="J38" s="12">
+        <v>0.25854452452917925</v>
+      </c>
+      <c r="AQ38" s="12">
         <f t="shared" si="200"/>
-        <v>0.28472830337506766</v>
-      </c>
-      <c r="K38" s="12">
+        <v>0.30977301173314825</v>
+      </c>
+      <c r="AR38" s="12">
         <f t="shared" si="200"/>
-        <v>0.30896150113231963</v>
-      </c>
-      <c r="L38" s="12">
+        <v>0.32474298943239188</v>
+      </c>
+      <c r="AS38" s="12">
         <f t="shared" si="200"/>
-        <v>0.35166240409207161</v>
-      </c>
-      <c r="M38" s="12">
+        <v>0.33392637225625643</v>
+      </c>
+      <c r="AT38" s="12">
         <f t="shared" si="200"/>
-        <v>0.29612403100775192</v>
-      </c>
-      <c r="N38" s="12">
+        <v>0.34093457656720699</v>
+      </c>
+      <c r="AU38" s="12">
         <f t="shared" si="200"/>
-        <v>0.65712616822429903</v>
-      </c>
-      <c r="O38" s="12">
+        <v>0.3454627959422899</v>
+      </c>
+      <c r="AV38" s="12">
         <f t="shared" si="200"/>
-        <v>0.3229193341869398</v>
-      </c>
-      <c r="P38" s="12">
-        <f t="shared" si="200"/>
-        <v>0.29100391134289438</v>
-      </c>
-      <c r="Q38" s="12">
-        <f t="shared" si="200"/>
-        <v>0.308005082592122</v>
-      </c>
-      <c r="R38" s="12">
-        <f t="shared" si="200"/>
-        <v>0.3</v>
-      </c>
-      <c r="S38" s="12">
-        <f t="shared" ref="S38:AH38" si="201">S24/S6</f>
-        <v>0.29704364148287188</v>
-      </c>
-      <c r="T38" s="12">
+        <v>0.35133302849880699</v>
+      </c>
+      <c r="AW38" s="12">
+        <f t="shared" ref="AW38:BA38" si="201">AW24/AW6</f>
+        <v>0.35344770368758954</v>
+      </c>
+      <c r="AX38" s="12">
         <f t="shared" si="201"/>
-        <v>0.26858185134518925</v>
-      </c>
-      <c r="U38" s="12">
+        <v>0.35553842527345508</v>
+      </c>
+      <c r="AY38" s="12">
         <f t="shared" si="201"/>
-        <v>0.25625986916309496</v>
-      </c>
-      <c r="V38" s="12">
+        <v>0.3576053649291141</v>
+      </c>
+      <c r="AZ38" s="12">
         <f t="shared" si="201"/>
-        <v>0.25988950276243095</v>
-      </c>
-      <c r="W38" s="12">
+        <v>0.35964869140565164</v>
+      </c>
+      <c r="BA38" s="12">
         <f t="shared" si="201"/>
-        <v>0.2678839957035446</v>
-      </c>
-      <c r="X38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.26889534883720928</v>
-      </c>
-      <c r="Y38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.28691206543967279</v>
-      </c>
-      <c r="Z38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.29377971473851028</v>
-      </c>
-      <c r="AA38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.11964492473948282</v>
-      </c>
-      <c r="AB38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.29628932002260311</v>
-      </c>
-      <c r="AC38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.31139053254437871</v>
-      </c>
-      <c r="AD38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.30021405636817694</v>
-      </c>
-      <c r="AE38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.31694084704235209</v>
-      </c>
-      <c r="AF38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.32161039290778937</v>
-      </c>
-      <c r="AG38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.32127026929219088</v>
-      </c>
-      <c r="AH38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.32437544134464757</v>
-      </c>
-      <c r="AJ38" s="12">
-        <f t="shared" ref="AJ38:AV38" si="202">AJ24/AJ6</f>
-        <v>0.26405243698247322</v>
-      </c>
-      <c r="AK38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.26424723434196229</v>
-      </c>
-      <c r="AL38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.40876593099160707</v>
-      </c>
-      <c r="AM38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.30547988596769082</v>
-      </c>
-      <c r="AN38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.27013518118823127</v>
-      </c>
-      <c r="AO38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.27966407336802512</v>
-      </c>
-      <c r="AP38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.25854452452917925</v>
-      </c>
-      <c r="AQ38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.31085598652842067</v>
-      </c>
-      <c r="AR38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.33299110258078046</v>
-      </c>
-      <c r="AS38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.34192490681813836</v>
-      </c>
-      <c r="AT38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.34874290952235348</v>
-      </c>
-      <c r="AU38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.35314686020074731</v>
-      </c>
-      <c r="AV38" s="12">
-        <f t="shared" si="202"/>
-        <v>0.35888166970730123</v>
-      </c>
-      <c r="AW38" s="12">
-        <f t="shared" ref="AW38:BA38" si="203">AW24/AW6</f>
-        <v>0.36093612486155235</v>
-      </c>
-      <c r="AX38" s="12">
-        <f t="shared" si="203"/>
-        <v>0.36296722105771478</v>
-      </c>
-      <c r="AY38" s="12">
-        <f t="shared" si="203"/>
-        <v>0.36497512422202655</v>
-      </c>
-      <c r="AZ38" s="12">
-        <f t="shared" si="203"/>
-        <v>0.36695999741707369</v>
-      </c>
-      <c r="BA38" s="12">
-        <f t="shared" si="203"/>
-        <v>0.36892200084561133</v>
+        <v>0.36166857053688578</v>
       </c>
       <c r="BC38" t="s">
         <v>51</v>
       </c>
       <c r="BD38" s="6">
         <f>Main!D3</f>
-        <v>412.39</v>
+        <v>362.17</v>
       </c>
     </row>
-    <row r="39" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:56" x14ac:dyDescent="0.3">
       <c r="BC39" s="1" t="s">
         <v>52</v>
       </c>
       <c r="BD39" s="13">
         <f>BD37/BD38-1</f>
-        <v>-0.14407415761800457</v>
+        <v>-7.2226029407125303E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:56" x14ac:dyDescent="0.3">
       <c r="BC40" t="s">
         <v>53</v>
       </c>
       <c r="BD40" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="2:57" x14ac:dyDescent="0.3">
-      <c r="BE44" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/ADBE.xlsx
+++ b/Financial Analysis/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFF1873-C50F-4D46-9A99-FA0984226A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BCA65D-B403-4D7A-B226-83A235D4838F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{030F5AE8-2ADC-4446-9A99-98294E370635}"/>
   </bookViews>
@@ -848,14 +848,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>362.17</v>
+        <v>350.14</v>
       </c>
       <c r="E3" s="4">
-        <v>45909</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45909</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="4">
         <v>45911</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>153632.514</v>
+        <v>148529.38799999998</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>39</v>
@@ -942,7 +942,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>154085.514</v>
+        <v>148982.38799999998</v>
       </c>
     </row>
   </sheetData>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="BD38" s="6">
         <f>Main!D3</f>
-        <v>362.17</v>
+        <v>350.14</v>
       </c>
     </row>
     <row r="39" spans="2:56" x14ac:dyDescent="0.3">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="BD39" s="13">
         <f>BD37/BD38-1</f>
-        <v>-7.2226029407125303E-2</v>
+        <v>-4.0349863112979167E-2</v>
       </c>
     </row>
     <row r="40" spans="2:56" x14ac:dyDescent="0.3">

--- a/Financial Analysis/ADBE.xlsx
+++ b/Financial Analysis/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BCA65D-B403-4D7A-B226-83A235D4838F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E347E133-1BF4-49D6-B1FE-C2D7C89CD371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{030F5AE8-2ADC-4446-9A99-98294E370635}"/>
   </bookViews>
@@ -298,7 +298,7 @@
     <t>Service revenue y/y</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Undervalued</t>
   </si>
 </sst>
 </file>
@@ -416,13 +416,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
@@ -440,7 +440,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24452580" y="0"/>
+          <a:off x="25199340" y="0"/>
           <a:ext cx="0" cy="8328660"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -848,17 +848,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>350.14</v>
+        <v>271.73</v>
       </c>
       <c r="E3" s="4">
-        <v>45937</v>
+        <v>46059</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="4">
-        <v>45911</v>
+        <v>46093</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>37</v>
@@ -871,11 +871,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>424.2</f>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>38</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>148529.38799999998</v>
+        <v>113311.41</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>39</v>
@@ -942,7 +942,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>148982.38799999998</v>
+        <v>113764.41</v>
       </c>
     </row>
   </sheetData>
@@ -1285,12 +1285,11 @@
         <v>5641</v>
       </c>
       <c r="AG3" s="14">
-        <f>AC3*1.11</f>
-        <v>5749.8</v>
+        <v>5989</v>
       </c>
       <c r="AH3" s="14">
-        <f>AD3*1.1</f>
-        <v>5901.5000000000009</v>
+        <f>AD3*1.12</f>
+        <v>6008.8</v>
       </c>
       <c r="AI3" s="7"/>
       <c r="AM3" s="5">
@@ -1311,7 +1310,7 @@
       </c>
       <c r="AQ3" s="5">
         <f>SUM(AE3:AH3)</f>
-        <v>22775.3</v>
+        <v>23121.8</v>
       </c>
     </row>
     <row r="4" spans="2:53" x14ac:dyDescent="0.3">
@@ -1385,12 +1384,10 @@
         <v>88</v>
       </c>
       <c r="AG4" s="14">
-        <f>AC4*1.02</f>
-        <v>83.64</v>
+        <v>74</v>
       </c>
       <c r="AH4" s="14">
-        <f>AD4*1.02</f>
-        <v>82.62</v>
+        <v>70</v>
       </c>
       <c r="AI4" s="7"/>
       <c r="AM4" s="5">
@@ -1411,7 +1408,7 @@
       </c>
       <c r="AQ4" s="5">
         <f>SUM(AE4:AH4)</f>
-        <v>349.26</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="2:53" x14ac:dyDescent="0.3">
@@ -1485,12 +1482,11 @@
         <v>144</v>
       </c>
       <c r="AG5" s="14">
-        <f t="shared" ref="AG5:AH5" si="0">AC5*0.95</f>
-        <v>138.69999999999999</v>
+        <v>131</v>
       </c>
       <c r="AH5" s="14">
-        <f t="shared" si="0"/>
-        <v>152</v>
+        <f>AD5*0.92</f>
+        <v>147.20000000000002</v>
       </c>
       <c r="AI5" s="7"/>
       <c r="AM5" s="5">
@@ -1511,7 +1507,7 @@
       </c>
       <c r="AQ5" s="5">
         <f>SUM(AE5:AH5)</f>
-        <v>570.70000000000005</v>
+        <v>558.20000000000005</v>
       </c>
     </row>
     <row r="6" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1555,84 +1551,84 @@
         <v>3424</v>
       </c>
       <c r="O6" s="9">
-        <f t="shared" ref="O6:AE6" si="1">SUM(O3:O5)</f>
+        <f t="shared" ref="O6:AE6" si="0">SUM(O3:O5)</f>
         <v>3905</v>
       </c>
       <c r="P6" s="9">
+        <f t="shared" si="0"/>
+        <v>3835</v>
+      </c>
+      <c r="Q6" s="9">
+        <f t="shared" si="0"/>
+        <v>3935</v>
+      </c>
+      <c r="R6" s="9">
+        <f t="shared" si="0"/>
+        <v>4110</v>
+      </c>
+      <c r="S6" s="9">
+        <f t="shared" si="0"/>
+        <v>4262</v>
+      </c>
+      <c r="T6" s="9">
+        <f t="shared" si="0"/>
+        <v>4386</v>
+      </c>
+      <c r="U6" s="9">
+        <f t="shared" si="0"/>
+        <v>4433</v>
+      </c>
+      <c r="V6" s="9">
+        <f t="shared" si="0"/>
+        <v>4525</v>
+      </c>
+      <c r="W6" s="9">
+        <f t="shared" si="0"/>
+        <v>4655</v>
+      </c>
+      <c r="X6" s="9">
+        <f t="shared" si="0"/>
+        <v>4816</v>
+      </c>
+      <c r="Y6" s="9">
+        <f t="shared" si="0"/>
+        <v>4890</v>
+      </c>
+      <c r="Z6" s="9">
+        <f t="shared" si="0"/>
+        <v>5048</v>
+      </c>
+      <c r="AA6" s="9">
+        <f t="shared" si="0"/>
+        <v>5182</v>
+      </c>
+      <c r="AB6" s="9">
+        <f t="shared" si="0"/>
+        <v>5309</v>
+      </c>
+      <c r="AC6" s="9">
+        <f t="shared" si="0"/>
+        <v>5408</v>
+      </c>
+      <c r="AD6" s="9">
+        <f t="shared" si="0"/>
+        <v>5606</v>
+      </c>
+      <c r="AE6" s="9">
+        <f t="shared" si="0"/>
+        <v>5714</v>
+      </c>
+      <c r="AF6" s="9">
+        <f t="shared" ref="AF6:AH6" si="1">SUM(AF3:AF5)</f>
+        <v>5873</v>
+      </c>
+      <c r="AG6" s="9">
         <f t="shared" si="1"/>
-        <v>3835</v>
-      </c>
-      <c r="Q6" s="9">
+        <v>6194</v>
+      </c>
+      <c r="AH6" s="9">
         <f t="shared" si="1"/>
-        <v>3935</v>
-      </c>
-      <c r="R6" s="9">
-        <f t="shared" si="1"/>
-        <v>4110</v>
-      </c>
-      <c r="S6" s="9">
-        <f t="shared" si="1"/>
-        <v>4262</v>
-      </c>
-      <c r="T6" s="9">
-        <f t="shared" si="1"/>
-        <v>4386</v>
-      </c>
-      <c r="U6" s="9">
-        <f t="shared" si="1"/>
-        <v>4433</v>
-      </c>
-      <c r="V6" s="9">
-        <f t="shared" si="1"/>
-        <v>4525</v>
-      </c>
-      <c r="W6" s="9">
-        <f t="shared" si="1"/>
-        <v>4655</v>
-      </c>
-      <c r="X6" s="9">
-        <f t="shared" si="1"/>
-        <v>4816</v>
-      </c>
-      <c r="Y6" s="9">
-        <f t="shared" si="1"/>
-        <v>4890</v>
-      </c>
-      <c r="Z6" s="9">
-        <f t="shared" si="1"/>
-        <v>5048</v>
-      </c>
-      <c r="AA6" s="9">
-        <f t="shared" si="1"/>
-        <v>5182</v>
-      </c>
-      <c r="AB6" s="9">
-        <f t="shared" si="1"/>
-        <v>5309</v>
-      </c>
-      <c r="AC6" s="9">
-        <f t="shared" si="1"/>
-        <v>5408</v>
-      </c>
-      <c r="AD6" s="9">
-        <f t="shared" si="1"/>
-        <v>5606</v>
-      </c>
-      <c r="AE6" s="9">
-        <f t="shared" si="1"/>
-        <v>5714</v>
-      </c>
-      <c r="AF6" s="9">
-        <f t="shared" ref="AF6:AH6" si="2">SUM(AF3:AF5)</f>
-        <v>5873</v>
-      </c>
-      <c r="AG6" s="9">
-        <f t="shared" si="2"/>
-        <v>5972.14</v>
-      </c>
-      <c r="AH6" s="9">
-        <f t="shared" si="2"/>
-        <v>6136.1200000000008</v>
+        <v>6226</v>
       </c>
       <c r="AJ6" s="9">
         <f>SUM(C6:F6)</f>
@@ -1664,47 +1660,47 @@
       </c>
       <c r="AQ6" s="9">
         <f>SUM(AQ3:AQ5)</f>
-        <v>23695.26</v>
+        <v>24007</v>
       </c>
       <c r="AR6" s="9">
-        <f>AQ6*1.08</f>
-        <v>25590.880799999999</v>
+        <f>AQ6*1.1</f>
+        <v>26407.7</v>
       </c>
       <c r="AS6" s="9">
-        <f>AR6*1.05</f>
-        <v>26870.42484</v>
+        <f>AR6*1.08</f>
+        <v>28520.316000000003</v>
       </c>
       <c r="AT6" s="9">
-        <f>AS6*1.04</f>
-        <v>27945.241833600001</v>
+        <f>AS6*1.05</f>
+        <v>29946.331800000004</v>
       </c>
       <c r="AU6" s="9">
-        <f>AT6*1.03</f>
-        <v>28783.599088608004</v>
+        <f>AT6*1.04</f>
+        <v>31144.185072000004</v>
       </c>
       <c r="AV6" s="9">
         <f>AU6*1.03</f>
-        <v>29647.107061266244</v>
+        <v>32078.510624160004</v>
       </c>
       <c r="AW6" s="9">
-        <f t="shared" ref="AW6" si="3">AV6*1.02</f>
-        <v>30240.049202491569</v>
+        <f t="shared" ref="AW6" si="2">AV6*1.02</f>
+        <v>32720.080836643207</v>
       </c>
       <c r="AX6" s="9">
-        <f t="shared" ref="AX6" si="4">AW6*1.02</f>
-        <v>30844.8501865414</v>
+        <f t="shared" ref="AX6" si="3">AW6*1.02</f>
+        <v>33374.482453376069</v>
       </c>
       <c r="AY6" s="9">
-        <f t="shared" ref="AY6" si="5">AX6*1.02</f>
-        <v>31461.747190272228</v>
+        <f t="shared" ref="AY6" si="4">AX6*1.02</f>
+        <v>34041.972102443593</v>
       </c>
       <c r="AZ6" s="9">
-        <f t="shared" ref="AZ6" si="6">AY6*1.02</f>
-        <v>32090.982134077673</v>
+        <f t="shared" ref="AZ6" si="5">AY6*1.02</f>
+        <v>34722.811544492462</v>
       </c>
       <c r="BA6" s="9">
-        <f t="shared" ref="BA6" si="7">AZ6*1.02</f>
-        <v>32732.801776759228</v>
+        <f t="shared" ref="BA6" si="6">AZ6*1.02</f>
+        <v>35417.267775382315</v>
       </c>
     </row>
     <row r="7" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1777,7 +1773,9 @@
       <c r="AF7" s="5">
         <v>505</v>
       </c>
-      <c r="AG7" s="5"/>
+      <c r="AG7" s="5">
+        <v>522</v>
+      </c>
       <c r="AH7" s="5"/>
       <c r="AJ7" s="9"/>
       <c r="AK7" s="9"/>
@@ -1800,7 +1798,7 @@
       </c>
       <c r="AQ7" s="5">
         <f>SUM(AE7:AH7)</f>
-        <v>995</v>
+        <v>1517</v>
       </c>
       <c r="AR7" s="9"/>
       <c r="AS7" s="9"/>
@@ -1883,7 +1881,9 @@
       <c r="AF8" s="5">
         <v>6</v>
       </c>
-      <c r="AG8" s="5"/>
+      <c r="AG8" s="5">
+        <v>6</v>
+      </c>
       <c r="AH8" s="5"/>
       <c r="AJ8" s="9"/>
       <c r="AK8" s="9"/>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AQ8" s="5">
         <f>SUM(AE8:AH8)</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AR8" s="9"/>
       <c r="AS8" s="9"/>
@@ -1989,7 +1989,9 @@
       <c r="AF9" s="5">
         <v>127</v>
       </c>
-      <c r="AG9" s="5"/>
+      <c r="AG9" s="5">
+        <v>121</v>
+      </c>
       <c r="AH9" s="5"/>
       <c r="AJ9" s="9"/>
       <c r="AK9" s="9"/>
@@ -2012,7 +2014,7 @@
       </c>
       <c r="AQ9" s="5">
         <f>SUM(AE9:AH9)</f>
-        <v>253</v>
+        <v>374</v>
       </c>
       <c r="AR9" s="9"/>
       <c r="AS9" s="9"/>
@@ -2066,84 +2068,84 @@
         <v>428</v>
       </c>
       <c r="O10" s="5">
-        <f t="shared" ref="O10:AF10" si="8">SUM(O7:O9)</f>
+        <f t="shared" ref="O10:AG10" si="7">SUM(O7:O9)</f>
         <v>447</v>
       </c>
       <c r="P10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>444</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>467</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>507</v>
       </c>
       <c r="S10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>512</v>
       </c>
       <c r="T10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>539</v>
       </c>
       <c r="U10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>546</v>
       </c>
       <c r="V10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>568</v>
       </c>
       <c r="W10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>568</v>
       </c>
       <c r="X10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>572</v>
       </c>
       <c r="Y10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>580</v>
       </c>
       <c r="Z10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>634</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>590</v>
       </c>
       <c r="AB10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>598</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>554</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>616</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>622</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>638</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" ref="AG10:AH10" si="9">AG6-AG11</f>
-        <v>656.9354000000003</v>
+        <f t="shared" si="7"/>
+        <v>649</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="9"/>
-        <v>674.97320000000036</v>
+        <f t="shared" ref="AH10" si="8">AH6-AH11</f>
+        <v>684.85999999999967</v>
       </c>
       <c r="AJ10" s="5">
         <f>SUM(C10:F10)</f>
@@ -2175,47 +2177,47 @@
       </c>
       <c r="AQ10" s="5">
         <f>SUM(AQ7:AQ9)</f>
-        <v>1260</v>
+        <v>1909</v>
       </c>
       <c r="AR10" s="5">
-        <f t="shared" ref="AR10:AV10" si="10">AR6-AR11</f>
-        <v>2814.9968879999979</v>
+        <f t="shared" ref="AR10:AV10" si="9">AR6-AR11</f>
+        <v>2904.8469999999979</v>
       </c>
       <c r="AS10" s="5">
+        <f t="shared" si="9"/>
+        <v>3137.2347599999994</v>
+      </c>
+      <c r="AT10" s="5">
+        <f t="shared" si="9"/>
+        <v>3294.096497999999</v>
+      </c>
+      <c r="AU10" s="5">
+        <f t="shared" si="9"/>
+        <v>3425.8603579199989</v>
+      </c>
+      <c r="AV10" s="5">
+        <f t="shared" si="9"/>
+        <v>3528.6361686575983</v>
+      </c>
+      <c r="AW10" s="5">
+        <f t="shared" ref="AW10:BA10" si="10">AW6-AW11</f>
+        <v>3599.2088920307506</v>
+      </c>
+      <c r="AX10" s="5">
         <f t="shared" si="10"/>
-        <v>2955.746732399999</v>
-      </c>
-      <c r="AT10" s="5">
+        <v>3671.1930698713659</v>
+      </c>
+      <c r="AY10" s="5">
         <f t="shared" si="10"/>
-        <v>3073.9766016959984</v>
-      </c>
-      <c r="AU10" s="5">
+        <v>3744.6169312687962</v>
+      </c>
+      <c r="AZ10" s="5">
         <f t="shared" si="10"/>
-        <v>3166.1958997468791</v>
-      </c>
-      <c r="AV10" s="5">
+        <v>3819.5092698941698</v>
+      </c>
+      <c r="BA10" s="5">
         <f t="shared" si="10"/>
-        <v>3261.1817767392859</v>
-      </c>
-      <c r="AW10" s="5">
-        <f t="shared" ref="AW10:BA10" si="11">AW6-AW11</f>
-        <v>3326.4054122740708</v>
-      </c>
-      <c r="AX10" s="5">
-        <f t="shared" si="11"/>
-        <v>3392.933520519553</v>
-      </c>
-      <c r="AY10" s="5">
-        <f t="shared" si="11"/>
-        <v>3460.7921909299439</v>
-      </c>
-      <c r="AZ10" s="5">
-        <f t="shared" si="11"/>
-        <v>3530.0080347485418</v>
-      </c>
-      <c r="BA10" s="5">
-        <f t="shared" si="11"/>
-        <v>3600.608195443514</v>
+        <v>3895.8994552920558</v>
       </c>
     </row>
     <row r="11" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2223,204 +2225,204 @@
         <v>24</v>
       </c>
       <c r="C11" s="9">
-        <f t="shared" ref="C11:O11" si="12">C6-C10</f>
+        <f t="shared" ref="C11:O11" si="11">C6-C10</f>
         <v>1820.0499999999997</v>
       </c>
       <c r="D11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1914.0200000000002</v>
       </c>
       <c r="E11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1995.59</v>
       </c>
       <c r="F11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1824.8999999999999</v>
       </c>
       <c r="G11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2204</v>
       </c>
       <c r="H11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2337</v>
       </c>
       <c r="I11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2418</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2539.96</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2639</v>
       </c>
       <c r="L11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2713</v>
       </c>
       <c r="M11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2798</v>
       </c>
       <c r="N11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2996</v>
       </c>
       <c r="O11" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>3458</v>
       </c>
       <c r="P11" s="9">
-        <f t="shared" ref="P11" si="13">P6-P10</f>
+        <f t="shared" ref="P11" si="12">P6-P10</f>
         <v>3391</v>
       </c>
       <c r="Q11" s="9">
-        <f t="shared" ref="Q11" si="14">Q6-Q10</f>
+        <f t="shared" ref="Q11" si="13">Q6-Q10</f>
         <v>3468</v>
       </c>
       <c r="R11" s="9">
-        <f t="shared" ref="R11" si="15">R6-R10</f>
+        <f t="shared" ref="R11" si="14">R6-R10</f>
         <v>3603</v>
       </c>
       <c r="S11" s="9">
-        <f t="shared" ref="S11:U11" si="16">S6-S10</f>
+        <f t="shared" ref="S11:U11" si="15">S6-S10</f>
         <v>3750</v>
       </c>
       <c r="T11" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>3847</v>
       </c>
       <c r="U11" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>3887</v>
       </c>
       <c r="V11" s="9">
-        <f t="shared" ref="V11" si="17">V6-V10</f>
+        <f t="shared" ref="V11" si="16">V6-V10</f>
         <v>3957</v>
       </c>
       <c r="W11" s="9">
-        <f t="shared" ref="W11:X11" si="18">W6-W10</f>
+        <f t="shared" ref="W11:X11" si="17">W6-W10</f>
         <v>4087</v>
       </c>
       <c r="X11" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>4244</v>
       </c>
       <c r="Y11" s="9">
-        <f t="shared" ref="Y11" si="19">Y6-Y10</f>
+        <f t="shared" ref="Y11" si="18">Y6-Y10</f>
         <v>4310</v>
       </c>
       <c r="Z11" s="9">
-        <f t="shared" ref="Z11" si="20">Z6-Z10</f>
+        <f t="shared" ref="Z11" si="19">Z6-Z10</f>
         <v>4414</v>
       </c>
       <c r="AA11" s="9">
-        <f t="shared" ref="AA11:AB11" si="21">AA6-AA10</f>
+        <f t="shared" ref="AA11:AB11" si="20">AA6-AA10</f>
         <v>4592</v>
       </c>
       <c r="AB11" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>4711</v>
       </c>
       <c r="AC11" s="9">
-        <f t="shared" ref="AC11" si="22">AC6-AC10</f>
+        <f t="shared" ref="AC11" si="21">AC6-AC10</f>
         <v>4854</v>
       </c>
       <c r="AD11" s="9">
-        <f t="shared" ref="AD11" si="23">AD6-AD10</f>
+        <f t="shared" ref="AD11" si="22">AD6-AD10</f>
         <v>4990</v>
       </c>
       <c r="AE11" s="9">
-        <f t="shared" ref="AE11:AF11" si="24">AE6-AE10</f>
+        <f t="shared" ref="AE11:AG11" si="23">AE6-AE10</f>
         <v>5092</v>
       </c>
       <c r="AF11" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>5235</v>
       </c>
       <c r="AG11" s="9">
-        <f t="shared" ref="AG11:AH11" si="25">AG6*0.89</f>
-        <v>5315.2046</v>
+        <f t="shared" si="23"/>
+        <v>5545</v>
       </c>
       <c r="AH11" s="9">
+        <f t="shared" ref="AH11" si="24">AH6*0.89</f>
+        <v>5541.14</v>
+      </c>
+      <c r="AJ11" s="9">
+        <f t="shared" ref="AJ11:AP11" si="25">AJ6-AJ10</f>
+        <v>7554.5599999999995</v>
+      </c>
+      <c r="AK11" s="9">
         <f t="shared" si="25"/>
-        <v>5461.1468000000004</v>
-      </c>
-      <c r="AJ11" s="9">
-        <f t="shared" ref="AJ11:AP11" si="26">AJ6-AJ10</f>
-        <v>7554.5599999999995</v>
-      </c>
-      <c r="AK11" s="9">
-        <f t="shared" si="26"/>
         <v>9498.9600000000009</v>
       </c>
       <c r="AL11" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>11146</v>
       </c>
       <c r="AM11" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>13920</v>
       </c>
       <c r="AN11" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>15441</v>
       </c>
       <c r="AO11" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>17055</v>
       </c>
       <c r="AP11" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>19147</v>
       </c>
       <c r="AQ11" s="9">
         <f>AQ6*0.89</f>
-        <v>21088.7814</v>
+        <v>21366.23</v>
       </c>
       <c r="AR11" s="9">
         <f>AR6*0.89</f>
-        <v>22775.883912000001</v>
+        <v>23502.853000000003</v>
       </c>
       <c r="AS11" s="9">
-        <f t="shared" ref="AS11:BA11" si="27">AS6*0.89</f>
-        <v>23914.678107600001</v>
+        <f t="shared" ref="AS11:BA11" si="26">AS6*0.89</f>
+        <v>25383.081240000003</v>
       </c>
       <c r="AT11" s="9">
-        <f t="shared" si="27"/>
-        <v>24871.265231904003</v>
+        <f t="shared" si="26"/>
+        <v>26652.235302000005</v>
       </c>
       <c r="AU11" s="9">
-        <f t="shared" si="27"/>
-        <v>25617.403188861124</v>
+        <f t="shared" si="26"/>
+        <v>27718.324714080005</v>
       </c>
       <c r="AV11" s="9">
-        <f t="shared" si="27"/>
-        <v>26385.925284526958</v>
+        <f t="shared" si="26"/>
+        <v>28549.874455502406</v>
       </c>
       <c r="AW11" s="9">
-        <f t="shared" si="27"/>
-        <v>26913.643790217498</v>
+        <f t="shared" si="26"/>
+        <v>29120.871944612456</v>
       </c>
       <c r="AX11" s="9">
-        <f t="shared" si="27"/>
-        <v>27451.916666021847</v>
+        <f t="shared" si="26"/>
+        <v>29703.289383504703</v>
       </c>
       <c r="AY11" s="9">
-        <f t="shared" si="27"/>
-        <v>28000.954999342284</v>
+        <f t="shared" si="26"/>
+        <v>30297.355171174797</v>
       </c>
       <c r="AZ11" s="9">
-        <f t="shared" si="27"/>
-        <v>28560.974099329131</v>
+        <f t="shared" si="26"/>
+        <v>30903.302274598293</v>
       </c>
       <c r="BA11" s="9">
-        <f t="shared" si="27"/>
-        <v>29132.193581315714</v>
+        <f t="shared" si="26"/>
+        <v>31521.36832009026</v>
       </c>
     </row>
     <row r="12" spans="2:53" x14ac:dyDescent="0.3">
@@ -2518,12 +2520,11 @@
         <v>1082</v>
       </c>
       <c r="AG12" s="5">
-        <f>AC12*1.07</f>
-        <v>1093.54</v>
+        <v>1098</v>
       </c>
       <c r="AH12" s="5">
-        <f>AD12*1.1</f>
-        <v>1098.9000000000001</v>
+        <f>AD12*1.11</f>
+        <v>1108.8900000000001</v>
       </c>
       <c r="AJ12" s="5">
         <f>SUM(C12:F12)</f>
@@ -2555,47 +2556,47 @@
       </c>
       <c r="AQ12" s="5">
         <f>SUM(AE12:AH12)</f>
-        <v>4300.4400000000005</v>
+        <v>4314.8900000000003</v>
       </c>
       <c r="AR12" s="5">
         <f>AQ12*1.07</f>
-        <v>4601.470800000001</v>
+        <v>4616.9323000000004</v>
       </c>
       <c r="AS12" s="5">
         <f>AR12*1.05</f>
-        <v>4831.5443400000013</v>
+        <v>4847.7789150000008</v>
       </c>
       <c r="AT12" s="5">
         <f>AS12*1.04</f>
-        <v>5024.8061136000015</v>
+        <v>5041.6900716000009</v>
       </c>
       <c r="AU12" s="5">
         <f>AT12*1.03</f>
-        <v>5175.5502970080015</v>
+        <v>5192.9407737480014</v>
       </c>
       <c r="AV12" s="5">
-        <f t="shared" ref="AV12" si="28">AU12*1.02</f>
-        <v>5279.0613029481619</v>
+        <f t="shared" ref="AV12" si="27">AU12*1.02</f>
+        <v>5296.7995892229619</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" ref="AW12" si="29">AV12*1.02</f>
-        <v>5384.6425290071256</v>
+        <f t="shared" ref="AW12" si="28">AV12*1.02</f>
+        <v>5402.7355810074214</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" ref="AX12" si="30">AW12*1.02</f>
-        <v>5492.3353795872681</v>
+        <f t="shared" ref="AX12" si="29">AW12*1.02</f>
+        <v>5510.7902926275701</v>
       </c>
       <c r="AY12" s="5">
-        <f t="shared" ref="AY12" si="31">AX12*1.02</f>
-        <v>5602.1820871790133</v>
+        <f t="shared" ref="AY12" si="30">AX12*1.02</f>
+        <v>5621.0060984801212</v>
       </c>
       <c r="AZ12" s="5">
-        <f t="shared" ref="AZ12" si="32">AY12*1.02</f>
-        <v>5714.2257289225936</v>
+        <f t="shared" ref="AZ12" si="31">AY12*1.02</f>
+        <v>5733.4262204497236</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" ref="BA12" si="33">AZ12*1.02</f>
-        <v>5828.5102435010458</v>
+        <f t="shared" ref="BA12" si="32">AZ12*1.02</f>
+        <v>5848.0947448587185</v>
       </c>
     </row>
     <row r="13" spans="2:53" x14ac:dyDescent="0.3">
@@ -2693,12 +2694,11 @@
         <v>1626</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" ref="AG13:AH13" si="34">AG6*0.26</f>
-        <v>1552.7564000000002</v>
+        <v>1728</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="34"/>
-        <v>1595.3912000000003</v>
+        <f>AH6*0.28</f>
+        <v>1743.2800000000002</v>
       </c>
       <c r="AJ13" s="5">
         <f>SUM(C13:F13)</f>
@@ -2730,47 +2730,47 @@
       </c>
       <c r="AQ13" s="5">
         <f>SUM(AE13:AH13)</f>
-        <v>6269.1476000000002</v>
+        <v>6592.2800000000007</v>
       </c>
       <c r="AR13" s="5">
-        <f>AQ13*1.02</f>
-        <v>6394.5305520000002</v>
+        <f>AQ13*1.05</f>
+        <v>6921.8940000000011</v>
       </c>
       <c r="AS13" s="5">
-        <f t="shared" ref="AS13:AV13" si="35">AR13*1.01</f>
-        <v>6458.4758575200003</v>
+        <f>AR13*1.03</f>
+        <v>7129.5508200000013</v>
       </c>
       <c r="AT13" s="5">
-        <f t="shared" si="35"/>
-        <v>6523.0606160952002</v>
+        <f>AS13*1.02</f>
+        <v>7272.141836400001</v>
       </c>
       <c r="AU13" s="5">
-        <f t="shared" si="35"/>
-        <v>6588.2912222561527</v>
+        <f t="shared" ref="AU13:AV13" si="33">AT13*1.01</f>
+        <v>7344.8632547640009</v>
       </c>
       <c r="AV13" s="5">
-        <f t="shared" si="35"/>
-        <v>6654.1741344787142</v>
+        <f t="shared" si="33"/>
+        <v>7418.3118873116409</v>
       </c>
       <c r="AW13" s="5">
-        <f t="shared" ref="AW13:AW14" si="36">AV13*1.01</f>
-        <v>6720.7158758235018</v>
+        <f t="shared" ref="AW13" si="34">AV13*1.01</f>
+        <v>7492.4950061847576</v>
       </c>
       <c r="AX13" s="5">
-        <f t="shared" ref="AX13:AX14" si="37">AW13*1.01</f>
-        <v>6787.9230345817368</v>
+        <f t="shared" ref="AX13" si="35">AW13*1.01</f>
+        <v>7567.4199562466056</v>
       </c>
       <c r="AY13" s="5">
-        <f t="shared" ref="AY13:AY14" si="38">AX13*1.01</f>
-        <v>6855.8022649275545</v>
+        <f t="shared" ref="AY13" si="36">AX13*1.01</f>
+        <v>7643.0941558090717</v>
       </c>
       <c r="AZ13" s="5">
-        <f t="shared" ref="AZ13:AZ14" si="39">AY13*1.01</f>
-        <v>6924.3602875768302</v>
+        <f t="shared" ref="AZ13" si="37">AY13*1.01</f>
+        <v>7719.5250973671627</v>
       </c>
       <c r="BA13" s="5">
-        <f t="shared" ref="BA13:BA14" si="40">AZ13*1.01</f>
-        <v>6993.6038904525985</v>
+        <f t="shared" ref="BA13" si="38">AZ13*1.01</f>
+        <v>7796.7203483408348</v>
       </c>
     </row>
     <row r="14" spans="2:53" x14ac:dyDescent="0.3">
@@ -2868,12 +2868,11 @@
         <v>377</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" ref="AG14" si="41">AC14*1.03</f>
-        <v>376.98</v>
+        <v>421</v>
       </c>
       <c r="AH14" s="5">
-        <f>AD14*0.87</f>
-        <v>396.71999999999997</v>
+        <f>AD14*1.15</f>
+        <v>524.4</v>
       </c>
       <c r="AJ14" s="5">
         <f>SUM(C14:F14)</f>
@@ -2905,47 +2904,47 @@
       </c>
       <c r="AQ14" s="5">
         <f>SUM(AE14:AH14)</f>
-        <v>1517.7</v>
+        <v>1689.4</v>
       </c>
       <c r="AR14" s="5">
-        <f>AQ14*1.02</f>
-        <v>1548.0540000000001</v>
+        <f>AQ14*1.05</f>
+        <v>1773.8700000000001</v>
       </c>
       <c r="AS14" s="5">
-        <f>AR14*1.02</f>
-        <v>1579.0150800000001</v>
+        <f>AR14*1.04</f>
+        <v>1844.8248000000001</v>
       </c>
       <c r="AT14" s="5">
-        <f t="shared" ref="AT14:AV14" si="42">AS14*1.01</f>
-        <v>1594.8052308000001</v>
+        <f>AS14*1.03</f>
+        <v>1900.1695440000001</v>
       </c>
       <c r="AU14" s="5">
-        <f t="shared" si="42"/>
-        <v>1610.7532831080002</v>
+        <f>AT14*1.02</f>
+        <v>1938.1729348800002</v>
       </c>
       <c r="AV14" s="5">
-        <f t="shared" si="42"/>
-        <v>1626.8608159390803</v>
+        <f t="shared" ref="AV14:BA14" si="39">AU14*1.02</f>
+        <v>1976.9363935776003</v>
       </c>
       <c r="AW14" s="5">
-        <f t="shared" si="36"/>
-        <v>1643.1294240984712</v>
+        <f t="shared" si="39"/>
+        <v>2016.4751214491523</v>
       </c>
       <c r="AX14" s="5">
-        <f t="shared" si="37"/>
-        <v>1659.5607183394559</v>
+        <f t="shared" si="39"/>
+        <v>2056.8046238781353</v>
       </c>
       <c r="AY14" s="5">
-        <f t="shared" si="38"/>
-        <v>1676.1563255228505</v>
+        <f t="shared" si="39"/>
+        <v>2097.940716355698</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="39"/>
-        <v>1692.917888778079</v>
+        <v>2139.8995306828119</v>
       </c>
       <c r="BA14" s="5">
-        <f t="shared" si="40"/>
-        <v>1709.8470676658599</v>
+        <f t="shared" si="39"/>
+        <v>2182.697521296468</v>
       </c>
     </row>
     <row r="15" spans="2:53" x14ac:dyDescent="0.3">
@@ -3044,10 +3043,10 @@
         <v>41</v>
       </c>
       <c r="AG15" s="5">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AH15" s="5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ15" s="5">
         <f>SUM(C15:F15)</f>
@@ -3079,47 +3078,47 @@
       </c>
       <c r="AQ15" s="5">
         <f>SUM(AE15:AH15)</f>
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="AR15" s="5">
-        <f t="shared" ref="AR15:AV15" si="43">AQ15*1.04</f>
-        <v>172.64000000000001</v>
+        <f t="shared" ref="AR15:AV15" si="40">AQ15*1.04</f>
+        <v>163.28</v>
       </c>
       <c r="AS15" s="5">
-        <f t="shared" si="43"/>
-        <v>179.54560000000001</v>
+        <f t="shared" si="40"/>
+        <v>169.81120000000001</v>
       </c>
       <c r="AT15" s="5">
-        <f t="shared" si="43"/>
-        <v>186.72742400000001</v>
+        <f t="shared" si="40"/>
+        <v>176.60364800000002</v>
       </c>
       <c r="AU15" s="5">
-        <f t="shared" si="43"/>
-        <v>194.19652096000002</v>
+        <f t="shared" si="40"/>
+        <v>183.66779392000004</v>
       </c>
       <c r="AV15" s="5">
-        <f t="shared" si="43"/>
-        <v>201.96438179840001</v>
+        <f t="shared" si="40"/>
+        <v>191.01450567680004</v>
       </c>
       <c r="AW15" s="5">
-        <f t="shared" ref="AW15" si="44">AV15*1.04</f>
-        <v>210.04295707033603</v>
+        <f t="shared" ref="AW15" si="41">AV15*1.04</f>
+        <v>198.65508590387205</v>
       </c>
       <c r="AX15" s="5">
-        <f t="shared" ref="AX15" si="45">AW15*1.04</f>
-        <v>218.44467535314948</v>
+        <f t="shared" ref="AX15" si="42">AW15*1.04</f>
+        <v>206.60128934002694</v>
       </c>
       <c r="AY15" s="5">
-        <f t="shared" ref="AY15" si="46">AX15*1.04</f>
-        <v>227.18246236727546</v>
+        <f t="shared" ref="AY15" si="43">AX15*1.04</f>
+        <v>214.86534091362802</v>
       </c>
       <c r="AZ15" s="5">
-        <f t="shared" ref="AZ15" si="47">AY15*1.04</f>
-        <v>236.26976086196649</v>
+        <f t="shared" ref="AZ15" si="44">AY15*1.04</f>
+        <v>223.45995455017314</v>
       </c>
       <c r="BA15" s="5">
-        <f t="shared" ref="BA15" si="48">AZ15*1.04</f>
-        <v>245.72055129644517</v>
+        <f t="shared" ref="BA15" si="45">AZ15*1.04</f>
+        <v>232.39835273218006</v>
       </c>
     </row>
     <row r="16" spans="2:53" x14ac:dyDescent="0.3">
@@ -3127,204 +3126,204 @@
         <v>29</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16:M16" si="49">SUM(C12:C15)</f>
+        <f t="shared" ref="C16:M16" si="46">SUM(C12:C15)</f>
         <v>1117.3100000000002</v>
       </c>
       <c r="D16" s="5">
+        <f t="shared" si="46"/>
+        <v>1215.5400000000002</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="46"/>
+        <v>1276.9699999999998</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="46"/>
+        <v>1384.81</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="46"/>
+        <v>1509</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="46"/>
+        <v>1587</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="46"/>
+        <v>1564</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="46"/>
+        <v>1570.0100000000002</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="shared" si="46"/>
+        <v>1702</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="46"/>
+        <v>1697</v>
+      </c>
+      <c r="M16" s="5">
+        <f t="shared" si="46"/>
+        <v>1729</v>
+      </c>
+      <c r="N16" s="5">
+        <f t="shared" ref="N16:P16" si="47">SUM(N12:N15)</f>
+        <v>1781</v>
+      </c>
+      <c r="O16" s="5">
+        <f t="shared" ref="O16" si="48">SUM(O12:O15)</f>
+        <v>2004</v>
+      </c>
+      <c r="P16" s="5">
+        <f t="shared" si="47"/>
+        <v>1985</v>
+      </c>
+      <c r="Q16" s="5">
+        <f t="shared" ref="Q16:T16" si="49">SUM(Q12:Q15)</f>
+        <v>2027</v>
+      </c>
+      <c r="R16" s="5">
         <f t="shared" si="49"/>
-        <v>1215.5400000000002</v>
-      </c>
-      <c r="E16" s="5">
+        <v>2102</v>
+      </c>
+      <c r="S16" s="5">
         <f t="shared" si="49"/>
-        <v>1276.9699999999998</v>
-      </c>
-      <c r="F16" s="5">
+        <v>2170</v>
+      </c>
+      <c r="T16" s="5">
         <f t="shared" si="49"/>
-        <v>1384.81</v>
-      </c>
-      <c r="G16" s="5">
-        <f t="shared" si="49"/>
-        <v>1509</v>
-      </c>
-      <c r="H16" s="5">
-        <f t="shared" si="49"/>
-        <v>1587</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="49"/>
-        <v>1564</v>
-      </c>
-      <c r="J16" s="5">
-        <f t="shared" si="49"/>
-        <v>1570.0100000000002</v>
-      </c>
-      <c r="K16" s="5">
-        <f t="shared" si="49"/>
-        <v>1702</v>
-      </c>
-      <c r="L16" s="5">
-        <f t="shared" si="49"/>
-        <v>1697</v>
-      </c>
-      <c r="M16" s="5">
-        <f t="shared" si="49"/>
-        <v>1729</v>
-      </c>
-      <c r="N16" s="5">
-        <f t="shared" ref="N16:P16" si="50">SUM(N12:N15)</f>
-        <v>1781</v>
-      </c>
-      <c r="O16" s="5">
-        <f t="shared" ref="O16" si="51">SUM(O12:O15)</f>
-        <v>2004</v>
-      </c>
-      <c r="P16" s="5">
-        <f t="shared" si="50"/>
-        <v>1985</v>
-      </c>
-      <c r="Q16" s="5">
-        <f t="shared" ref="Q16:T16" si="52">SUM(Q12:Q15)</f>
-        <v>2027</v>
-      </c>
-      <c r="R16" s="5">
+        <v>2318</v>
+      </c>
+      <c r="U16" s="5">
+        <f t="shared" ref="U16" si="50">SUM(U12:U15)</f>
+        <v>2403</v>
+      </c>
+      <c r="V16" s="5">
+        <f t="shared" ref="V16" si="51">SUM(V12:V15)</f>
+        <v>2452</v>
+      </c>
+      <c r="W16" s="5">
+        <f t="shared" ref="W16:X16" si="52">SUM(W12:W15)</f>
+        <v>2501</v>
+      </c>
+      <c r="X16" s="5">
         <f t="shared" si="52"/>
-        <v>2102</v>
-      </c>
-      <c r="S16" s="5">
-        <f t="shared" si="52"/>
-        <v>2170</v>
-      </c>
-      <c r="T16" s="5">
-        <f t="shared" si="52"/>
-        <v>2318</v>
-      </c>
-      <c r="U16" s="5">
-        <f t="shared" ref="U16" si="53">SUM(U12:U15)</f>
-        <v>2403</v>
-      </c>
-      <c r="V16" s="5">
-        <f t="shared" ref="V16" si="54">SUM(V12:V15)</f>
-        <v>2452</v>
-      </c>
-      <c r="W16" s="5">
-        <f t="shared" ref="W16:X16" si="55">SUM(W12:W15)</f>
-        <v>2501</v>
-      </c>
-      <c r="X16" s="5">
+        <v>2620</v>
+      </c>
+      <c r="Y16" s="5">
+        <f t="shared" ref="Y16" si="53">SUM(Y12:Y15)</f>
+        <v>2613</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" ref="Z16" si="54">SUM(Z12:Z15)</f>
+        <v>2671</v>
+      </c>
+      <c r="AA16" s="5">
+        <f t="shared" ref="AA16:AB16" si="55">SUM(AA12:AA15)</f>
+        <v>3685</v>
+      </c>
+      <c r="AB16" s="5">
         <f t="shared" si="55"/>
-        <v>2620</v>
-      </c>
-      <c r="Y16" s="5">
-        <f t="shared" ref="Y16" si="56">SUM(Y12:Y15)</f>
-        <v>2613</v>
-      </c>
-      <c r="Z16" s="5">
-        <f t="shared" ref="Z16" si="57">SUM(Z12:Z15)</f>
-        <v>2671</v>
-      </c>
-      <c r="AA16" s="5">
-        <f t="shared" ref="AA16:AB16" si="58">SUM(AA12:AA15)</f>
-        <v>3685</v>
-      </c>
-      <c r="AB16" s="5">
+        <v>2826</v>
+      </c>
+      <c r="AC16" s="5">
+        <f t="shared" ref="AC16" si="56">SUM(AC12:AC15)</f>
+        <v>2862</v>
+      </c>
+      <c r="AD16" s="5">
+        <f t="shared" ref="AD16" si="57">SUM(AD12:AD15)</f>
+        <v>3033</v>
+      </c>
+      <c r="AE16" s="5">
+        <f t="shared" ref="AE16:AH16" si="58">SUM(AE12:AE15)</f>
+        <v>2929</v>
+      </c>
+      <c r="AF16" s="5">
         <f t="shared" si="58"/>
-        <v>2826</v>
-      </c>
-      <c r="AC16" s="5">
-        <f t="shared" ref="AC16" si="59">SUM(AC12:AC15)</f>
-        <v>2862</v>
-      </c>
-      <c r="AD16" s="5">
-        <f t="shared" ref="AD16" si="60">SUM(AD12:AD15)</f>
-        <v>3033</v>
-      </c>
-      <c r="AE16" s="5">
-        <f t="shared" ref="AE16:AH16" si="61">SUM(AE12:AE15)</f>
-        <v>2929</v>
-      </c>
-      <c r="AF16" s="5">
-        <f t="shared" si="61"/>
         <v>3126</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="61"/>
-        <v>3065.2764000000002</v>
+        <f t="shared" si="58"/>
+        <v>3284</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="61"/>
-        <v>3133.0112000000004</v>
+        <f t="shared" si="58"/>
+        <v>3414.57</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" ref="AJ16:AL16" si="62">SUM(AJ12:AJ15)</f>
+        <f t="shared" ref="AJ16:AL16" si="59">SUM(AJ12:AJ15)</f>
         <v>4994.630000000001</v>
       </c>
       <c r="AK16" s="5">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>6230.01</v>
       </c>
       <c r="AL16" s="5">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>6909</v>
       </c>
       <c r="AM16" s="5">
-        <f t="shared" ref="AM16" si="63">SUM(AM12:AM15)</f>
+        <f t="shared" ref="AM16" si="60">SUM(AM12:AM15)</f>
         <v>8118</v>
       </c>
       <c r="AN16" s="5">
-        <f t="shared" ref="AN16" si="64">SUM(AN12:AN15)</f>
+        <f t="shared" ref="AN16" si="61">SUM(AN12:AN15)</f>
         <v>9343</v>
       </c>
       <c r="AO16" s="5">
-        <f t="shared" ref="AO16" si="65">SUM(AO12:AO15)</f>
+        <f t="shared" ref="AO16" si="62">SUM(AO12:AO15)</f>
         <v>10405</v>
       </c>
       <c r="AP16" s="5">
-        <f t="shared" ref="AP16" si="66">SUM(AP12:AP15)</f>
+        <f t="shared" ref="AP16" si="63">SUM(AP12:AP15)</f>
         <v>12406</v>
       </c>
       <c r="AQ16" s="5">
-        <f t="shared" ref="AQ16" si="67">SUM(AQ12:AQ15)</f>
-        <v>12253.287600000001</v>
+        <f t="shared" ref="AQ16" si="64">SUM(AQ12:AQ15)</f>
+        <v>12753.570000000002</v>
       </c>
       <c r="AR16" s="5">
-        <f t="shared" ref="AR16" si="68">SUM(AR12:AR15)</f>
-        <v>12716.695352000001</v>
+        <f t="shared" ref="AR16" si="65">SUM(AR12:AR15)</f>
+        <v>13475.976300000002</v>
       </c>
       <c r="AS16" s="5">
-        <f t="shared" ref="AS16" si="69">SUM(AS12:AS15)</f>
-        <v>13048.58087752</v>
+        <f t="shared" ref="AS16" si="66">SUM(AS12:AS15)</f>
+        <v>13991.965735000003</v>
       </c>
       <c r="AT16" s="5">
-        <f t="shared" ref="AT16" si="70">SUM(AT12:AT15)</f>
-        <v>13329.399384495202</v>
+        <f t="shared" ref="AT16" si="67">SUM(AT12:AT15)</f>
+        <v>14390.605100000002</v>
       </c>
       <c r="AU16" s="5">
-        <f t="shared" ref="AU16" si="71">SUM(AU12:AU15)</f>
-        <v>13568.791323332156</v>
+        <f t="shared" ref="AU16" si="68">SUM(AU12:AU15)</f>
+        <v>14659.644757312002</v>
       </c>
       <c r="AV16" s="5">
-        <f t="shared" ref="AV16:BA16" si="72">SUM(AV12:AV15)</f>
-        <v>13762.060635164356</v>
+        <f t="shared" ref="AV16:BA16" si="69">SUM(AV12:AV15)</f>
+        <v>14883.062375789003</v>
       </c>
       <c r="AW16" s="5">
-        <f t="shared" si="72"/>
-        <v>13958.530785999435</v>
+        <f t="shared" si="69"/>
+        <v>15110.360794545202</v>
       </c>
       <c r="AX16" s="5">
-        <f t="shared" si="72"/>
-        <v>14158.263807861613</v>
+        <f t="shared" si="69"/>
+        <v>15341.616162092339</v>
       </c>
       <c r="AY16" s="5">
-        <f t="shared" si="72"/>
-        <v>14361.323139996692</v>
+        <f t="shared" si="69"/>
+        <v>15576.90631155852</v>
       </c>
       <c r="AZ16" s="5">
-        <f t="shared" si="72"/>
-        <v>14567.77366613947</v>
+        <f t="shared" si="69"/>
+        <v>15816.31080304987</v>
       </c>
       <c r="BA16" s="5">
-        <f t="shared" si="72"/>
-        <v>14777.681752915949</v>
+        <f t="shared" si="69"/>
+        <v>16059.910967228201</v>
       </c>
     </row>
     <row r="17" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3332,204 +3331,204 @@
         <v>30</v>
       </c>
       <c r="C17" s="9">
-        <f t="shared" ref="C17:M17" si="73">C11-C16</f>
+        <f t="shared" ref="C17:M17" si="70">C11-C16</f>
         <v>702.73999999999955</v>
       </c>
       <c r="D17" s="9">
+        <f t="shared" si="70"/>
+        <v>698.48</v>
+      </c>
+      <c r="E17" s="9">
+        <f t="shared" si="70"/>
+        <v>718.62000000000012</v>
+      </c>
+      <c r="F17" s="9">
+        <f t="shared" si="70"/>
+        <v>440.08999999999992</v>
+      </c>
+      <c r="G17" s="9">
+        <f t="shared" si="70"/>
+        <v>695</v>
+      </c>
+      <c r="H17" s="9">
+        <f t="shared" si="70"/>
+        <v>750</v>
+      </c>
+      <c r="I17" s="9">
+        <f t="shared" si="70"/>
+        <v>854</v>
+      </c>
+      <c r="J17" s="9">
+        <f t="shared" si="70"/>
+        <v>969.94999999999982</v>
+      </c>
+      <c r="K17" s="9">
+        <f t="shared" si="70"/>
+        <v>937</v>
+      </c>
+      <c r="L17" s="9">
+        <f t="shared" si="70"/>
+        <v>1016</v>
+      </c>
+      <c r="M17" s="9">
+        <f t="shared" si="70"/>
+        <v>1069</v>
+      </c>
+      <c r="N17" s="9">
+        <f t="shared" ref="N17:P17" si="71">N11-N16</f>
+        <v>1215</v>
+      </c>
+      <c r="O17" s="9">
+        <f t="shared" ref="O17" si="72">O11-O16</f>
+        <v>1454</v>
+      </c>
+      <c r="P17" s="9">
+        <f t="shared" si="71"/>
+        <v>1406</v>
+      </c>
+      <c r="Q17" s="9">
+        <f t="shared" ref="Q17:T17" si="73">Q11-Q16</f>
+        <v>1441</v>
+      </c>
+      <c r="R17" s="9">
         <f t="shared" si="73"/>
-        <v>698.48</v>
-      </c>
-      <c r="E17" s="9">
+        <v>1501</v>
+      </c>
+      <c r="S17" s="9">
         <f t="shared" si="73"/>
-        <v>718.62000000000012</v>
-      </c>
-      <c r="F17" s="9">
+        <v>1580</v>
+      </c>
+      <c r="T17" s="9">
         <f t="shared" si="73"/>
-        <v>440.08999999999992</v>
-      </c>
-      <c r="G17" s="9">
-        <f t="shared" si="73"/>
-        <v>695</v>
-      </c>
-      <c r="H17" s="9">
-        <f t="shared" si="73"/>
-        <v>750</v>
-      </c>
-      <c r="I17" s="9">
-        <f t="shared" si="73"/>
-        <v>854</v>
-      </c>
-      <c r="J17" s="9">
-        <f t="shared" si="73"/>
-        <v>969.94999999999982</v>
-      </c>
-      <c r="K17" s="9">
-        <f t="shared" si="73"/>
-        <v>937</v>
-      </c>
-      <c r="L17" s="9">
-        <f t="shared" si="73"/>
-        <v>1016</v>
-      </c>
-      <c r="M17" s="9">
-        <f t="shared" si="73"/>
-        <v>1069</v>
-      </c>
-      <c r="N17" s="9">
-        <f t="shared" ref="N17:P17" si="74">N11-N16</f>
-        <v>1215</v>
-      </c>
-      <c r="O17" s="9">
-        <f t="shared" ref="O17" si="75">O11-O16</f>
-        <v>1454</v>
-      </c>
-      <c r="P17" s="9">
-        <f t="shared" si="74"/>
-        <v>1406</v>
-      </c>
-      <c r="Q17" s="9">
-        <f t="shared" ref="Q17:T17" si="76">Q11-Q16</f>
-        <v>1441</v>
-      </c>
-      <c r="R17" s="9">
+        <v>1529</v>
+      </c>
+      <c r="U17" s="9">
+        <f t="shared" ref="U17" si="74">U11-U16</f>
+        <v>1484</v>
+      </c>
+      <c r="V17" s="9">
+        <f t="shared" ref="V17" si="75">V11-V16</f>
+        <v>1505</v>
+      </c>
+      <c r="W17" s="9">
+        <f t="shared" ref="W17:X17" si="76">W11-W16</f>
+        <v>1586</v>
+      </c>
+      <c r="X17" s="9">
         <f t="shared" si="76"/>
-        <v>1501</v>
-      </c>
-      <c r="S17" s="9">
-        <f t="shared" si="76"/>
-        <v>1580</v>
-      </c>
-      <c r="T17" s="9">
-        <f t="shared" si="76"/>
-        <v>1529</v>
-      </c>
-      <c r="U17" s="9">
-        <f t="shared" ref="U17" si="77">U11-U16</f>
-        <v>1484</v>
-      </c>
-      <c r="V17" s="9">
-        <f t="shared" ref="V17" si="78">V11-V16</f>
-        <v>1505</v>
-      </c>
-      <c r="W17" s="9">
-        <f t="shared" ref="W17:X17" si="79">W11-W16</f>
-        <v>1586</v>
-      </c>
-      <c r="X17" s="9">
+        <v>1624</v>
+      </c>
+      <c r="Y17" s="9">
+        <f t="shared" ref="Y17" si="77">Y11-Y16</f>
+        <v>1697</v>
+      </c>
+      <c r="Z17" s="9">
+        <f t="shared" ref="Z17" si="78">Z11-Z16</f>
+        <v>1743</v>
+      </c>
+      <c r="AA17" s="9">
+        <f t="shared" ref="AA17:AB17" si="79">AA11-AA16</f>
+        <v>907</v>
+      </c>
+      <c r="AB17" s="9">
         <f t="shared" si="79"/>
-        <v>1624</v>
-      </c>
-      <c r="Y17" s="9">
-        <f t="shared" ref="Y17" si="80">Y11-Y16</f>
-        <v>1697</v>
-      </c>
-      <c r="Z17" s="9">
-        <f t="shared" ref="Z17" si="81">Z11-Z16</f>
-        <v>1743</v>
-      </c>
-      <c r="AA17" s="9">
-        <f t="shared" ref="AA17:AB17" si="82">AA11-AA16</f>
-        <v>907</v>
-      </c>
-      <c r="AB17" s="9">
+        <v>1885</v>
+      </c>
+      <c r="AC17" s="9">
+        <f t="shared" ref="AC17" si="80">AC11-AC16</f>
+        <v>1992</v>
+      </c>
+      <c r="AD17" s="9">
+        <f t="shared" ref="AD17" si="81">AD11-AD16</f>
+        <v>1957</v>
+      </c>
+      <c r="AE17" s="9">
+        <f t="shared" ref="AE17:AH17" si="82">AE11-AE16</f>
+        <v>2163</v>
+      </c>
+      <c r="AF17" s="9">
         <f t="shared" si="82"/>
-        <v>1885</v>
-      </c>
-      <c r="AC17" s="9">
-        <f t="shared" ref="AC17" si="83">AC11-AC16</f>
-        <v>1992</v>
-      </c>
-      <c r="AD17" s="9">
-        <f t="shared" ref="AD17" si="84">AD11-AD16</f>
-        <v>1957</v>
-      </c>
-      <c r="AE17" s="9">
-        <f t="shared" ref="AE17:AH17" si="85">AE11-AE16</f>
-        <v>2163</v>
-      </c>
-      <c r="AF17" s="9">
-        <f t="shared" si="85"/>
         <v>2109</v>
       </c>
       <c r="AG17" s="9">
-        <f t="shared" si="85"/>
-        <v>2249.9281999999998</v>
+        <f t="shared" si="82"/>
+        <v>2261</v>
       </c>
       <c r="AH17" s="9">
-        <f t="shared" si="85"/>
-        <v>2328.1356000000001</v>
+        <f t="shared" si="82"/>
+        <v>2126.5700000000002</v>
       </c>
       <c r="AJ17" s="9">
-        <f t="shared" ref="AJ17:AL17" si="86">AJ11-AJ16</f>
+        <f t="shared" ref="AJ17:AL17" si="83">AJ11-AJ16</f>
         <v>2559.9299999999985</v>
       </c>
       <c r="AK17" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="83"/>
         <v>3268.9500000000007</v>
       </c>
       <c r="AL17" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="83"/>
         <v>4237</v>
       </c>
       <c r="AM17" s="9">
-        <f t="shared" ref="AM17" si="87">AM11-AM16</f>
+        <f t="shared" ref="AM17" si="84">AM11-AM16</f>
         <v>5802</v>
       </c>
       <c r="AN17" s="9">
-        <f t="shared" ref="AN17" si="88">AN11-AN16</f>
+        <f t="shared" ref="AN17" si="85">AN11-AN16</f>
         <v>6098</v>
       </c>
       <c r="AO17" s="9">
-        <f t="shared" ref="AO17" si="89">AO11-AO16</f>
+        <f t="shared" ref="AO17" si="86">AO11-AO16</f>
         <v>6650</v>
       </c>
       <c r="AP17" s="9">
-        <f t="shared" ref="AP17" si="90">AP11-AP16</f>
+        <f t="shared" ref="AP17" si="87">AP11-AP16</f>
         <v>6741</v>
       </c>
       <c r="AQ17" s="9">
-        <f t="shared" ref="AQ17" si="91">AQ11-AQ16</f>
-        <v>8835.4937999999984</v>
+        <f t="shared" ref="AQ17" si="88">AQ11-AQ16</f>
+        <v>8612.659999999998</v>
       </c>
       <c r="AR17" s="9">
-        <f t="shared" ref="AR17" si="92">AR11-AR16</f>
-        <v>10059.188560000001</v>
+        <f t="shared" ref="AR17" si="89">AR11-AR16</f>
+        <v>10026.876700000001</v>
       </c>
       <c r="AS17" s="9">
-        <f t="shared" ref="AS17" si="93">AS11-AS16</f>
-        <v>10866.09723008</v>
+        <f t="shared" ref="AS17" si="90">AS11-AS16</f>
+        <v>11391.115505</v>
       </c>
       <c r="AT17" s="9">
-        <f t="shared" ref="AT17" si="94">AT11-AT16</f>
-        <v>11541.865847408801</v>
+        <f t="shared" ref="AT17" si="91">AT11-AT16</f>
+        <v>12261.630202000002</v>
       </c>
       <c r="AU17" s="9">
-        <f t="shared" ref="AU17" si="95">AU11-AU16</f>
-        <v>12048.611865528968</v>
+        <f t="shared" ref="AU17" si="92">AU11-AU16</f>
+        <v>13058.679956768003</v>
       </c>
       <c r="AV17" s="9">
-        <f t="shared" ref="AV17:BA17" si="96">AV11-AV16</f>
-        <v>12623.864649362602</v>
+        <f t="shared" ref="AV17:BA17" si="93">AV11-AV16</f>
+        <v>13666.812079713403</v>
       </c>
       <c r="AW17" s="9">
-        <f t="shared" si="96"/>
-        <v>12955.113004218063</v>
+        <f t="shared" si="93"/>
+        <v>14010.511150067254</v>
       </c>
       <c r="AX17" s="9">
-        <f t="shared" si="96"/>
-        <v>13293.652858160234</v>
+        <f t="shared" si="93"/>
+        <v>14361.673221412364</v>
       </c>
       <c r="AY17" s="9">
-        <f t="shared" si="96"/>
-        <v>13639.631859345593</v>
+        <f t="shared" si="93"/>
+        <v>14720.448859616277</v>
       </c>
       <c r="AZ17" s="9">
-        <f t="shared" si="96"/>
-        <v>13993.200433189661</v>
+        <f t="shared" si="93"/>
+        <v>15086.991471548423</v>
       </c>
       <c r="BA17" s="9">
-        <f t="shared" si="96"/>
-        <v>14354.511828399765</v>
+        <f t="shared" si="93"/>
+        <v>15461.457352862059</v>
       </c>
     </row>
     <row r="18" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3603,10 +3602,10 @@
         <v>68</v>
       </c>
       <c r="AG18" s="5">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AH18" s="5">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AJ18" s="9"/>
       <c r="AK18" s="9"/>
@@ -3629,7 +3628,7 @@
       </c>
       <c r="AQ18" s="5">
         <f>SUM(AE18:AH18)</f>
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="AR18" s="9"/>
       <c r="AS18" s="9"/>
@@ -3713,7 +3712,7 @@
         <v>-2</v>
       </c>
       <c r="AG19" s="5">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AH19" s="5">
         <v>-10</v>
@@ -3739,7 +3738,7 @@
       </c>
       <c r="AQ19" s="5">
         <f>SUM(AE19:AH19)</f>
-        <v>-28</v>
+        <v>-30</v>
       </c>
       <c r="AR19" s="9"/>
       <c r="AS19" s="9"/>
@@ -3823,11 +3822,10 @@
         <v>-58</v>
       </c>
       <c r="AG20" s="5">
-        <f t="shared" ref="AG20:AH20" si="97">AC20*1.03</f>
-        <v>-91.67</v>
+        <v>-57</v>
       </c>
       <c r="AH20" s="5">
-        <f t="shared" si="97"/>
+        <f t="shared" ref="AH20" si="94">AD20*1.03</f>
         <v>-72.100000000000009</v>
       </c>
       <c r="AJ20" s="9"/>
@@ -3851,7 +3849,7 @@
       </c>
       <c r="AQ20" s="5">
         <f>SUM(AE20:AH20)</f>
-        <v>-296.77000000000004</v>
+        <v>-262.10000000000002</v>
       </c>
       <c r="AR20" s="9"/>
       <c r="AS20" s="9"/>
@@ -3905,84 +3903,84 @@
         <v>18</v>
       </c>
       <c r="O21" s="5">
-        <f t="shared" ref="O21:AE21" si="98">SUM(O18:O20)</f>
+        <f t="shared" ref="O21:AE21" si="95">SUM(O18:O20)</f>
         <v>21</v>
       </c>
       <c r="P21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>20</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>23</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>33</v>
       </c>
       <c r="S21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>37</v>
       </c>
       <c r="T21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>37</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>28</v>
       </c>
       <c r="V21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-12</v>
       </c>
       <c r="W21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-12</v>
       </c>
       <c r="X21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-26</v>
       </c>
       <c r="Y21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-46</v>
       </c>
       <c r="Z21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-65</v>
       </c>
       <c r="AA21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-61</v>
       </c>
       <c r="AB21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-45</v>
       </c>
       <c r="AC21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-50</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-34</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>-19</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" ref="AF21:AH21" si="99">SUM(AF18:AF20)</f>
+        <f t="shared" ref="AF21:AH21" si="96">SUM(AF18:AF20)</f>
         <v>8</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" si="99"/>
-        <v>-41.67</v>
+        <f t="shared" si="96"/>
+        <v>-3</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" si="99"/>
-        <v>-22.100000000000009</v>
+        <f t="shared" si="96"/>
+        <v>-15.100000000000009</v>
       </c>
       <c r="AJ21" s="5">
         <f>SUM(C21:F21)</f>
@@ -4001,60 +3999,60 @@
         <v>97</v>
       </c>
       <c r="AN21" s="5">
-        <f t="shared" ref="AN21:AQ21" si="100">SUM(AN18:AN20)</f>
+        <f t="shared" ref="AN21:AQ21" si="97">SUM(AN18:AN20)</f>
         <v>90</v>
       </c>
       <c r="AO21" s="5">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>-149</v>
       </c>
       <c r="AP21" s="5">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>-190</v>
       </c>
       <c r="AQ21" s="5">
-        <f t="shared" si="100"/>
-        <v>-74.770000000000039</v>
+        <f t="shared" si="97"/>
+        <v>-29.100000000000023</v>
       </c>
       <c r="AR21" s="5">
-        <f t="shared" ref="AR21:AV21" si="101">AQ21*1.01</f>
-        <v>-75.517700000000033</v>
+        <f t="shared" ref="AR21:AV21" si="98">AQ21*1.01</f>
+        <v>-29.391000000000023</v>
       </c>
       <c r="AS21" s="5">
-        <f t="shared" si="101"/>
-        <v>-76.272877000000037</v>
+        <f t="shared" si="98"/>
+        <v>-29.684910000000023</v>
       </c>
       <c r="AT21" s="5">
-        <f t="shared" si="101"/>
-        <v>-77.035605770000032</v>
+        <f t="shared" si="98"/>
+        <v>-29.981759100000023</v>
       </c>
       <c r="AU21" s="5">
-        <f t="shared" si="101"/>
-        <v>-77.805961827700031</v>
+        <f t="shared" si="98"/>
+        <v>-30.281576691000023</v>
       </c>
       <c r="AV21" s="5">
-        <f t="shared" si="101"/>
-        <v>-78.584021445977029</v>
+        <f t="shared" si="98"/>
+        <v>-30.584392457910024</v>
       </c>
       <c r="AW21" s="5">
-        <f t="shared" ref="AW21" si="102">AV21*1.01</f>
-        <v>-79.369861660436797</v>
+        <f t="shared" ref="AW21" si="99">AV21*1.01</f>
+        <v>-30.890236382489125</v>
       </c>
       <c r="AX21" s="5">
-        <f t="shared" ref="AX21" si="103">AW21*1.01</f>
-        <v>-80.163560277041171</v>
+        <f t="shared" ref="AX21" si="100">AW21*1.01</f>
+        <v>-31.199138746314016</v>
       </c>
       <c r="AY21" s="5">
-        <f t="shared" ref="AY21" si="104">AX21*1.01</f>
-        <v>-80.965195879811588</v>
+        <f t="shared" ref="AY21" si="101">AX21*1.01</f>
+        <v>-31.511130133777158</v>
       </c>
       <c r="AZ21" s="5">
-        <f t="shared" ref="AZ21" si="105">AY21*1.01</f>
-        <v>-81.774847838609702</v>
+        <f t="shared" ref="AZ21" si="102">AY21*1.01</f>
+        <v>-31.82624143511493</v>
       </c>
       <c r="BA21" s="5">
-        <f t="shared" ref="BA21" si="106">AZ21*1.01</f>
-        <v>-82.592596316995795</v>
+        <f t="shared" ref="BA21" si="103">AZ21*1.01</f>
+        <v>-32.144503849466076</v>
       </c>
     </row>
     <row r="22" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4062,204 +4060,204 @@
         <v>32</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:AE22" si="107">C17-C21</f>
+        <f t="shared" ref="C22:AE22" si="104">C17-C21</f>
         <v>702.50999999999954</v>
       </c>
       <c r="D22" s="9">
+        <f t="shared" si="104"/>
+        <v>690.78</v>
+      </c>
+      <c r="E22" s="9">
+        <f t="shared" si="104"/>
+        <v>701.37000000000012</v>
+      </c>
+      <c r="F22" s="9">
+        <f t="shared" si="104"/>
+        <v>418.78999999999991</v>
+      </c>
+      <c r="G22" s="9">
+        <f t="shared" si="104"/>
+        <v>702</v>
+      </c>
+      <c r="H22" s="9">
+        <f t="shared" si="104"/>
+        <v>711</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="104"/>
+        <v>835</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="104"/>
+        <v>957.16999999999985</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="104"/>
+        <v>919</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="104"/>
+        <v>1000</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="104"/>
+        <v>1060</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="104"/>
+        <v>1197</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" si="104"/>
+        <v>1433</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="104"/>
+        <v>1386</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" si="104"/>
+        <v>1418</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="104"/>
+        <v>1468</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" si="104"/>
+        <v>1543</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" si="104"/>
+        <v>1492</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" si="104"/>
+        <v>1456</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="104"/>
+        <v>1517</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="104"/>
+        <v>1598</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" si="104"/>
+        <v>1650</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="104"/>
+        <v>1743</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" si="104"/>
+        <v>1808</v>
+      </c>
+      <c r="AA22" s="9">
+        <f t="shared" si="104"/>
+        <v>968</v>
+      </c>
+      <c r="AB22" s="9">
+        <f t="shared" si="104"/>
+        <v>1930</v>
+      </c>
+      <c r="AC22" s="9">
+        <f t="shared" si="104"/>
+        <v>2042</v>
+      </c>
+      <c r="AD22" s="9">
+        <f t="shared" si="104"/>
+        <v>1991</v>
+      </c>
+      <c r="AE22" s="9">
+        <f t="shared" si="104"/>
+        <v>2182</v>
+      </c>
+      <c r="AF22" s="9">
+        <f t="shared" ref="AF22:AH22" si="105">AF17-AF21</f>
+        <v>2101</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" si="105"/>
+        <v>2264</v>
+      </c>
+      <c r="AH22" s="9">
+        <f t="shared" si="105"/>
+        <v>2141.67</v>
+      </c>
+      <c r="AJ22" s="9">
+        <f t="shared" ref="AJ22:AV22" si="106">AJ17-AJ21</f>
+        <v>2513.4499999999985</v>
+      </c>
+      <c r="AK22" s="9">
+        <f t="shared" si="106"/>
+        <v>3205.1700000000005</v>
+      </c>
+      <c r="AL22" s="9">
+        <f t="shared" si="106"/>
+        <v>4176</v>
+      </c>
+      <c r="AM22" s="9">
+        <f t="shared" si="106"/>
+        <v>5705</v>
+      </c>
+      <c r="AN22" s="9">
+        <f t="shared" si="106"/>
+        <v>6008</v>
+      </c>
+      <c r="AO22" s="9">
+        <f t="shared" si="106"/>
+        <v>6799</v>
+      </c>
+      <c r="AP22" s="9">
+        <f t="shared" si="106"/>
+        <v>6931</v>
+      </c>
+      <c r="AQ22" s="9">
+        <f t="shared" si="106"/>
+        <v>8641.7599999999984</v>
+      </c>
+      <c r="AR22" s="9">
+        <f t="shared" si="106"/>
+        <v>10056.2677</v>
+      </c>
+      <c r="AS22" s="9">
+        <f t="shared" si="106"/>
+        <v>11420.800415</v>
+      </c>
+      <c r="AT22" s="9">
+        <f t="shared" si="106"/>
+        <v>12291.611961100001</v>
+      </c>
+      <c r="AU22" s="9">
+        <f t="shared" si="106"/>
+        <v>13088.961533459003</v>
+      </c>
+      <c r="AV22" s="9">
+        <f t="shared" si="106"/>
+        <v>13697.396472171313</v>
+      </c>
+      <c r="AW22" s="9">
+        <f t="shared" ref="AW22:BA22" si="107">AW17-AW21</f>
+        <v>14041.401386449743</v>
+      </c>
+      <c r="AX22" s="9">
         <f t="shared" si="107"/>
-        <v>690.78</v>
-      </c>
-      <c r="E22" s="9">
+        <v>14392.872360158677</v>
+      </c>
+      <c r="AY22" s="9">
         <f t="shared" si="107"/>
-        <v>701.37000000000012</v>
-      </c>
-      <c r="F22" s="9">
+        <v>14751.959989750054</v>
+      </c>
+      <c r="AZ22" s="9">
         <f t="shared" si="107"/>
-        <v>418.78999999999991</v>
-      </c>
-      <c r="G22" s="9">
+        <v>15118.817712983539</v>
+      </c>
+      <c r="BA22" s="9">
         <f t="shared" si="107"/>
-        <v>702</v>
-      </c>
-      <c r="H22" s="9">
-        <f t="shared" si="107"/>
-        <v>711</v>
-      </c>
-      <c r="I22" s="9">
-        <f t="shared" si="107"/>
-        <v>835</v>
-      </c>
-      <c r="J22" s="9">
-        <f t="shared" si="107"/>
-        <v>957.16999999999985</v>
-      </c>
-      <c r="K22" s="9">
-        <f t="shared" si="107"/>
-        <v>919</v>
-      </c>
-      <c r="L22" s="9">
-        <f t="shared" si="107"/>
-        <v>1000</v>
-      </c>
-      <c r="M22" s="9">
-        <f t="shared" si="107"/>
-        <v>1060</v>
-      </c>
-      <c r="N22" s="9">
-        <f t="shared" si="107"/>
-        <v>1197</v>
-      </c>
-      <c r="O22" s="9">
-        <f t="shared" si="107"/>
-        <v>1433</v>
-      </c>
-      <c r="P22" s="9">
-        <f t="shared" si="107"/>
-        <v>1386</v>
-      </c>
-      <c r="Q22" s="9">
-        <f t="shared" si="107"/>
-        <v>1418</v>
-      </c>
-      <c r="R22" s="9">
-        <f t="shared" si="107"/>
-        <v>1468</v>
-      </c>
-      <c r="S22" s="9">
-        <f t="shared" si="107"/>
-        <v>1543</v>
-      </c>
-      <c r="T22" s="9">
-        <f t="shared" si="107"/>
-        <v>1492</v>
-      </c>
-      <c r="U22" s="9">
-        <f t="shared" si="107"/>
-        <v>1456</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" si="107"/>
-        <v>1517</v>
-      </c>
-      <c r="W22" s="9">
-        <f t="shared" si="107"/>
-        <v>1598</v>
-      </c>
-      <c r="X22" s="9">
-        <f t="shared" si="107"/>
-        <v>1650</v>
-      </c>
-      <c r="Y22" s="9">
-        <f t="shared" si="107"/>
-        <v>1743</v>
-      </c>
-      <c r="Z22" s="9">
-        <f t="shared" si="107"/>
-        <v>1808</v>
-      </c>
-      <c r="AA22" s="9">
-        <f t="shared" si="107"/>
-        <v>968</v>
-      </c>
-      <c r="AB22" s="9">
-        <f t="shared" si="107"/>
-        <v>1930</v>
-      </c>
-      <c r="AC22" s="9">
-        <f t="shared" si="107"/>
-        <v>2042</v>
-      </c>
-      <c r="AD22" s="9">
-        <f t="shared" si="107"/>
-        <v>1991</v>
-      </c>
-      <c r="AE22" s="9">
-        <f t="shared" si="107"/>
-        <v>2182</v>
-      </c>
-      <c r="AF22" s="9">
-        <f t="shared" ref="AF22:AH22" si="108">AF17-AF21</f>
-        <v>2101</v>
-      </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="108"/>
-        <v>2291.5981999999999</v>
-      </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="108"/>
-        <v>2350.2356</v>
-      </c>
-      <c r="AJ22" s="9">
-        <f t="shared" ref="AJ22:AV22" si="109">AJ17-AJ21</f>
-        <v>2513.4499999999985</v>
-      </c>
-      <c r="AK22" s="9">
-        <f t="shared" si="109"/>
-        <v>3205.1700000000005</v>
-      </c>
-      <c r="AL22" s="9">
-        <f t="shared" si="109"/>
-        <v>4176</v>
-      </c>
-      <c r="AM22" s="9">
-        <f t="shared" si="109"/>
-        <v>5705</v>
-      </c>
-      <c r="AN22" s="9">
-        <f t="shared" si="109"/>
-        <v>6008</v>
-      </c>
-      <c r="AO22" s="9">
-        <f t="shared" si="109"/>
-        <v>6799</v>
-      </c>
-      <c r="AP22" s="9">
-        <f t="shared" si="109"/>
-        <v>6931</v>
-      </c>
-      <c r="AQ22" s="9">
-        <f t="shared" si="109"/>
-        <v>8910.2637999999988</v>
-      </c>
-      <c r="AR22" s="9">
-        <f t="shared" si="109"/>
-        <v>10134.706260000001</v>
-      </c>
-      <c r="AS22" s="9">
-        <f t="shared" si="109"/>
-        <v>10942.37010708</v>
-      </c>
-      <c r="AT22" s="9">
-        <f t="shared" si="109"/>
-        <v>11618.9014531788</v>
-      </c>
-      <c r="AU22" s="9">
-        <f t="shared" si="109"/>
-        <v>12126.417827356669</v>
-      </c>
-      <c r="AV22" s="9">
-        <f t="shared" si="109"/>
-        <v>12702.448670808579</v>
-      </c>
-      <c r="AW22" s="9">
-        <f t="shared" ref="AW22:BA22" si="110">AW17-AW21</f>
-        <v>13034.482865878499</v>
-      </c>
-      <c r="AX22" s="9">
-        <f t="shared" si="110"/>
-        <v>13373.816418437276</v>
-      </c>
-      <c r="AY22" s="9">
-        <f t="shared" si="110"/>
-        <v>13720.597055225404</v>
-      </c>
-      <c r="AZ22" s="9">
-        <f t="shared" si="110"/>
-        <v>14074.97528102827</v>
-      </c>
-      <c r="BA22" s="9">
-        <f t="shared" si="110"/>
-        <v>14437.104424716761</v>
+        <v>15493.601856711524</v>
       </c>
     </row>
     <row r="23" spans="2:179" x14ac:dyDescent="0.3">
@@ -4357,12 +4355,11 @@
         <v>410</v>
       </c>
       <c r="AG23" s="5">
-        <f t="shared" ref="AG23:AH23" si="111">AG22*0.17</f>
-        <v>389.57169400000004</v>
+        <v>408</v>
       </c>
       <c r="AH23" s="5">
-        <f t="shared" si="111"/>
-        <v>399.540052</v>
+        <f t="shared" ref="AH23" si="108">AH22*0.17</f>
+        <v>364.08390000000003</v>
       </c>
       <c r="AJ23" s="5">
         <f>SUM(C23:F23)</f>
@@ -4394,47 +4391,47 @@
       </c>
       <c r="AQ23" s="5">
         <f>SUM(AE23:AH23)</f>
-        <v>1570.111746</v>
+        <v>1553.0839000000001</v>
       </c>
       <c r="AR23" s="5">
         <f>AR22*0.18</f>
-        <v>1824.2471268000002</v>
+        <v>1810.1281859999999</v>
       </c>
       <c r="AS23" s="5">
-        <f t="shared" ref="AS23:BA23" si="112">AS22*0.18</f>
-        <v>1969.6266192743999</v>
+        <f t="shared" ref="AS23:BA23" si="109">AS22*0.18</f>
+        <v>2055.7440747000001</v>
       </c>
       <c r="AT23" s="5">
-        <f t="shared" si="112"/>
-        <v>2091.4022615721838</v>
+        <f t="shared" si="109"/>
+        <v>2212.4901529980002</v>
       </c>
       <c r="AU23" s="5">
-        <f t="shared" si="112"/>
-        <v>2182.7552089242004</v>
+        <f t="shared" si="109"/>
+        <v>2356.0130760226207</v>
       </c>
       <c r="AV23" s="5">
-        <f t="shared" si="112"/>
-        <v>2286.4407607455441</v>
+        <f t="shared" si="109"/>
+        <v>2465.5313649908362</v>
       </c>
       <c r="AW23" s="5">
-        <f t="shared" si="112"/>
-        <v>2346.2069158581298</v>
+        <f t="shared" si="109"/>
+        <v>2527.4522495609535</v>
       </c>
       <c r="AX23" s="5">
-        <f t="shared" si="112"/>
-        <v>2407.2869553187097</v>
+        <f t="shared" si="109"/>
+        <v>2590.717024828562</v>
       </c>
       <c r="AY23" s="5">
-        <f t="shared" si="112"/>
-        <v>2469.7074699405725</v>
+        <f t="shared" si="109"/>
+        <v>2655.3527981550096</v>
       </c>
       <c r="AZ23" s="5">
-        <f t="shared" si="112"/>
-        <v>2533.4955505850885</v>
+        <f t="shared" si="109"/>
+        <v>2721.3871883370366</v>
       </c>
       <c r="BA23" s="5">
-        <f t="shared" si="112"/>
-        <v>2598.6787964490168</v>
+        <f t="shared" si="109"/>
+        <v>2788.8483342080744</v>
       </c>
     </row>
     <row r="24" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4442,708 +4439,708 @@
         <v>34</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:M24" si="113">C22-C23</f>
+        <f t="shared" ref="C24:M24" si="110">C22-C23</f>
         <v>583.07999999999947</v>
       </c>
       <c r="D24" s="9">
+        <f t="shared" si="110"/>
+        <v>663.15</v>
+      </c>
+      <c r="E24" s="9">
+        <f t="shared" si="110"/>
+        <v>666.30000000000007</v>
+      </c>
+      <c r="F24" s="9">
+        <f t="shared" si="110"/>
+        <v>397.80999999999989</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="110"/>
+        <v>674</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="110"/>
+        <v>633</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="110"/>
+        <v>793</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="110"/>
+        <v>851.88999999999987</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="110"/>
+        <v>955</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="110"/>
+        <v>1100</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="110"/>
+        <v>955</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" ref="N24:P24" si="111">N22-N23</f>
+        <v>2250</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" ref="O24" si="112">O22-O23</f>
+        <v>1261</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="111"/>
+        <v>1116</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" ref="Q24:T24" si="113">Q22-Q23</f>
+        <v>1212</v>
+      </c>
+      <c r="R24" s="9">
         <f t="shared" si="113"/>
-        <v>663.15</v>
-      </c>
-      <c r="E24" s="9">
+        <v>1233</v>
+      </c>
+      <c r="S24" s="9">
         <f t="shared" si="113"/>
-        <v>666.30000000000007</v>
-      </c>
-      <c r="F24" s="9">
+        <v>1266</v>
+      </c>
+      <c r="T24" s="9">
         <f t="shared" si="113"/>
-        <v>397.80999999999989</v>
-      </c>
-      <c r="G24" s="9">
-        <f t="shared" si="113"/>
-        <v>674</v>
-      </c>
-      <c r="H24" s="9">
-        <f t="shared" si="113"/>
-        <v>633</v>
-      </c>
-      <c r="I24" s="9">
-        <f t="shared" si="113"/>
-        <v>793</v>
-      </c>
-      <c r="J24" s="9">
-        <f t="shared" si="113"/>
-        <v>851.88999999999987</v>
-      </c>
-      <c r="K24" s="9">
-        <f t="shared" si="113"/>
-        <v>955</v>
-      </c>
-      <c r="L24" s="9">
-        <f t="shared" si="113"/>
-        <v>1100</v>
-      </c>
-      <c r="M24" s="9">
-        <f t="shared" si="113"/>
-        <v>955</v>
-      </c>
-      <c r="N24" s="9">
-        <f t="shared" ref="N24:P24" si="114">N22-N23</f>
-        <v>2250</v>
-      </c>
-      <c r="O24" s="9">
-        <f t="shared" ref="O24" si="115">O22-O23</f>
-        <v>1261</v>
-      </c>
-      <c r="P24" s="9">
-        <f t="shared" si="114"/>
-        <v>1116</v>
-      </c>
-      <c r="Q24" s="9">
-        <f t="shared" ref="Q24:T24" si="116">Q22-Q23</f>
-        <v>1212</v>
-      </c>
-      <c r="R24" s="9">
+        <v>1178</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" ref="U24" si="114">U22-U23</f>
+        <v>1136</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" ref="V24" si="115">V22-V23</f>
+        <v>1176</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" ref="W24:X24" si="116">W22-W23</f>
+        <v>1247</v>
+      </c>
+      <c r="X24" s="9">
         <f t="shared" si="116"/>
-        <v>1233</v>
-      </c>
-      <c r="S24" s="9">
-        <f t="shared" si="116"/>
-        <v>1266</v>
-      </c>
-      <c r="T24" s="9">
-        <f t="shared" si="116"/>
-        <v>1178</v>
-      </c>
-      <c r="U24" s="9">
-        <f t="shared" ref="U24" si="117">U22-U23</f>
-        <v>1136</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" ref="V24" si="118">V22-V23</f>
-        <v>1176</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" ref="W24:X24" si="119">W22-W23</f>
-        <v>1247</v>
-      </c>
-      <c r="X24" s="9">
+        <v>1295</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" ref="Y24" si="117">Y22-Y23</f>
+        <v>1403</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" ref="Z24" si="118">Z22-Z23</f>
+        <v>1483</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" ref="AA24:AB24" si="119">AA22-AA23</f>
+        <v>620</v>
+      </c>
+      <c r="AB24" s="9">
         <f t="shared" si="119"/>
-        <v>1295</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" ref="Y24" si="120">Y22-Y23</f>
-        <v>1403</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" ref="Z24" si="121">Z22-Z23</f>
-        <v>1483</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" ref="AA24:AB24" si="122">AA22-AA23</f>
-        <v>620</v>
-      </c>
-      <c r="AB24" s="9">
+        <v>1573</v>
+      </c>
+      <c r="AC24" s="9">
+        <f t="shared" ref="AC24" si="120">AC22-AC23</f>
+        <v>1684</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" ref="AD24" si="121">AD22-AD23</f>
+        <v>1683</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" ref="AE24:AH24" si="122">AE22-AE23</f>
+        <v>1811</v>
+      </c>
+      <c r="AF24" s="9">
         <f t="shared" si="122"/>
-        <v>1573</v>
-      </c>
-      <c r="AC24" s="9">
-        <f t="shared" ref="AC24" si="123">AC22-AC23</f>
-        <v>1684</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" ref="AD24" si="124">AD22-AD23</f>
-        <v>1683</v>
-      </c>
-      <c r="AE24" s="9">
-        <f t="shared" ref="AE24:AH24" si="125">AE22-AE23</f>
-        <v>1811</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="125"/>
         <v>1691</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="125"/>
-        <v>1902.0265059999999</v>
+        <f t="shared" si="122"/>
+        <v>1856</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="125"/>
-        <v>1950.6955479999999</v>
+        <f t="shared" si="122"/>
+        <v>1777.5861</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" ref="AJ24:AL24" si="126">AJ22-AJ23</f>
+        <f t="shared" ref="AJ24:AL24" si="123">AJ22-AJ23</f>
         <v>2310.3399999999983</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="123"/>
         <v>2951.8900000000003</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="123"/>
         <v>5260</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" ref="AM24" si="127">AM22-AM23</f>
+        <f t="shared" ref="AM24" si="124">AM22-AM23</f>
         <v>4822</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" ref="AN24" si="128">AN22-AN23</f>
+        <f t="shared" ref="AN24" si="125">AN22-AN23</f>
         <v>4756</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" ref="AO24" si="129">AO22-AO23</f>
+        <f t="shared" ref="AO24" si="126">AO22-AO23</f>
         <v>5428</v>
       </c>
       <c r="AP24" s="9">
-        <f t="shared" ref="AP24" si="130">AP22-AP23</f>
+        <f t="shared" ref="AP24" si="127">AP22-AP23</f>
         <v>5560</v>
       </c>
       <c r="AQ24" s="9">
-        <f t="shared" ref="AQ24" si="131">AQ22-AQ23</f>
-        <v>7340.1520539999983</v>
+        <f t="shared" ref="AQ24" si="128">AQ22-AQ23</f>
+        <v>7088.6760999999988</v>
       </c>
       <c r="AR24" s="9">
-        <f t="shared" ref="AR24" si="132">AR22-AR23</f>
-        <v>8310.4591332</v>
+        <f t="shared" ref="AR24" si="129">AR22-AR23</f>
+        <v>8246.1395140000004</v>
       </c>
       <c r="AS24" s="9">
-        <f t="shared" ref="AS24" si="133">AS22-AS23</f>
-        <v>8972.7434878055992</v>
+        <f t="shared" ref="AS24" si="130">AS22-AS23</f>
+        <v>9365.0563402999996</v>
       </c>
       <c r="AT24" s="9">
-        <f t="shared" ref="AT24" si="134">AT22-AT23</f>
-        <v>9527.4991916066156</v>
+        <f t="shared" ref="AT24" si="131">AT22-AT23</f>
+        <v>10079.121808102002</v>
       </c>
       <c r="AU24" s="9">
-        <f t="shared" ref="AU24" si="135">AU22-AU23</f>
-        <v>9943.6626184324687</v>
+        <f t="shared" ref="AU24" si="132">AU22-AU23</f>
+        <v>10732.948457436383</v>
       </c>
       <c r="AV24" s="9">
-        <f t="shared" ref="AV24:BA24" si="136">AV22-AV23</f>
-        <v>10416.007910063036</v>
+        <f t="shared" ref="AV24:BA24" si="133">AV22-AV23</f>
+        <v>11231.865107180476</v>
       </c>
       <c r="AW24" s="9">
-        <f t="shared" si="136"/>
-        <v>10688.275950020368</v>
+        <f t="shared" si="133"/>
+        <v>11513.94913688879</v>
       </c>
       <c r="AX24" s="9">
-        <f t="shared" si="136"/>
-        <v>10966.529463118566</v>
+        <f t="shared" si="133"/>
+        <v>11802.155335330115</v>
       </c>
       <c r="AY24" s="9">
-        <f t="shared" si="136"/>
-        <v>11250.889585284831</v>
+        <f t="shared" si="133"/>
+        <v>12096.607191595045</v>
       </c>
       <c r="AZ24" s="9">
-        <f t="shared" si="136"/>
-        <v>11541.479730443181</v>
+        <f t="shared" si="133"/>
+        <v>12397.430524646501</v>
       </c>
       <c r="BA24" s="9">
-        <f t="shared" si="136"/>
-        <v>11838.425628267745</v>
+        <f t="shared" si="133"/>
+        <v>12704.75352250345</v>
       </c>
       <c r="BB24" s="1">
         <f>BA24*(1+$BD$32)</f>
-        <v>11720.041371985068</v>
+        <v>12577.705987278416</v>
       </c>
       <c r="BC24" s="1">
-        <f t="shared" ref="BC24:DN24" si="137">BB24*(1+$BD$32)</f>
-        <v>11602.840958265217</v>
+        <f t="shared" ref="BC24:DN24" si="134">BB24*(1+$BD$32)</f>
+        <v>12451.928927405632</v>
       </c>
       <c r="BD24" s="1">
-        <f t="shared" si="137"/>
-        <v>11486.812548682565</v>
+        <f t="shared" si="134"/>
+        <v>12327.409638131576</v>
       </c>
       <c r="BE24" s="1">
-        <f t="shared" si="137"/>
-        <v>11371.944423195739</v>
+        <f t="shared" si="134"/>
+        <v>12204.13554175026</v>
       </c>
       <c r="BF24" s="1">
-        <f t="shared" si="137"/>
-        <v>11258.224978963781</v>
+        <f t="shared" si="134"/>
+        <v>12082.094186332757</v>
       </c>
       <c r="BG24" s="1">
-        <f t="shared" si="137"/>
-        <v>11145.642729174142</v>
+        <f t="shared" si="134"/>
+        <v>11961.27324446943</v>
       </c>
       <c r="BH24" s="1">
-        <f t="shared" si="137"/>
-        <v>11034.186301882401</v>
+        <f t="shared" si="134"/>
+        <v>11841.660512024735</v>
       </c>
       <c r="BI24" s="1">
-        <f t="shared" si="137"/>
-        <v>10923.844438863576</v>
+        <f t="shared" si="134"/>
+        <v>11723.243906904487</v>
       </c>
       <c r="BJ24" s="1">
-        <f t="shared" si="137"/>
-        <v>10814.60599447494</v>
+        <f t="shared" si="134"/>
+        <v>11606.011467835442</v>
       </c>
       <c r="BK24" s="1">
-        <f t="shared" si="137"/>
-        <v>10706.45993453019</v>
+        <f t="shared" si="134"/>
+        <v>11489.951353157088</v>
       </c>
       <c r="BL24" s="1">
-        <f t="shared" si="137"/>
-        <v>10599.395335184889</v>
+        <f t="shared" si="134"/>
+        <v>11375.051839625517</v>
       </c>
       <c r="BM24" s="1">
-        <f t="shared" si="137"/>
-        <v>10493.40138183304</v>
+        <f t="shared" si="134"/>
+        <v>11261.301321229263</v>
       </c>
       <c r="BN24" s="1">
-        <f t="shared" si="137"/>
-        <v>10388.46736801471</v>
+        <f t="shared" si="134"/>
+        <v>11148.68830801697</v>
       </c>
       <c r="BO24" s="1">
-        <f t="shared" si="137"/>
-        <v>10284.582694334562</v>
+        <f t="shared" si="134"/>
+        <v>11037.2014249368</v>
       </c>
       <c r="BP24" s="1">
-        <f t="shared" si="137"/>
-        <v>10181.736867391217</v>
+        <f t="shared" si="134"/>
+        <v>10926.829410687433</v>
       </c>
       <c r="BQ24" s="1">
-        <f t="shared" si="137"/>
-        <v>10079.919498717305</v>
+        <f t="shared" si="134"/>
+        <v>10817.561116580559</v>
       </c>
       <c r="BR24" s="1">
-        <f t="shared" si="137"/>
-        <v>9979.1203037301311</v>
+        <f t="shared" si="134"/>
+        <v>10709.385505414753</v>
       </c>
       <c r="BS24" s="1">
-        <f t="shared" si="137"/>
-        <v>9879.3291006928303</v>
+        <f t="shared" si="134"/>
+        <v>10602.291650360607</v>
       </c>
       <c r="BT24" s="1">
-        <f t="shared" si="137"/>
-        <v>9780.5358096859018</v>
+        <f t="shared" si="134"/>
+        <v>10496.268733857001</v>
       </c>
       <c r="BU24" s="1">
-        <f t="shared" si="137"/>
-        <v>9682.7304515890428</v>
+        <f t="shared" si="134"/>
+        <v>10391.306046518432</v>
       </c>
       <c r="BV24" s="1">
-        <f t="shared" si="137"/>
-        <v>9585.9031470731516</v>
+        <f t="shared" si="134"/>
+        <v>10287.392986053248</v>
       </c>
       <c r="BW24" s="1">
-        <f t="shared" si="137"/>
-        <v>9490.0441156024208</v>
+        <f t="shared" si="134"/>
+        <v>10184.519056192716</v>
       </c>
       <c r="BX24" s="1">
-        <f t="shared" si="137"/>
-        <v>9395.1436744463972</v>
+        <f t="shared" si="134"/>
+        <v>10082.673865630788</v>
       </c>
       <c r="BY24" s="1">
-        <f t="shared" si="137"/>
-        <v>9301.1922377019328</v>
+        <f t="shared" si="134"/>
+        <v>9981.8471269744805</v>
       </c>
       <c r="BZ24" s="1">
-        <f t="shared" si="137"/>
-        <v>9208.180315324913</v>
+        <f t="shared" si="134"/>
+        <v>9882.0286557047348</v>
       </c>
       <c r="CA24" s="1">
-        <f t="shared" si="137"/>
-        <v>9116.098512171664</v>
+        <f t="shared" si="134"/>
+        <v>9783.2083691476873</v>
       </c>
       <c r="CB24" s="1">
-        <f t="shared" si="137"/>
-        <v>9024.9375270499477</v>
+        <f t="shared" si="134"/>
+        <v>9685.3762854562101</v>
       </c>
       <c r="CC24" s="1">
-        <f t="shared" si="137"/>
-        <v>8934.6881517794482</v>
+        <f t="shared" si="134"/>
+        <v>9588.5225226016482</v>
       </c>
       <c r="CD24" s="1">
-        <f t="shared" si="137"/>
-        <v>8845.3412702616533</v>
+        <f t="shared" si="134"/>
+        <v>9492.6372973756315</v>
       </c>
       <c r="CE24" s="1">
-        <f t="shared" si="137"/>
-        <v>8756.887857559037</v>
+        <f t="shared" si="134"/>
+        <v>9397.7109244018757</v>
       </c>
       <c r="CF24" s="1">
-        <f t="shared" si="137"/>
-        <v>8669.3189789834469</v>
+        <f t="shared" si="134"/>
+        <v>9303.733815157857</v>
       </c>
       <c r="CG24" s="1">
-        <f t="shared" si="137"/>
-        <v>8582.6257891936129</v>
+        <f t="shared" si="134"/>
+        <v>9210.6964770062787</v>
       </c>
       <c r="CH24" s="1">
-        <f t="shared" si="137"/>
-        <v>8496.7995313016763</v>
+        <f t="shared" si="134"/>
+        <v>9118.5895122362163</v>
       </c>
       <c r="CI24" s="1">
-        <f t="shared" si="137"/>
-        <v>8411.8315359886601</v>
+        <f t="shared" si="134"/>
+        <v>9027.4036171138541</v>
       </c>
       <c r="CJ24" s="1">
-        <f t="shared" si="137"/>
-        <v>8327.7132206287733</v>
+        <f t="shared" si="134"/>
+        <v>8937.1295809427156</v>
       </c>
       <c r="CK24" s="1">
-        <f t="shared" si="137"/>
-        <v>8244.4360884224861</v>
+        <f t="shared" si="134"/>
+        <v>8847.7582851332882</v>
       </c>
       <c r="CL24" s="1">
-        <f t="shared" si="137"/>
-        <v>8161.9917275382613</v>
+        <f t="shared" si="134"/>
+        <v>8759.2807022819543</v>
       </c>
       <c r="CM24" s="1">
-        <f t="shared" si="137"/>
-        <v>8080.3718102628791</v>
+        <f t="shared" si="134"/>
+        <v>8671.6878952591342</v>
       </c>
       <c r="CN24" s="1">
-        <f t="shared" si="137"/>
-        <v>7999.5680921602507</v>
+        <f t="shared" si="134"/>
+        <v>8584.9710163065429</v>
       </c>
       <c r="CO24" s="1">
-        <f t="shared" si="137"/>
-        <v>7919.5724112386479</v>
+        <f t="shared" si="134"/>
+        <v>8499.1213061434773</v>
       </c>
       <c r="CP24" s="1">
-        <f t="shared" si="137"/>
-        <v>7840.3766871262615</v>
+        <f t="shared" si="134"/>
+        <v>8414.1300930820416</v>
       </c>
       <c r="CQ24" s="1">
-        <f t="shared" si="137"/>
-        <v>7761.9729202549988</v>
+        <f t="shared" si="134"/>
+        <v>8329.9887921512218</v>
       </c>
       <c r="CR24" s="1">
-        <f t="shared" si="137"/>
-        <v>7684.3531910524489</v>
+        <f t="shared" si="134"/>
+        <v>8246.6889042297098</v>
       </c>
       <c r="CS24" s="1">
-        <f t="shared" si="137"/>
-        <v>7607.5096591419242</v>
+        <f t="shared" si="134"/>
+        <v>8164.2220151874126</v>
       </c>
       <c r="CT24" s="1">
-        <f t="shared" si="137"/>
-        <v>7531.4345625505048</v>
+        <f t="shared" si="134"/>
+        <v>8082.5797950355382</v>
       </c>
       <c r="CU24" s="1">
-        <f t="shared" si="137"/>
-        <v>7456.120216925</v>
+        <f t="shared" si="134"/>
+        <v>8001.7539970851831</v>
       </c>
       <c r="CV24" s="1">
-        <f t="shared" si="137"/>
-        <v>7381.5590147557496</v>
+        <f t="shared" si="134"/>
+        <v>7921.7364571143307</v>
       </c>
       <c r="CW24" s="1">
-        <f t="shared" si="137"/>
-        <v>7307.7434246081921</v>
+        <f t="shared" si="134"/>
+        <v>7842.5190925431871</v>
       </c>
       <c r="CX24" s="1">
-        <f t="shared" si="137"/>
-        <v>7234.6659903621103</v>
+        <f t="shared" si="134"/>
+        <v>7764.0939016177554</v>
       </c>
       <c r="CY24" s="1">
-        <f t="shared" si="137"/>
-        <v>7162.3193304584893</v>
+        <f t="shared" si="134"/>
+        <v>7686.4529626015774</v>
       </c>
       <c r="CZ24" s="1">
-        <f t="shared" si="137"/>
-        <v>7090.6961371539046</v>
+        <f t="shared" si="134"/>
+        <v>7609.5884329755618</v>
       </c>
       <c r="DA24" s="1">
-        <f t="shared" si="137"/>
-        <v>7019.7891757823654</v>
+        <f t="shared" si="134"/>
+        <v>7533.492548645806</v>
       </c>
       <c r="DB24" s="1">
-        <f t="shared" si="137"/>
-        <v>6949.5912840245419</v>
+        <f t="shared" si="134"/>
+        <v>7458.1576231593481</v>
       </c>
       <c r="DC24" s="1">
-        <f t="shared" si="137"/>
-        <v>6880.0953711842967</v>
+        <f t="shared" si="134"/>
+        <v>7383.5760469277548</v>
       </c>
       <c r="DD24" s="1">
-        <f t="shared" si="137"/>
-        <v>6811.2944174724535</v>
+        <f t="shared" si="134"/>
+        <v>7309.7402864584774</v>
       </c>
       <c r="DE24" s="1">
-        <f t="shared" si="137"/>
-        <v>6743.1814732977291</v>
+        <f t="shared" si="134"/>
+        <v>7236.6428835938923</v>
       </c>
       <c r="DF24" s="1">
-        <f t="shared" si="137"/>
-        <v>6675.7496585647514</v>
+        <f t="shared" si="134"/>
+        <v>7164.2764547579536</v>
       </c>
       <c r="DG24" s="1">
-        <f t="shared" si="137"/>
-        <v>6608.9921619791039</v>
+        <f t="shared" si="134"/>
+        <v>7092.633690210374</v>
       </c>
       <c r="DH24" s="1">
-        <f t="shared" si="137"/>
-        <v>6542.9022403593126</v>
+        <f t="shared" si="134"/>
+        <v>7021.7073533082703</v>
       </c>
       <c r="DI24" s="1">
-        <f t="shared" si="137"/>
-        <v>6477.4732179557195</v>
+        <f t="shared" si="134"/>
+        <v>6951.4902797751874</v>
       </c>
       <c r="DJ24" s="1">
-        <f t="shared" si="137"/>
-        <v>6412.6984857761627</v>
+        <f t="shared" si="134"/>
+        <v>6881.9753769774352</v>
       </c>
       <c r="DK24" s="1">
-        <f t="shared" si="137"/>
-        <v>6348.5715009184014</v>
+        <f t="shared" si="134"/>
+        <v>6813.1556232076609</v>
       </c>
       <c r="DL24" s="1">
-        <f t="shared" si="137"/>
-        <v>6285.0857859092175</v>
+        <f t="shared" si="134"/>
+        <v>6745.024066975584</v>
       </c>
       <c r="DM24" s="1">
-        <f t="shared" si="137"/>
-        <v>6222.2349280501248</v>
+        <f t="shared" si="134"/>
+        <v>6677.5738263058283</v>
       </c>
       <c r="DN24" s="1">
-        <f t="shared" si="137"/>
-        <v>6160.0125787696234</v>
+        <f t="shared" si="134"/>
+        <v>6610.7980880427704</v>
       </c>
       <c r="DO24" s="1">
-        <f t="shared" ref="DO24:FW24" si="138">DN24*(1+$BD$32)</f>
-        <v>6098.4124529819273</v>
+        <f t="shared" ref="DO24:FW24" si="135">DN24*(1+$BD$32)</f>
+        <v>6544.6901071623424</v>
       </c>
       <c r="DP24" s="1">
-        <f t="shared" si="138"/>
-        <v>6037.428328452108</v>
+        <f t="shared" si="135"/>
+        <v>6479.2432060907186</v>
       </c>
       <c r="DQ24" s="1">
-        <f t="shared" si="138"/>
-        <v>5977.054045167587</v>
+        <f t="shared" si="135"/>
+        <v>6414.4507740298113</v>
       </c>
       <c r="DR24" s="1">
-        <f t="shared" si="138"/>
-        <v>5917.2835047159115</v>
+        <f t="shared" si="135"/>
+        <v>6350.3062662895136</v>
       </c>
       <c r="DS24" s="1">
-        <f t="shared" si="138"/>
-        <v>5858.1106696687521</v>
+        <f t="shared" si="135"/>
+        <v>6286.8032036266186</v>
       </c>
       <c r="DT24" s="1">
-        <f t="shared" si="138"/>
-        <v>5799.5295629720649</v>
+        <f t="shared" si="135"/>
+        <v>6223.9351715903522</v>
       </c>
       <c r="DU24" s="1">
-        <f t="shared" si="138"/>
-        <v>5741.5342673423438</v>
+        <f t="shared" si="135"/>
+        <v>6161.6958198744487</v>
       </c>
       <c r="DV24" s="1">
-        <f t="shared" si="138"/>
-        <v>5684.11892466892</v>
+        <f t="shared" si="135"/>
+        <v>6100.0788616757045</v>
       </c>
       <c r="DW24" s="1">
-        <f t="shared" si="138"/>
-        <v>5627.2777354222308</v>
+        <f t="shared" si="135"/>
+        <v>6039.0780730589477</v>
       </c>
       <c r="DX24" s="1">
-        <f t="shared" si="138"/>
-        <v>5571.0049580680088</v>
+        <f t="shared" si="135"/>
+        <v>5978.6872923283581</v>
       </c>
       <c r="DY24" s="1">
-        <f t="shared" si="138"/>
-        <v>5515.2949084873289</v>
+        <f t="shared" si="135"/>
+        <v>5918.9004194050749</v>
       </c>
       <c r="DZ24" s="1">
-        <f t="shared" si="138"/>
-        <v>5460.1419594024555</v>
+        <f t="shared" si="135"/>
+        <v>5859.7114152110244</v>
       </c>
       <c r="EA24" s="1">
-        <f t="shared" si="138"/>
-        <v>5405.5405398084313</v>
+        <f t="shared" si="135"/>
+        <v>5801.114301058914</v>
       </c>
       <c r="EB24" s="1">
-        <f t="shared" si="138"/>
-        <v>5351.4851344103472</v>
+        <f t="shared" si="135"/>
+        <v>5743.103158048325</v>
       </c>
       <c r="EC24" s="1">
-        <f t="shared" si="138"/>
-        <v>5297.9702830662436</v>
+        <f t="shared" si="135"/>
+        <v>5685.6721264678417</v>
       </c>
       <c r="ED24" s="1">
-        <f t="shared" si="138"/>
-        <v>5244.9905802355815</v>
+        <f t="shared" si="135"/>
+        <v>5628.8154052031632</v>
       </c>
       <c r="EE24" s="1">
-        <f t="shared" si="138"/>
-        <v>5192.5406744332258</v>
+        <f t="shared" si="135"/>
+        <v>5572.5272511511312</v>
       </c>
       <c r="EF24" s="1">
-        <f t="shared" si="138"/>
-        <v>5140.6152676888933</v>
+        <f t="shared" si="135"/>
+        <v>5516.8019786396198</v>
       </c>
       <c r="EG24" s="1">
-        <f t="shared" si="138"/>
-        <v>5089.2091150120041</v>
+        <f t="shared" si="135"/>
+        <v>5461.6339588532237</v>
       </c>
       <c r="EH24" s="1">
-        <f t="shared" si="138"/>
-        <v>5038.3170238618841</v>
+        <f t="shared" si="135"/>
+        <v>5407.0176192646913</v>
       </c>
       <c r="EI24" s="1">
-        <f t="shared" si="138"/>
-        <v>4987.9338536232653</v>
+        <f t="shared" si="135"/>
+        <v>5352.9474430720447</v>
       </c>
       <c r="EJ24" s="1">
-        <f t="shared" si="138"/>
-        <v>4938.054515087033</v>
+        <f t="shared" si="135"/>
+        <v>5299.4179686413245</v>
       </c>
       <c r="EK24" s="1">
-        <f t="shared" si="138"/>
-        <v>4888.6739699361624</v>
+        <f t="shared" si="135"/>
+        <v>5246.4237889549113</v>
       </c>
       <c r="EL24" s="1">
-        <f t="shared" si="138"/>
-        <v>4839.7872302368005</v>
+        <f t="shared" si="135"/>
+        <v>5193.9595510653626</v>
       </c>
       <c r="EM24" s="1">
-        <f t="shared" si="138"/>
-        <v>4791.3893579344322</v>
+        <f t="shared" si="135"/>
+        <v>5142.0199555547088</v>
       </c>
       <c r="EN24" s="1">
-        <f t="shared" si="138"/>
-        <v>4743.4754643550878</v>
+        <f t="shared" si="135"/>
+        <v>5090.599755999162</v>
       </c>
       <c r="EO24" s="1">
-        <f t="shared" si="138"/>
-        <v>4696.0407097115367</v>
+        <f t="shared" si="135"/>
+        <v>5039.6937584391699</v>
       </c>
       <c r="EP24" s="1">
-        <f t="shared" si="138"/>
-        <v>4649.0803026144213</v>
+        <f t="shared" si="135"/>
+        <v>4989.2968208547782</v>
       </c>
       <c r="EQ24" s="1">
-        <f t="shared" si="138"/>
-        <v>4602.5894995882772</v>
+        <f t="shared" si="135"/>
+        <v>4939.40385264623</v>
       </c>
       <c r="ER24" s="1">
-        <f t="shared" si="138"/>
-        <v>4556.5636045923948</v>
+        <f t="shared" si="135"/>
+        <v>4890.0098141197677</v>
       </c>
       <c r="ES24" s="1">
-        <f t="shared" si="138"/>
-        <v>4510.9979685464705</v>
+        <f t="shared" si="135"/>
+        <v>4841.1097159785704</v>
       </c>
       <c r="ET24" s="1">
-        <f t="shared" si="138"/>
-        <v>4465.8879888610054</v>
+        <f t="shared" si="135"/>
+        <v>4792.6986188187848</v>
       </c>
       <c r="EU24" s="1">
-        <f t="shared" si="138"/>
-        <v>4421.2291089723949</v>
+        <f t="shared" si="135"/>
+        <v>4744.7716326305972</v>
       </c>
       <c r="EV24" s="1">
-        <f t="shared" si="138"/>
-        <v>4377.0168178826707</v>
+        <f t="shared" si="135"/>
+        <v>4697.3239163042908</v>
       </c>
       <c r="EW24" s="1">
-        <f t="shared" si="138"/>
-        <v>4333.246649703844</v>
+        <f t="shared" si="135"/>
+        <v>4650.3506771412476</v>
       </c>
       <c r="EX24" s="1">
-        <f t="shared" si="138"/>
-        <v>4289.9141832068053</v>
+        <f t="shared" si="135"/>
+        <v>4603.8471703698351</v>
       </c>
       <c r="EY24" s="1">
-        <f t="shared" si="138"/>
-        <v>4247.0150413747369</v>
+        <f t="shared" si="135"/>
+        <v>4557.8086986661365</v>
       </c>
       <c r="EZ24" s="1">
-        <f t="shared" si="138"/>
-        <v>4204.5448909609895</v>
+        <f t="shared" si="135"/>
+        <v>4512.2306116794753</v>
       </c>
       <c r="FA24" s="1">
-        <f t="shared" si="138"/>
-        <v>4162.4994420513794</v>
+        <f t="shared" si="135"/>
+        <v>4467.1083055626805</v>
       </c>
       <c r="FB24" s="1">
-        <f t="shared" si="138"/>
-        <v>4120.8744476308657</v>
+        <f t="shared" si="135"/>
+        <v>4422.4372225070538</v>
       </c>
       <c r="FC24" s="1">
-        <f t="shared" si="138"/>
-        <v>4079.6657031545569</v>
+        <f t="shared" si="135"/>
+        <v>4378.2128502819833</v>
       </c>
       <c r="FD24" s="1">
-        <f t="shared" si="138"/>
-        <v>4038.8690461230112</v>
+        <f t="shared" si="135"/>
+        <v>4334.4307217791638</v>
       </c>
       <c r="FE24" s="1">
-        <f t="shared" si="138"/>
-        <v>3998.4803556617812</v>
+        <f t="shared" si="135"/>
+        <v>4291.0864145613723</v>
       </c>
       <c r="FF24" s="1">
-        <f t="shared" si="138"/>
-        <v>3958.4955521051634</v>
+        <f t="shared" si="135"/>
+        <v>4248.1755504157582</v>
       </c>
       <c r="FG24" s="1">
-        <f t="shared" si="138"/>
-        <v>3918.9105965841118</v>
+        <f t="shared" si="135"/>
+        <v>4205.6937949116009</v>
       </c>
       <c r="FH24" s="1">
-        <f t="shared" si="138"/>
-        <v>3879.7214906182708</v>
+        <f t="shared" si="135"/>
+        <v>4163.6368569624847</v>
       </c>
       <c r="FI24" s="1">
-        <f t="shared" si="138"/>
-        <v>3840.9242757120878</v>
+        <f t="shared" si="135"/>
+        <v>4122.0004883928596</v>
       </c>
       <c r="FJ24" s="1">
-        <f t="shared" si="138"/>
-        <v>3802.515032954967</v>
+        <f t="shared" si="135"/>
+        <v>4080.780483508931</v>
       </c>
       <c r="FK24" s="1">
-        <f t="shared" si="138"/>
-        <v>3764.4898826254171</v>
+        <f t="shared" si="135"/>
+        <v>4039.9726786738415</v>
       </c>
       <c r="FL24" s="1">
-        <f t="shared" si="138"/>
-        <v>3726.8449837991629</v>
+        <f t="shared" si="135"/>
+        <v>3999.572951887103</v>
       </c>
       <c r="FM24" s="1">
-        <f t="shared" si="138"/>
-        <v>3689.5765339611712</v>
+        <f t="shared" si="135"/>
+        <v>3959.577222368232</v>
       </c>
       <c r="FN24" s="1">
-        <f t="shared" si="138"/>
-        <v>3652.6807686215593</v>
+        <f t="shared" si="135"/>
+        <v>3919.9814501445499</v>
       </c>
       <c r="FO24" s="1">
-        <f t="shared" si="138"/>
-        <v>3616.1539609353435</v>
+        <f t="shared" si="135"/>
+        <v>3880.7816356431044</v>
       </c>
       <c r="FP24" s="1">
-        <f t="shared" si="138"/>
-        <v>3579.9924213259901</v>
+        <f t="shared" si="135"/>
+        <v>3841.9738192866735</v>
       </c>
       <c r="FQ24" s="1">
-        <f t="shared" si="138"/>
-        <v>3544.1924971127301</v>
+        <f t="shared" si="135"/>
+        <v>3803.5540810938069</v>
       </c>
       <c r="FR24" s="1">
-        <f t="shared" si="138"/>
-        <v>3508.7505721416028</v>
+        <f t="shared" si="135"/>
+        <v>3765.5185402828688</v>
       </c>
       <c r="FS24" s="1">
-        <f t="shared" si="138"/>
-        <v>3473.6630664201866</v>
+        <f t="shared" si="135"/>
+        <v>3727.8633548800399</v>
       </c>
       <c r="FT24" s="1">
-        <f t="shared" si="138"/>
-        <v>3438.9264357559846</v>
+        <f t="shared" si="135"/>
+        <v>3690.5847213312395</v>
       </c>
       <c r="FU24" s="1">
-        <f t="shared" si="138"/>
-        <v>3404.5371713984246</v>
+        <f t="shared" si="135"/>
+        <v>3653.6788741179271</v>
       </c>
       <c r="FV24" s="1">
-        <f t="shared" si="138"/>
-        <v>3370.4917996844401</v>
+        <f t="shared" si="135"/>
+        <v>3617.1420853767477</v>
       </c>
       <c r="FW24" s="1">
-        <f t="shared" si="138"/>
-        <v>3336.7868816875957</v>
+        <f t="shared" si="135"/>
+        <v>3580.9706645229803</v>
       </c>
     </row>
     <row r="25" spans="2:179" x14ac:dyDescent="0.3">
@@ -5242,12 +5239,12 @@
         <v>424.2</v>
       </c>
       <c r="AG25" s="5">
-        <f>424.2</f>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AH25" s="5">
-        <f>424.2</f>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AJ25" s="5">
         <v>480</v>
@@ -5271,48 +5268,48 @@
         <v>478</v>
       </c>
       <c r="AQ25" s="5">
-        <f t="shared" ref="AQ25:BA25" si="139">424.2</f>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AR25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AS25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AT25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AU25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AV25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AW25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AX25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AY25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="AZ25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
       <c r="BA25" s="5">
-        <f t="shared" si="139"/>
-        <v>424.2</v>
+        <f>417</f>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="2:179" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5320,204 +5317,204 @@
         <v>35</v>
       </c>
       <c r="C26" s="8">
-        <f t="shared" ref="C26:M26" si="140">C24/C25</f>
+        <f t="shared" ref="C26:M26" si="136">C24/C25</f>
         <v>1.2147499999999989</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>1.3815625</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>1.3881250000000001</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>0.82877083333333312</v>
       </c>
       <c r="G26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>1.4041666666666666</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>1.3187500000000001</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>1.6520833333333333</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>1.774770833333333</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>1.9895833333333333</v>
       </c>
       <c r="L26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>2.2916666666666665</v>
       </c>
       <c r="M26" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="136"/>
         <v>1.9895833333333333</v>
       </c>
       <c r="N26" s="8">
-        <f t="shared" ref="N26:S26" si="141">N24/N25</f>
+        <f t="shared" ref="N26:S26" si="137">N24/N25</f>
         <v>4.6875</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" ref="O26" si="142">O24/O25</f>
+        <f t="shared" ref="O26" si="138">O24/O25</f>
         <v>2.8922018348623855</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>2.5596330275229358</v>
       </c>
       <c r="Q26" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>2.7798165137614679</v>
       </c>
       <c r="R26" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>2.8279816513761467</v>
       </c>
       <c r="S26" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="137"/>
         <v>2.903669724770642</v>
       </c>
       <c r="T26" s="8">
-        <f t="shared" ref="T26" si="143">T24/T25</f>
+        <f t="shared" ref="T26" si="139">T24/T25</f>
         <v>2.7018348623853212</v>
       </c>
       <c r="U26" s="8">
-        <f t="shared" ref="U26" si="144">U24/U25</f>
+        <f t="shared" ref="U26" si="140">U24/U25</f>
         <v>2.6055045871559632</v>
       </c>
       <c r="V26" s="8">
-        <f t="shared" ref="V26" si="145">V24/V25</f>
+        <f t="shared" ref="V26" si="141">V24/V25</f>
         <v>2.6972477064220182</v>
       </c>
       <c r="W26" s="8">
-        <f t="shared" ref="W26:X26" si="146">W24/W25</f>
+        <f t="shared" ref="W26:X26" si="142">W24/W25</f>
         <v>2.8600917431192658</v>
       </c>
       <c r="X26" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>2.9701834862385321</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" ref="Y26" si="147">Y24/Y25</f>
+        <f t="shared" ref="Y26" si="143">Y24/Y25</f>
         <v>3.2178899082568808</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" ref="Z26" si="148">Z24/Z25</f>
+        <f t="shared" ref="Z26" si="144">Z24/Z25</f>
         <v>3.4013761467889907</v>
       </c>
       <c r="AA26" s="8">
-        <f t="shared" ref="AA26:AB26" si="149">AA24/AA25</f>
+        <f t="shared" ref="AA26:AB26" si="145">AA24/AA25</f>
         <v>1.4220183486238531</v>
       </c>
       <c r="AB26" s="8">
+        <f t="shared" si="145"/>
+        <v>3.6077981651376145</v>
+      </c>
+      <c r="AC26" s="8">
+        <f t="shared" ref="AC26" si="146">AC24/AC25</f>
+        <v>3.8623853211009176</v>
+      </c>
+      <c r="AD26" s="8">
+        <f t="shared" ref="AD26" si="147">AD24/AD25</f>
+        <v>3.8600917431192658</v>
+      </c>
+      <c r="AE26" s="8">
+        <f t="shared" ref="AE26:AH26" si="148">AE24/AE25</f>
+        <v>4.1536697247706424</v>
+      </c>
+      <c r="AF26" s="8">
+        <f t="shared" si="148"/>
+        <v>3.9863272041489863</v>
+      </c>
+      <c r="AG26" s="8">
+        <f t="shared" si="148"/>
+        <v>4.4508393285371701</v>
+      </c>
+      <c r="AH26" s="8">
+        <f t="shared" si="148"/>
+        <v>4.2627964028776981</v>
+      </c>
+      <c r="AJ26" s="8">
+        <f t="shared" ref="AJ26:AL26" si="149">AJ24/AJ25</f>
+        <v>4.8132083333333302</v>
+      </c>
+      <c r="AK26" s="8">
         <f t="shared" si="149"/>
-        <v>3.6077981651376145</v>
-      </c>
-      <c r="AC26" s="8">
-        <f t="shared" ref="AC26" si="150">AC24/AC25</f>
-        <v>3.8623853211009176</v>
-      </c>
-      <c r="AD26" s="8">
-        <f t="shared" ref="AD26" si="151">AD24/AD25</f>
-        <v>3.8600917431192658</v>
-      </c>
-      <c r="AE26" s="8">
-        <f t="shared" ref="AE26:AH26" si="152">AE24/AE25</f>
-        <v>4.1536697247706424</v>
-      </c>
-      <c r="AF26" s="8">
-        <f t="shared" si="152"/>
-        <v>3.9863272041489863</v>
-      </c>
-      <c r="AG26" s="8">
-        <f t="shared" si="152"/>
-        <v>4.4837965723715225</v>
-      </c>
-      <c r="AH26" s="8">
-        <f t="shared" si="152"/>
-        <v>4.5985279302215938</v>
-      </c>
-      <c r="AJ26" s="8">
-        <f t="shared" ref="AJ26:AL26" si="153">AJ24/AJ25</f>
-        <v>4.8132083333333302</v>
-      </c>
-      <c r="AK26" s="8">
-        <f t="shared" si="153"/>
         <v>6.1497708333333341</v>
       </c>
       <c r="AL26" s="8">
-        <f t="shared" si="153"/>
+        <f t="shared" si="149"/>
         <v>10.958333333333334</v>
       </c>
       <c r="AM26" s="8">
-        <f t="shared" ref="AM26" si="154">AM24/AM25</f>
+        <f t="shared" ref="AM26" si="150">AM24/AM25</f>
         <v>10.087866108786612</v>
       </c>
       <c r="AN26" s="8">
-        <f t="shared" ref="AN26" si="155">AN24/AN25</f>
+        <f t="shared" ref="AN26" si="151">AN24/AN25</f>
         <v>9.94979079497908</v>
       </c>
       <c r="AO26" s="8">
-        <f t="shared" ref="AO26" si="156">AO24/AO25</f>
+        <f t="shared" ref="AO26" si="152">AO24/AO25</f>
         <v>11.355648535564853</v>
       </c>
       <c r="AP26" s="8">
-        <f t="shared" ref="AP26" si="157">AP24/AP25</f>
+        <f t="shared" ref="AP26" si="153">AP24/AP25</f>
         <v>11.631799163179917</v>
       </c>
       <c r="AQ26" s="8">
-        <f t="shared" ref="AQ26" si="158">AQ24/AQ25</f>
-        <v>17.303517336162184</v>
+        <f t="shared" ref="AQ26" si="154">AQ24/AQ25</f>
+        <v>16.999223261390885</v>
       </c>
       <c r="AR26" s="8">
-        <f t="shared" ref="AR26" si="159">AR24/AR25</f>
-        <v>19.590898475247524</v>
+        <f t="shared" ref="AR26" si="155">AR24/AR25</f>
+        <v>19.77491490167866</v>
       </c>
       <c r="AS26" s="8">
-        <f t="shared" ref="AS26" si="160">AS24/AS25</f>
-        <v>21.152153436599715</v>
+        <f t="shared" ref="AS26" si="156">AS24/AS25</f>
+        <v>22.45816868177458</v>
       </c>
       <c r="AT26" s="8">
-        <f t="shared" ref="AT26" si="161">AT24/AT25</f>
-        <v>22.459922658195701</v>
+        <f t="shared" ref="AT26" si="157">AT24/AT25</f>
+        <v>24.17055589472902</v>
       </c>
       <c r="AU26" s="8">
-        <f t="shared" ref="AU26" si="162">AU24/AU25</f>
-        <v>23.440977412617794</v>
+        <f t="shared" ref="AU26" si="158">AU24/AU25</f>
+        <v>25.738485509439769</v>
       </c>
       <c r="AV26" s="8">
-        <f t="shared" ref="AV26:BA26" si="163">AV24/AV25</f>
-        <v>24.55447409255784</v>
+        <f t="shared" ref="AV26:BA26" si="159">AV24/AV25</f>
+        <v>26.934928314581477</v>
       </c>
       <c r="AW26" s="8">
-        <f t="shared" si="163"/>
-        <v>25.196312942056505</v>
+        <f t="shared" si="159"/>
+        <v>27.611388817479114</v>
       </c>
       <c r="AX26" s="8">
-        <f t="shared" si="163"/>
-        <v>25.852261817818402</v>
+        <f t="shared" si="159"/>
+        <v>28.302530780168141</v>
       </c>
       <c r="AY26" s="8">
-        <f t="shared" si="163"/>
-        <v>26.522606283085409</v>
+        <f t="shared" si="159"/>
+        <v>29.008650339556464</v>
       </c>
       <c r="AZ26" s="8">
-        <f t="shared" si="163"/>
-        <v>27.207637271200333</v>
+        <f t="shared" si="159"/>
+        <v>29.730049219775783</v>
       </c>
       <c r="BA26" s="8">
-        <f t="shared" si="163"/>
-        <v>27.907651174605718</v>
+        <f t="shared" si="159"/>
+        <v>30.467034826147362</v>
       </c>
     </row>
     <row r="28" spans="2:179" x14ac:dyDescent="0.3">
@@ -5525,84 +5522,84 @@
         <v>87</v>
       </c>
       <c r="S28" s="12">
-        <f t="shared" ref="S28:AH28" si="164">S3/O3-1</f>
+        <f t="shared" ref="S28:AH28" si="160">S3/O3-1</f>
         <v>0.1043526785714286</v>
       </c>
       <c r="T28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.15625</v>
       </c>
       <c r="U28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.12879409351927817</v>
       </c>
       <c r="V28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.11017838405036717</v>
       </c>
       <c r="W28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.10485093481556351</v>
       </c>
       <c r="X28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.10982800982800978</v>
       </c>
       <c r="Y28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.1218507751937985</v>
       </c>
       <c r="Z28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.12547258979206055</v>
       </c>
       <c r="AA28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.12417104962268466</v>
       </c>
       <c r="AB28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.12021253044055791</v>
       </c>
       <c r="AC28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.11854890952278119</v>
       </c>
       <c r="AD28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.12639093008608016</v>
       </c>
       <c r="AE28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.11533767290480057</v>
       </c>
       <c r="AF28" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="160"/>
         <v>0.11482213438735167</v>
       </c>
       <c r="AG28" s="12">
-        <f t="shared" si="164"/>
-        <v>0.1100000000000001</v>
+        <f t="shared" si="160"/>
+        <v>0.15617760617760612</v>
       </c>
       <c r="AH28" s="12">
-        <f t="shared" si="164"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="160"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AN28" s="12">
-        <f t="shared" ref="AN28:AP30" si="165">AN3/AM3-1</f>
+        <f t="shared" ref="AN28:AP30" si="161">AN3/AM3-1</f>
         <v>0.12454539216359017</v>
       </c>
       <c r="AO28" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="161"/>
         <v>0.11569441054430074</v>
       </c>
       <c r="AP28" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="161"/>
         <v>0.12234740756945972</v>
       </c>
       <c r="AQ28" s="12">
-        <f t="shared" ref="AQ28:AQ30" si="166">AQ3/AP3-1</f>
-        <v>0.10985332098825595</v>
+        <f t="shared" ref="AQ28:AQ30" si="162">AQ3/AP3-1</f>
+        <v>0.12673846303786362</v>
       </c>
       <c r="AR28" s="12"/>
       <c r="AS28" s="12"/>
@@ -5620,84 +5617,84 @@
         <v>88</v>
       </c>
       <c r="S29" s="12">
-        <f t="shared" ref="S29:AH29" si="167">S4/O4-1</f>
+        <f t="shared" ref="S29:AH29" si="163">S4/O4-1</f>
         <v>-6.4516129032258118E-2</v>
       </c>
       <c r="T29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-4.5751633986928053E-2</v>
       </c>
       <c r="U29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>5.8823529411764719E-2</v>
       </c>
       <c r="V29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-0.1015625</v>
       </c>
       <c r="W29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-0.17241379310344829</v>
       </c>
       <c r="X29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-0.1095890410958904</v>
       </c>
       <c r="Y29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-0.23809523809523814</v>
       </c>
       <c r="Z29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-8.6956521739129933E-3</v>
       </c>
       <c r="AA29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-8.3333333333333037E-3</v>
       </c>
       <c r="AB29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-0.19999999999999996</v>
       </c>
       <c r="AC29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-0.14583333333333337</v>
       </c>
       <c r="AD29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-0.28947368421052633</v>
       </c>
       <c r="AE29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-0.20168067226890751</v>
       </c>
       <c r="AF29" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>-0.15384615384615385</v>
       </c>
       <c r="AG29" s="12">
-        <f t="shared" si="167"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="163"/>
+        <v>-9.7560975609756073E-2</v>
       </c>
       <c r="AH29" s="12">
-        <f t="shared" si="167"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="163"/>
+        <v>-0.13580246913580252</v>
       </c>
       <c r="AN29" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="161"/>
         <v>-4.1441441441441462E-2</v>
       </c>
       <c r="AO29" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="161"/>
         <v>-0.13533834586466165</v>
       </c>
       <c r="AP29" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="161"/>
         <v>-0.16086956521739126</v>
       </c>
       <c r="AQ29" s="12">
-        <f t="shared" si="166"/>
-        <v>-9.5181347150259055E-2</v>
+        <f t="shared" si="162"/>
+        <v>-0.15284974093264247</v>
       </c>
       <c r="AR29" s="12"/>
       <c r="AS29" s="12"/>
@@ -5715,84 +5712,84 @@
         <v>89</v>
       </c>
       <c r="S30" s="12">
-        <f t="shared" ref="S30:AH30" si="168">S5/O5-1</f>
+        <f t="shared" ref="S30:AH30" si="164">S5/O5-1</f>
         <v>-4.216867469879515E-2</v>
       </c>
       <c r="T30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>4.9382716049382713E-2</v>
       </c>
       <c r="U30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>0.12578616352201255</v>
       </c>
       <c r="V30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>4.705882352941182E-2</v>
       </c>
       <c r="W30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>1.8867924528301883E-2</v>
       </c>
       <c r="X30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>-5.8823529411764497E-3</v>
       </c>
       <c r="Y30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>-8.9385474860335212E-2</v>
       </c>
       <c r="Z30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>-3.9325842696629199E-2</v>
       </c>
       <c r="AA30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>-9.259259259259256E-2</v>
       </c>
       <c r="AB30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>-0.14201183431952658</v>
       </c>
       <c r="AC30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>-0.10429447852760731</v>
       </c>
       <c r="AD30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>-6.4327485380117011E-2</v>
       </c>
       <c r="AE30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>-7.4829931972789088E-2</v>
       </c>
       <c r="AF30" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="164"/>
         <v>-6.8965517241379448E-3</v>
       </c>
       <c r="AG30" s="12">
-        <f t="shared" si="168"/>
-        <v>-5.0000000000000044E-2</v>
+        <f t="shared" si="164"/>
+        <v>-0.10273972602739723</v>
       </c>
       <c r="AH30" s="12">
-        <f t="shared" si="168"/>
-        <v>-5.0000000000000044E-2</v>
+        <f t="shared" si="164"/>
+        <v>-7.9999999999999849E-2</v>
       </c>
       <c r="AN30" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="161"/>
         <v>4.4140030441400357E-2</v>
       </c>
       <c r="AO30" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="161"/>
         <v>-3.0612244897959218E-2</v>
       </c>
       <c r="AP30" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="161"/>
         <v>-0.10075187969924815</v>
       </c>
       <c r="AQ30" s="12">
-        <f t="shared" si="166"/>
-        <v>-4.5652173913043437E-2</v>
+        <f t="shared" si="162"/>
+        <v>-6.6555183946488183E-2</v>
       </c>
       <c r="AR30" s="12"/>
       <c r="AS30" s="12"/>
@@ -5810,183 +5807,183 @@
         <v>44</v>
       </c>
       <c r="G31" s="12">
-        <f t="shared" ref="G31:R31" si="169">G6/C6-1</f>
+        <f t="shared" ref="G31:R31" si="165">G6/C6-1</f>
         <v>0.25111234036412622</v>
       </c>
       <c r="H31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.24990889876831135</v>
       </c>
       <c r="I31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.23697121008432709</v>
       </c>
       <c r="J31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.36983554318364975</v>
       </c>
       <c r="K31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.18838908112264519</v>
       </c>
       <c r="L31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.13994169096209919</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.13796753705010589</v>
       </c>
       <c r="N31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.14440797609577727</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.26334519572953741</v>
       </c>
       <c r="P31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.22602301790281332</v>
       </c>
       <c r="Q31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.22015503875969</v>
       </c>
       <c r="R31" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="165"/>
         <v>0.20035046728971961</v>
       </c>
       <c r="S31" s="12">
-        <f t="shared" ref="S31:AH31" si="170">S6/O6-1</f>
+        <f t="shared" ref="S31:AH31" si="166">S6/O6-1</f>
         <v>9.1421254801536511E-2</v>
       </c>
       <c r="T31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.14367666232073018</v>
       </c>
       <c r="U31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.12655654383735704</v>
       </c>
       <c r="V31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.1009732360097324</v>
       </c>
       <c r="W31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>9.2210229938995747E-2</v>
       </c>
       <c r="X31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>9.8039215686274606E-2</v>
       </c>
       <c r="Y31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.1030904579291676</v>
       </c>
       <c r="Z31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.1155801104972376</v>
       </c>
       <c r="AA31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.11321160042964551</v>
       </c>
       <c r="AB31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.10236710963455153</v>
       </c>
       <c r="AC31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.10593047034764824</v>
       </c>
       <c r="AD31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.11053882725832009</v>
       </c>
       <c r="AE31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.10266306445387885</v>
       </c>
       <c r="AF31" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="166"/>
         <v>0.10623469579958567</v>
       </c>
       <c r="AG31" s="12">
-        <f t="shared" si="170"/>
-        <v>0.10431582840236686</v>
+        <f t="shared" si="166"/>
+        <v>0.14534023668639051</v>
       </c>
       <c r="AH31" s="12">
-        <f t="shared" si="170"/>
-        <v>9.4562968248305568E-2</v>
+        <f t="shared" si="166"/>
+        <v>0.11059579022475918</v>
       </c>
       <c r="AK31" s="12">
-        <f t="shared" ref="AK31:AV31" si="171">AK6/AJ6-1</f>
+        <f t="shared" ref="AK31:AV31" si="167">AK6/AJ6-1</f>
         <v>0.2767445182895123</v>
       </c>
       <c r="AL31" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="167"/>
         <v>0.15191738564525448</v>
       </c>
       <c r="AM31" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="167"/>
         <v>0.22668635374572577</v>
       </c>
       <c r="AN31" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="167"/>
         <v>0.11536268609439349</v>
       </c>
       <c r="AO31" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="167"/>
         <v>0.10240826990798602</v>
       </c>
       <c r="AP31" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="167"/>
         <v>0.10799113813179462</v>
       </c>
       <c r="AQ31" s="12">
-        <f t="shared" si="171"/>
-        <v>0.10184887235526618</v>
+        <f t="shared" si="167"/>
+        <v>0.11634503603813062</v>
       </c>
       <c r="AR31" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="167"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AS31" s="12">
+        <f t="shared" si="167"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AS31" s="12">
-        <f t="shared" si="171"/>
+      <c r="AT31" s="12">
+        <f t="shared" si="167"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AT31" s="12">
-        <f t="shared" si="171"/>
+      <c r="AU31" s="12">
+        <f t="shared" si="167"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AU31" s="12">
-        <f t="shared" si="171"/>
+      <c r="AV31" s="12">
+        <f t="shared" si="167"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AV31" s="12">
-        <f t="shared" si="171"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="AW31" s="12">
-        <f t="shared" ref="AW31:BA31" si="172">AW6/AV6-1</f>
+        <f t="shared" ref="AW31:BA31" si="168">AW6/AV6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX31" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AY31" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ31" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA31" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5995,203 +5992,203 @@
         <v>41</v>
       </c>
       <c r="C32" s="12">
-        <f t="shared" ref="C32:R32" si="173">C11/C6</f>
+        <f t="shared" ref="C32:R32" si="169">C11/C6</f>
         <v>0.87546598042280954</v>
       </c>
       <c r="D32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.87184789738357271</v>
       </c>
       <c r="E32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.8710258917191892</v>
       </c>
       <c r="F32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.83551571313456885</v>
       </c>
       <c r="G32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.8473663975394079</v>
       </c>
       <c r="H32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.85167638483965014</v>
       </c>
       <c r="I32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.85321100917431192</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.84893413637974025</v>
       </c>
       <c r="K32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.85376900679391787</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.86732736572890023</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.86759689922480621</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.875</v>
       </c>
       <c r="O32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.88553137003841231</v>
       </c>
       <c r="P32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.8842242503259452</v>
       </c>
       <c r="Q32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.88132147395171534</v>
       </c>
       <c r="R32" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.87664233576642336</v>
       </c>
       <c r="S32" s="12">
-        <f t="shared" ref="S32:AH32" si="174">S11/S6</f>
+        <f t="shared" ref="S32:AH32" si="170">S11/S6</f>
         <v>0.87986860628812769</v>
       </c>
       <c r="T32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.87710898312813501</v>
       </c>
       <c r="U32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.87683284457478006</v>
       </c>
       <c r="V32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.87447513812154698</v>
       </c>
       <c r="W32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.87798066595059077</v>
       </c>
       <c r="X32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.8812292358803987</v>
       </c>
       <c r="Y32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.88139059304703471</v>
       </c>
       <c r="Z32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.87440570522979399</v>
       </c>
       <c r="AA32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.88614434581242763</v>
       </c>
       <c r="AB32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.88736108495008481</v>
       </c>
       <c r="AC32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.8975591715976331</v>
       </c>
       <c r="AD32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.89011773100249736</v>
       </c>
       <c r="AE32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.89114455722786134</v>
       </c>
       <c r="AF32" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.89136727396560533</v>
       </c>
       <c r="AG32" s="12">
-        <f t="shared" si="174"/>
-        <v>0.8899999999999999</v>
+        <f t="shared" si="170"/>
+        <v>0.89522118178882792</v>
       </c>
       <c r="AH32" s="12">
-        <f t="shared" si="174"/>
-        <v>0.8899999999999999</v>
+        <f t="shared" si="170"/>
+        <v>0.89</v>
       </c>
       <c r="AJ32" s="12">
-        <f t="shared" ref="AJ32:AV32" si="175">AJ11/AJ6</f>
+        <f t="shared" ref="AJ32:AV32" si="171">AJ11/AJ6</f>
         <v>0.86342269030978736</v>
       </c>
       <c r="AK32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.85032772533018708</v>
       </c>
       <c r="AL32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.86617967050046629</v>
       </c>
       <c r="AM32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.88184985745961353</v>
       </c>
       <c r="AN32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.87703055776439853</v>
       </c>
       <c r="AO32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.87871605955999799</v>
       </c>
       <c r="AP32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.89035108114392003</v>
       </c>
       <c r="AQ32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.89</v>
       </c>
       <c r="AR32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.89000000000000012</v>
       </c>
       <c r="AS32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.89</v>
       </c>
       <c r="AT32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.89</v>
       </c>
       <c r="AU32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.89</v>
       </c>
       <c r="AV32" s="12">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>0.89</v>
       </c>
       <c r="AW32" s="12">
-        <f t="shared" ref="AW32:BA32" si="176">AW11/AW6</f>
+        <f t="shared" ref="AW32:BA32" si="172">AW11/AW6</f>
         <v>0.89</v>
       </c>
       <c r="AX32" s="12">
-        <f t="shared" si="176"/>
+        <f t="shared" si="172"/>
         <v>0.89</v>
       </c>
       <c r="AY32" s="12">
-        <f t="shared" si="176"/>
+        <f t="shared" si="172"/>
         <v>0.89</v>
       </c>
       <c r="AZ32" s="12">
-        <f t="shared" si="176"/>
+        <f t="shared" si="172"/>
         <v>0.89</v>
       </c>
       <c r="BA32" s="12">
-        <f t="shared" si="176"/>
+        <f t="shared" si="172"/>
         <v>0.89</v>
       </c>
       <c r="BC32" t="s">
@@ -6206,204 +6203,204 @@
         <v>42</v>
       </c>
       <c r="C33" s="12">
-        <f t="shared" ref="C33:R33" si="177">C17/C6</f>
+        <f t="shared" ref="C33:R33" si="173">C17/C6</f>
         <v>0.33802640756150926</v>
       </c>
       <c r="D33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.31816194154944971</v>
       </c>
       <c r="E33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.31365993330656289</v>
       </c>
       <c r="F33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.20149164896344587</v>
       </c>
       <c r="G33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.26720492118415995</v>
       </c>
       <c r="H33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.27332361516034986</v>
       </c>
       <c r="I33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.30134086097388851</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.32418765082187473</v>
       </c>
       <c r="K33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.30313814299579422</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.32480818414322249</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.33147286821705424</v>
       </c>
       <c r="N33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.35484813084112149</v>
       </c>
       <c r="O33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.37234314980793853</v>
       </c>
       <c r="P33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.36662320730117343</v>
       </c>
       <c r="Q33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.36620076238881832</v>
       </c>
       <c r="R33" s="12">
-        <f t="shared" si="177"/>
+        <f t="shared" si="173"/>
         <v>0.36520681265206811</v>
       </c>
       <c r="S33" s="12">
-        <f t="shared" ref="S33:AH33" si="178">S17/S6</f>
+        <f t="shared" ref="S33:AH33" si="174">S17/S6</f>
         <v>0.37071797278273111</v>
       </c>
       <c r="T33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.34860921112631099</v>
       </c>
       <c r="U33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.33476201218136703</v>
       </c>
       <c r="V33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.33259668508287293</v>
       </c>
       <c r="W33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.3407089151450054</v>
       </c>
       <c r="X33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.33720930232558138</v>
       </c>
       <c r="Y33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.34703476482617585</v>
       </c>
       <c r="Z33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.3452852614896989</v>
       </c>
       <c r="AA33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.17502894635275956</v>
       </c>
       <c r="AB33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.35505744961386326</v>
       </c>
       <c r="AC33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.36834319526627218</v>
       </c>
       <c r="AD33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.34909026043524793</v>
       </c>
       <c r="AE33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.37854392719635982</v>
       </c>
       <c r="AF33" s="12">
-        <f t="shared" si="178"/>
+        <f t="shared" si="174"/>
         <v>0.35910097054316364</v>
       </c>
       <c r="AG33" s="12">
-        <f t="shared" si="178"/>
-        <v>0.37673735043049889</v>
+        <f t="shared" si="174"/>
+        <v>0.36503067484662577</v>
       </c>
       <c r="AH33" s="12">
-        <f t="shared" si="178"/>
-        <v>0.37941493973390344</v>
+        <f t="shared" si="174"/>
+        <v>0.34156280115644078</v>
       </c>
       <c r="AJ33" s="12">
-        <f t="shared" ref="AJ33:AV33" si="179">AJ17/AJ6</f>
+        <f t="shared" ref="AJ33:AV33" si="175">AJ17/AJ6</f>
         <v>0.29257847546445231</v>
       </c>
       <c r="AK33" s="12">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.29262980554904067</v>
       </c>
       <c r="AL33" s="12">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.32926639726453216</v>
       </c>
       <c r="AM33" s="12">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.36756414317389929</v>
       </c>
       <c r="AN33" s="12">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.34635919572872886</v>
       </c>
       <c r="AO33" s="12">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.3426245556185275</v>
       </c>
       <c r="AP33" s="12">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.31346198558474775</v>
       </c>
       <c r="AQ33" s="12">
-        <f t="shared" si="179"/>
-        <v>0.37288022161394302</v>
+        <f t="shared" si="175"/>
+        <v>0.35875619610946802</v>
       </c>
       <c r="AR33" s="12">
-        <f t="shared" si="179"/>
-        <v>0.39307707454914959</v>
+        <f t="shared" si="175"/>
+        <v>0.37969519117530115</v>
       </c>
       <c r="AS33" s="12">
-        <f t="shared" si="179"/>
-        <v>0.40438873947033582</v>
+        <f t="shared" si="175"/>
+        <v>0.39940355166471503</v>
       </c>
       <c r="AT33" s="12">
-        <f t="shared" si="179"/>
-        <v>0.41301721116370593</v>
+        <f t="shared" si="175"/>
+        <v>0.40945349446772644</v>
       </c>
       <c r="AU33" s="12">
-        <f t="shared" si="179"/>
-        <v>0.41859295734485052</v>
+        <f t="shared" si="175"/>
+        <v>0.4192975326398356</v>
       </c>
       <c r="AV33" s="12">
-        <f t="shared" si="179"/>
-        <v>0.42580426559917545</v>
+        <f t="shared" si="175"/>
+        <v>0.42604260028893648</v>
       </c>
       <c r="AW33" s="12">
-        <f t="shared" ref="AW33:BA33" si="180">AW17/AW6</f>
-        <v>0.42840912451791419</v>
+        <f t="shared" ref="AW33:BA33" si="176">AW17/AW6</f>
+        <v>0.42819304817782994</v>
       </c>
       <c r="AX33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.43098451695384415</v>
+        <f t="shared" si="176"/>
+        <v>0.43031897922239021</v>
       </c>
       <c r="AY33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.43353065476169361</v>
+        <f t="shared" si="176"/>
+        <v>0.43242056645007404</v>
       </c>
       <c r="AZ33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.4360477462087447</v>
+        <f t="shared" si="176"/>
+        <v>0.43449797987172029</v>
       </c>
       <c r="BA33" s="12">
-        <f t="shared" si="180"/>
-        <v>0.43853599598038934</v>
+        <f t="shared" si="176"/>
+        <v>0.43655138648523711</v>
       </c>
       <c r="BC33" t="s">
         <v>46</v>
@@ -6421,184 +6418,184 @@
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12">
-        <f t="shared" ref="G34:R34" si="181">G12/C12-1</f>
+        <f t="shared" ref="G34:R34" si="177">G12/C12-1</f>
         <v>0.33329510264938644</v>
       </c>
       <c r="H34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.27228503461363696</v>
       </c>
       <c r="I34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.22819330258672554</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.201557842100202</v>
       </c>
       <c r="K34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.1440860215053763</v>
       </c>
       <c r="L34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.11764705882352944</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.15510204081632661</v>
       </c>
       <c r="N34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.11644657863145258</v>
       </c>
       <c r="O34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.16541353383458657</v>
       </c>
       <c r="P34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.15037593984962405</v>
       </c>
       <c r="Q34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.15017667844522964</v>
       </c>
       <c r="R34" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.17741935483870974</v>
       </c>
       <c r="S34" s="12">
-        <f t="shared" ref="S34:AH34" si="182">S12/O12-1</f>
+        <f t="shared" ref="S34:AH34" si="178">S12/O12-1</f>
         <v>0.13064516129032255</v>
       </c>
       <c r="T34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.20588235294117641</v>
       </c>
       <c r="U34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.19047619047619047</v>
       </c>
       <c r="V34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.17656012176560121</v>
       </c>
       <c r="W34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.17974322396576325</v>
       </c>
       <c r="X34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.18699186991869921</v>
       </c>
       <c r="Y34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.13677419354838705</v>
       </c>
       <c r="Z34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.1500646830530401</v>
       </c>
       <c r="AA34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.13542926239419595</v>
       </c>
       <c r="AB34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.12328767123287676</v>
       </c>
       <c r="AC34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.16004540295119174</v>
       </c>
       <c r="AD34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.12373453318335215</v>
       </c>
       <c r="AE34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>9.2651757188498385E-2</v>
       </c>
       <c r="AF34" s="12">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>9.9593495934959364E-2</v>
       </c>
       <c r="AG34" s="12">
-        <f t="shared" si="182"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="178"/>
+        <v>7.4363992172211457E-2</v>
       </c>
       <c r="AH34" s="12">
-        <f t="shared" si="182"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="178"/>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AJ34" s="12"/>
       <c r="AK34" s="12">
-        <f t="shared" ref="AK34:AV34" si="183">AK12/AJ12-1</f>
+        <f t="shared" ref="AK34:AV34" si="179">AK12/AJ12-1</f>
         <v>0.25555172615602717</v>
       </c>
       <c r="AL34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.13320903252537808</v>
       </c>
       <c r="AM34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.16087751371115178</v>
       </c>
       <c r="AN34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.17598425196850398</v>
       </c>
       <c r="AO34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.16270505523937051</v>
       </c>
       <c r="AP34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.13561762165274982</v>
       </c>
       <c r="AQ34" s="12">
-        <f t="shared" si="183"/>
-        <v>9.0375253549695778E-2</v>
+        <f t="shared" si="179"/>
+        <v>9.4039046653143998E-2</v>
       </c>
       <c r="AR34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AS34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AT34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AU34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AV34" s="12">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW34" s="12">
-        <f t="shared" ref="AW34:BA34" si="184">AW12/AV12-1</f>
+        <f t="shared" ref="AW34:BA34" si="180">AW12/AV12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="180"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AY34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="180"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="180"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA34" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" si="180"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC34" t="s">
@@ -6606,7 +6603,7 @@
       </c>
       <c r="BD34" s="5">
         <f>NPV(BD33,AQ24:FW24)</f>
-        <v>142989.24752594542</v>
+        <v>151945.85412430231</v>
       </c>
     </row>
     <row r="35" spans="2:56" x14ac:dyDescent="0.3">
@@ -6614,204 +6611,204 @@
         <v>43</v>
       </c>
       <c r="C35" s="12">
-        <f t="shared" ref="C35:R35" si="185">C13/C6</f>
+        <f t="shared" ref="C35:R35" si="181">C13/C6</f>
         <v>0.27944876019144282</v>
       </c>
       <c r="D35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.29435718970920488</v>
       </c>
       <c r="E35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.29247341864971982</v>
       </c>
       <c r="F35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.33128067540839501</v>
       </c>
       <c r="G35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.30026912725874666</v>
       </c>
       <c r="H35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.30940233236151604</v>
       </c>
       <c r="I35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.28652081863091039</v>
       </c>
       <c r="J35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.26791646891314663</v>
       </c>
       <c r="K35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.27725655127790361</v>
       </c>
       <c r="L35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.28804347826086957</v>
       </c>
       <c r="M35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.27658914728682171</v>
       </c>
       <c r="N35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.27482476635514019</v>
       </c>
       <c r="O35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.26862996158770808</v>
       </c>
       <c r="P35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.27979139504563233</v>
       </c>
       <c r="Q35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.27141041931385007</v>
       </c>
       <c r="R35" s="12">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.2751824817518248</v>
       </c>
       <c r="S35" s="12">
-        <f t="shared" ref="S35:AH35" si="186">S13/S6</f>
+        <f t="shared" ref="S35:AH35" si="182">S13/S6</f>
         <v>0.2717034256217738</v>
       </c>
       <c r="T35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.28431372549019607</v>
       </c>
       <c r="U35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.28558538235957592</v>
       </c>
       <c r="V35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.28662983425414362</v>
       </c>
       <c r="W35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.27948442534908702</v>
       </c>
       <c r="X35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.27927740863787376</v>
       </c>
       <c r="Y35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.27341513292433539</v>
       </c>
       <c r="Z35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.27099841521394613</v>
       </c>
       <c r="AA35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.26090312620609801</v>
       </c>
       <c r="AB35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.27217931813900925</v>
       </c>
       <c r="AC35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.26460798816568049</v>
       </c>
       <c r="AD35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.27399215126650017</v>
       </c>
       <c r="AE35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.26163808190409521</v>
       </c>
       <c r="AF35" s="12">
-        <f t="shared" si="186"/>
+        <f t="shared" si="182"/>
         <v>0.27686020773029119</v>
       </c>
       <c r="AG35" s="12">
-        <f t="shared" si="186"/>
-        <v>0.26</v>
+        <f t="shared" si="182"/>
+        <v>0.27897965773329025</v>
       </c>
       <c r="AH35" s="12">
-        <f t="shared" si="186"/>
-        <v>0.26</v>
+        <f t="shared" si="182"/>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AJ35" s="12">
-        <f t="shared" ref="AJ35:AV35" si="187">AJ13/AJ6</f>
+        <f t="shared" ref="AJ35:AV35" si="183">AJ13/AJ6</f>
         <v>0.29953883342571913</v>
       </c>
       <c r="AK35" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="183"/>
         <v>0.29035962953878547</v>
       </c>
       <c r="AL35" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="183"/>
         <v>0.27906434566366178</v>
       </c>
       <c r="AM35" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="183"/>
         <v>0.27374089325308837</v>
       </c>
       <c r="AN35" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="183"/>
         <v>0.28217653072816085</v>
       </c>
       <c r="AO35" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="183"/>
         <v>0.27569684167138958</v>
       </c>
       <c r="AP35" s="12">
-        <f t="shared" si="187"/>
+        <f t="shared" si="183"/>
         <v>0.26803069053708439</v>
       </c>
       <c r="AQ35" s="12">
-        <f t="shared" si="187"/>
-        <v>0.2645739105627033</v>
+        <f t="shared" si="183"/>
+        <v>0.2745982421793644</v>
       </c>
       <c r="AR35" s="12">
-        <f t="shared" si="187"/>
-        <v>0.24987535997588642</v>
+        <f t="shared" si="183"/>
+        <v>0.26211650389848418</v>
       </c>
       <c r="AS35" s="12">
-        <f t="shared" si="187"/>
-        <v>0.24035629864347172</v>
+        <f t="shared" si="183"/>
+        <v>0.24998148056985064</v>
       </c>
       <c r="AT35" s="12">
-        <f t="shared" si="187"/>
-        <v>0.23342294387491</v>
+        <f t="shared" si="183"/>
+        <v>0.24283915255356919</v>
       </c>
       <c r="AU35" s="12">
-        <f t="shared" si="187"/>
-        <v>0.22889045952782436</v>
+        <f t="shared" si="183"/>
+        <v>0.23583417699913931</v>
       </c>
       <c r="AV35" s="12">
-        <f t="shared" si="187"/>
-        <v>0.22444598458553652</v>
+        <f t="shared" si="183"/>
+        <v>0.23125487259138902</v>
       </c>
       <c r="AW35" s="12">
-        <f t="shared" ref="AW35:BA35" si="188">AW13/AW6</f>
-        <v>0.22224553375626657</v>
+        <f t="shared" ref="AW35:BA35" si="184">AW13/AW6</f>
+        <v>0.2289876679581401</v>
       </c>
       <c r="AX35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.22006665597434238</v>
+        <f t="shared" si="184"/>
+        <v>0.22674269082129561</v>
       </c>
       <c r="AY35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.21790913973929982</v>
+        <f t="shared" si="184"/>
+        <v>0.22451972326422406</v>
       </c>
       <c r="AZ35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.21577277562420866</v>
+        <f t="shared" si="184"/>
+        <v>0.22231854950673172</v>
       </c>
       <c r="BA35" s="12">
-        <f t="shared" si="188"/>
-        <v>0.21365735625534385</v>
+        <f t="shared" si="184"/>
+        <v>0.22013895588411667</v>
       </c>
       <c r="BC35" t="s">
         <v>48</v>
@@ -6830,192 +6827,192 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12">
-        <f t="shared" ref="G36:R36" si="189">G14/C14-1</f>
+        <f t="shared" ref="G36:R36" si="185">G14/C14-1</f>
         <v>0.26730814362825628</v>
       </c>
       <c r="H36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>0.23006066052572471</v>
       </c>
       <c r="I36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>0.1898294034553949</v>
       </c>
       <c r="J36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>6.3951024252413502E-2</v>
       </c>
       <c r="K36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>0.25462962962962954</v>
       </c>
       <c r="L36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>2.2831050228310446E-2</v>
       </c>
       <c r="M36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>5.0228310502283158E-2</v>
       </c>
       <c r="N36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>7.5554375248970906E-2</v>
       </c>
       <c r="O36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>7.0110701107011009E-2</v>
       </c>
       <c r="P36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>0.14285714285714279</v>
       </c>
       <c r="Q36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>0.15217391304347827</v>
       </c>
       <c r="R36" s="12">
-        <f t="shared" si="189"/>
+        <f t="shared" si="185"/>
         <v>0.12757201646090532</v>
       </c>
       <c r="S36" s="12">
-        <f t="shared" ref="S36:AH36" si="190">S14/O14-1</f>
+        <f t="shared" ref="S36:AH36" si="186">S14/O14-1</f>
         <v>-7.241379310344831E-2</v>
       </c>
       <c r="T36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>0.13671875</v>
       </c>
       <c r="U36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>0.20377358490566033</v>
       </c>
       <c r="V36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>0.24087591240875916</v>
       </c>
       <c r="W36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>0.23048327137546476</v>
       </c>
       <c r="X36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>0.22680412371134029</v>
       </c>
       <c r="Y36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>0.10658307210031337</v>
       </c>
       <c r="Z36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>9.4117647058823639E-2</v>
       </c>
       <c r="AA36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>6.3444108761329332E-2</v>
       </c>
       <c r="AB36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>-5.6022408963585235E-3</v>
       </c>
       <c r="AC36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>3.6827195467422191E-2</v>
       </c>
       <c r="AD36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>0.22580645161290325</v>
       </c>
       <c r="AE36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>4.2613636363636465E-2</v>
       </c>
       <c r="AF36" s="12">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>6.197183098591541E-2</v>
       </c>
       <c r="AG36" s="12">
-        <f t="shared" si="190"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="186"/>
+        <v>0.1502732240437159</v>
       </c>
       <c r="AH36" s="12">
-        <f t="shared" si="190"/>
-        <v>-0.13000000000000012</v>
+        <f t="shared" si="186"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AJ36" s="12"/>
       <c r="AK36" s="12">
-        <f t="shared" ref="AK36:AV36" si="191">AK14/AJ14-1</f>
+        <f t="shared" ref="AK36:AV36" si="187">AK14/AJ14-1</f>
         <v>0.18128851239780386</v>
       </c>
       <c r="AL36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="187"/>
         <v>0.10008750696078095</v>
       </c>
       <c r="AM36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="187"/>
         <v>0.12086776859504123</v>
       </c>
       <c r="AN36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="187"/>
         <v>0.12350230414746544</v>
       </c>
       <c r="AO36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="187"/>
         <v>0.1591468416735029</v>
       </c>
       <c r="AP36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="187"/>
         <v>8.2094833687190283E-2</v>
       </c>
       <c r="AQ36" s="12">
-        <f t="shared" si="191"/>
-        <v>-7.3904512753433238E-3</v>
+        <f t="shared" si="187"/>
+        <v>0.10490516677567041</v>
       </c>
       <c r="AR36" s="12">
-        <f t="shared" si="191"/>
+        <f t="shared" si="187"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AS36" s="12">
+        <f t="shared" si="187"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AT36" s="12">
+        <f t="shared" si="187"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AU36" s="12">
+        <f t="shared" si="187"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AS36" s="12">
-        <f t="shared" si="191"/>
+      <c r="AV36" s="12">
+        <f t="shared" si="187"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AT36" s="12">
-        <f t="shared" si="191"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AU36" s="12">
-        <f t="shared" si="191"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AV36" s="12">
-        <f t="shared" si="191"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AW36" s="12">
-        <f t="shared" ref="AW36:BA36" si="192">AW14/AV14-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AW36:BA36" si="188">AW14/AV14-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX36" s="12">
-        <f t="shared" si="192"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="188"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AY36" s="12">
-        <f t="shared" si="192"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="188"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ36" s="12">
-        <f t="shared" si="192"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="188"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA36" s="12">
-        <f t="shared" si="192"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="188"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC36" t="s">
         <v>49</v>
       </c>
       <c r="BD36" s="5">
         <f>BD34+BD35</f>
-        <v>142536.24752594542</v>
+        <v>151492.85412430231</v>
       </c>
     </row>
     <row r="37" spans="2:56" x14ac:dyDescent="0.3">
@@ -7027,199 +7024,199 @@
         <v>0.17000469744202942</v>
       </c>
       <c r="D37" s="12">
-        <f t="shared" ref="D37:N37" si="193">D23/D22</f>
+        <f t="shared" ref="D37:N37" si="189">D23/D22</f>
         <v>3.9998262833318858E-2</v>
       </c>
       <c r="E37" s="12">
+        <f t="shared" si="189"/>
+        <v>5.000213867145728E-2</v>
+      </c>
+      <c r="F37" s="12">
+        <f t="shared" si="189"/>
+        <v>5.0096707180209664E-2</v>
+      </c>
+      <c r="G37" s="12">
+        <f t="shared" si="189"/>
+        <v>3.9886039886039885E-2</v>
+      </c>
+      <c r="H37" s="12">
+        <f t="shared" si="189"/>
+        <v>0.10970464135021098</v>
+      </c>
+      <c r="I37" s="12">
+        <f t="shared" si="189"/>
+        <v>5.0299401197604787E-2</v>
+      </c>
+      <c r="J37" s="12">
+        <f t="shared" si="189"/>
+        <v>0.10999091070551732</v>
+      </c>
+      <c r="K37" s="12">
+        <f t="shared" si="189"/>
+        <v>-3.9173014145810661E-2</v>
+      </c>
+      <c r="L37" s="12">
+        <f t="shared" si="189"/>
+        <v>-0.1</v>
+      </c>
+      <c r="M37" s="12">
+        <f t="shared" si="189"/>
+        <v>9.9056603773584911E-2</v>
+      </c>
+      <c r="N37" s="12">
+        <f t="shared" si="189"/>
+        <v>-0.87969924812030076</v>
+      </c>
+      <c r="O37" s="12">
+        <f t="shared" ref="O37:R37" si="190">O23/O22</f>
+        <v>0.12002791346824843</v>
+      </c>
+      <c r="P37" s="12">
+        <f t="shared" si="190"/>
+        <v>0.19480519480519481</v>
+      </c>
+      <c r="Q37" s="12">
+        <f t="shared" si="190"/>
+        <v>0.14527503526093088</v>
+      </c>
+      <c r="R37" s="12">
+        <f t="shared" si="190"/>
+        <v>0.16008174386920981</v>
+      </c>
+      <c r="S37" s="12">
+        <f t="shared" ref="S37:AH37" si="191">S23/S22</f>
+        <v>0.17952041477640959</v>
+      </c>
+      <c r="T37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.21045576407506703</v>
+      </c>
+      <c r="U37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.21978021978021978</v>
+      </c>
+      <c r="V37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.22478576137112721</v>
+      </c>
+      <c r="W37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.21964956195244056</v>
+      </c>
+      <c r="X37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.21515151515151515</v>
+      </c>
+      <c r="Y37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.19506597819850832</v>
+      </c>
+      <c r="Z37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.17975663716814158</v>
+      </c>
+      <c r="AA37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.35950413223140498</v>
+      </c>
+      <c r="AB37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.18497409326424871</v>
+      </c>
+      <c r="AC37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.17531831537708129</v>
+      </c>
+      <c r="AD37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.15469613259668508</v>
+      </c>
+      <c r="AE37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.17002749770852429</v>
+      </c>
+      <c r="AF37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.1951451689671585</v>
+      </c>
+      <c r="AG37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.18021201413427562</v>
+      </c>
+      <c r="AH37" s="12">
+        <f t="shared" si="191"/>
+        <v>0.17</v>
+      </c>
+      <c r="AJ37" s="12">
+        <f t="shared" ref="AJ37:AV37" si="192">AJ23/AJ22</f>
+        <v>8.0809246255147349E-2</v>
+      </c>
+      <c r="AK37" s="12">
+        <f t="shared" si="192"/>
+        <v>7.902232954882267E-2</v>
+      </c>
+      <c r="AL37" s="12">
+        <f t="shared" si="192"/>
+        <v>-0.25957854406130271</v>
+      </c>
+      <c r="AM37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.15477651183172655</v>
+      </c>
+      <c r="AN37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.20838881491344874</v>
+      </c>
+      <c r="AO37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.20164730107368731</v>
+      </c>
+      <c r="AP37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.19780695426345404</v>
+      </c>
+      <c r="AQ37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.17971847170020927</v>
+      </c>
+      <c r="AR37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.18</v>
+      </c>
+      <c r="AS37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="AT37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.18</v>
+      </c>
+      <c r="AU37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.18</v>
+      </c>
+      <c r="AV37" s="12">
+        <f t="shared" si="192"/>
+        <v>0.18</v>
+      </c>
+      <c r="AW37" s="12">
+        <f t="shared" ref="AW37:BA37" si="193">AW23/AW22</f>
+        <v>0.18</v>
+      </c>
+      <c r="AX37" s="12">
         <f t="shared" si="193"/>
-        <v>5.000213867145728E-2</v>
-      </c>
-      <c r="F37" s="12">
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="AY37" s="12">
         <f t="shared" si="193"/>
-        <v>5.0096707180209664E-2</v>
-      </c>
-      <c r="G37" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="AZ37" s="12">
         <f t="shared" si="193"/>
-        <v>3.9886039886039885E-2</v>
-      </c>
-      <c r="H37" s="12">
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="BA37" s="12">
         <f t="shared" si="193"/>
-        <v>0.10970464135021098</v>
-      </c>
-      <c r="I37" s="12">
-        <f t="shared" si="193"/>
-        <v>5.0299401197604787E-2</v>
-      </c>
-      <c r="J37" s="12">
-        <f t="shared" si="193"/>
-        <v>0.10999091070551732</v>
-      </c>
-      <c r="K37" s="12">
-        <f t="shared" si="193"/>
-        <v>-3.9173014145810661E-2</v>
-      </c>
-      <c r="L37" s="12">
-        <f t="shared" si="193"/>
-        <v>-0.1</v>
-      </c>
-      <c r="M37" s="12">
-        <f t="shared" si="193"/>
-        <v>9.9056603773584911E-2</v>
-      </c>
-      <c r="N37" s="12">
-        <f t="shared" si="193"/>
-        <v>-0.87969924812030076</v>
-      </c>
-      <c r="O37" s="12">
-        <f t="shared" ref="O37:R37" si="194">O23/O22</f>
-        <v>0.12002791346824843</v>
-      </c>
-      <c r="P37" s="12">
-        <f t="shared" si="194"/>
-        <v>0.19480519480519481</v>
-      </c>
-      <c r="Q37" s="12">
-        <f t="shared" si="194"/>
-        <v>0.14527503526093088</v>
-      </c>
-      <c r="R37" s="12">
-        <f t="shared" si="194"/>
-        <v>0.16008174386920981</v>
-      </c>
-      <c r="S37" s="12">
-        <f t="shared" ref="S37:AH37" si="195">S23/S22</f>
-        <v>0.17952041477640959</v>
-      </c>
-      <c r="T37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.21045576407506703</v>
-      </c>
-      <c r="U37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.21978021978021978</v>
-      </c>
-      <c r="V37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.22478576137112721</v>
-      </c>
-      <c r="W37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.21964956195244056</v>
-      </c>
-      <c r="X37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.21515151515151515</v>
-      </c>
-      <c r="Y37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.19506597819850832</v>
-      </c>
-      <c r="Z37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.17975663716814158</v>
-      </c>
-      <c r="AA37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.35950413223140498</v>
-      </c>
-      <c r="AB37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.18497409326424871</v>
-      </c>
-      <c r="AC37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.17531831537708129</v>
-      </c>
-      <c r="AD37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.15469613259668508</v>
-      </c>
-      <c r="AE37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.17002749770852429</v>
-      </c>
-      <c r="AF37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.1951451689671585</v>
-      </c>
-      <c r="AG37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.17</v>
-      </c>
-      <c r="AH37" s="12">
-        <f t="shared" si="195"/>
-        <v>0.17</v>
-      </c>
-      <c r="AJ37" s="12">
-        <f t="shared" ref="AJ37:AV37" si="196">AJ23/AJ22</f>
-        <v>8.0809246255147349E-2</v>
-      </c>
-      <c r="AK37" s="12">
-        <f t="shared" si="196"/>
-        <v>7.902232954882267E-2</v>
-      </c>
-      <c r="AL37" s="12">
-        <f t="shared" si="196"/>
-        <v>-0.25957854406130271</v>
-      </c>
-      <c r="AM37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.15477651183172655</v>
-      </c>
-      <c r="AN37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.20838881491344874</v>
-      </c>
-      <c r="AO37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.20164730107368731</v>
-      </c>
-      <c r="AP37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.19780695426345404</v>
-      </c>
-      <c r="AQ37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.17621383398323182</v>
-      </c>
-      <c r="AR37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.18</v>
-      </c>
-      <c r="AS37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.18</v>
-      </c>
-      <c r="AT37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.18</v>
-      </c>
-      <c r="AU37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.18</v>
-      </c>
-      <c r="AV37" s="12">
-        <f t="shared" si="196"/>
-        <v>0.18</v>
-      </c>
-      <c r="AW37" s="12">
-        <f t="shared" ref="AW37:BA37" si="197">AW23/AW22</f>
-        <v>0.18</v>
-      </c>
-      <c r="AX37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.18</v>
-      </c>
-      <c r="AY37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.18</v>
-      </c>
-      <c r="AZ37" s="12">
-        <f t="shared" si="197"/>
-        <v>0.18</v>
-      </c>
-      <c r="BA37" s="12">
-        <f t="shared" si="197"/>
         <v>0.18</v>
       </c>
       <c r="BC37" t="s">
@@ -7227,7 +7224,7 @@
       </c>
       <c r="BD37" s="6">
         <f>BD36/AV25</f>
-        <v>336.01189892962145</v>
+        <v>363.29221612542517</v>
       </c>
     </row>
     <row r="38" spans="2:56" x14ac:dyDescent="0.3">
@@ -7235,211 +7232,211 @@
         <v>61</v>
       </c>
       <c r="C38" s="12">
-        <f t="shared" ref="C38:R38" si="198">C24/C6</f>
+        <f t="shared" ref="C38:R38" si="194">C24/C6</f>
         <v>0.28046850573606846</v>
       </c>
       <c r="D38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.30206890897164929</v>
       </c>
       <c r="E38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.29082354173577529</v>
       </c>
       <c r="F38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.18213409274045853</v>
       </c>
       <c r="G38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.25913110342176088</v>
       </c>
       <c r="H38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.23068513119533526</v>
       </c>
       <c r="I38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.27981651376146788</v>
       </c>
       <c r="J38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.28472830337506766</v>
       </c>
       <c r="K38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.30896150113231963</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.35166240409207161</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.29612403100775192</v>
       </c>
       <c r="N38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.65712616822429903</v>
       </c>
       <c r="O38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.3229193341869398</v>
       </c>
       <c r="P38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.29100391134289438</v>
       </c>
       <c r="Q38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.308005082592122</v>
       </c>
       <c r="R38" s="12">
-        <f t="shared" si="198"/>
+        <f t="shared" si="194"/>
         <v>0.3</v>
       </c>
       <c r="S38" s="12">
-        <f t="shared" ref="S38:AH38" si="199">S24/S6</f>
+        <f t="shared" ref="S38:AH38" si="195">S24/S6</f>
         <v>0.29704364148287188</v>
       </c>
       <c r="T38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.26858185134518925</v>
       </c>
       <c r="U38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.25625986916309496</v>
       </c>
       <c r="V38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.25988950276243095</v>
       </c>
       <c r="W38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.2678839957035446</v>
       </c>
       <c r="X38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.26889534883720928</v>
       </c>
       <c r="Y38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.28691206543967279</v>
       </c>
       <c r="Z38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.29377971473851028</v>
       </c>
       <c r="AA38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.11964492473948282</v>
       </c>
       <c r="AB38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.29628932002260311</v>
       </c>
       <c r="AC38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.31139053254437871</v>
       </c>
       <c r="AD38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.30021405636817694</v>
       </c>
       <c r="AE38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.31694084704235209</v>
       </c>
       <c r="AF38" s="12">
-        <f t="shared" si="199"/>
+        <f t="shared" si="195"/>
         <v>0.28792780521028433</v>
       </c>
       <c r="AG38" s="12">
-        <f t="shared" si="199"/>
-        <v>0.31848324151811575</v>
+        <f t="shared" si="195"/>
+        <v>0.29964481756538586</v>
       </c>
       <c r="AH38" s="12">
-        <f t="shared" si="199"/>
-        <v>0.31790374829696938</v>
+        <f t="shared" si="195"/>
+        <v>0.28551013491808547</v>
       </c>
       <c r="AJ38" s="12">
-        <f t="shared" ref="AJ38:AV38" si="200">AJ24/AJ6</f>
+        <f t="shared" ref="AJ38:AV38" si="196">AJ24/AJ6</f>
         <v>0.26405243698247322</v>
       </c>
       <c r="AK38" s="12">
-        <f t="shared" si="200"/>
+        <f t="shared" si="196"/>
         <v>0.26424723434196229</v>
       </c>
       <c r="AL38" s="12">
-        <f t="shared" si="200"/>
+        <f t="shared" si="196"/>
         <v>0.40876593099160707</v>
       </c>
       <c r="AM38" s="12">
-        <f t="shared" si="200"/>
+        <f t="shared" si="196"/>
         <v>0.30547988596769082</v>
       </c>
       <c r="AN38" s="12">
-        <f t="shared" si="200"/>
+        <f t="shared" si="196"/>
         <v>0.27013518118823127</v>
       </c>
       <c r="AO38" s="12">
-        <f t="shared" si="200"/>
+        <f t="shared" si="196"/>
         <v>0.27966407336802512</v>
       </c>
       <c r="AP38" s="12">
-        <f t="shared" si="200"/>
+        <f t="shared" si="196"/>
         <v>0.25854452452917925</v>
       </c>
       <c r="AQ38" s="12">
-        <f t="shared" si="200"/>
-        <v>0.30977301173314825</v>
+        <f t="shared" si="196"/>
+        <v>0.29527538218019739</v>
       </c>
       <c r="AR38" s="12">
-        <f t="shared" si="200"/>
-        <v>0.32474298943239188</v>
+        <f t="shared" si="196"/>
+        <v>0.31226269285094876</v>
       </c>
       <c r="AS38" s="12">
-        <f t="shared" si="200"/>
-        <v>0.33392637225625643</v>
+        <f t="shared" si="196"/>
+        <v>0.32836439611328283</v>
       </c>
       <c r="AT38" s="12">
-        <f t="shared" si="200"/>
-        <v>0.34093457656720699</v>
+        <f t="shared" si="196"/>
+        <v>0.33657283554515349</v>
       </c>
       <c r="AU38" s="12">
-        <f t="shared" si="200"/>
-        <v>0.3454627959422899</v>
+        <f t="shared" si="196"/>
+        <v>0.34462126501700563</v>
       </c>
       <c r="AV38" s="12">
-        <f t="shared" si="200"/>
-        <v>0.35133302849880699</v>
+        <f t="shared" si="196"/>
+        <v>0.35013673916398008</v>
       </c>
       <c r="AW38" s="12">
-        <f t="shared" ref="AW38:BA38" si="201">AW24/AW6</f>
-        <v>0.35344770368758954</v>
+        <f t="shared" ref="AW38:BA38" si="197">AW24/AW6</f>
+        <v>0.35189244165907813</v>
       </c>
       <c r="AX38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.35553842527345508</v>
+        <f t="shared" si="197"/>
+        <v>0.35362811548666406</v>
       </c>
       <c r="AY38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.3576053649291141</v>
+        <f t="shared" si="197"/>
+        <v>0.35534390179253833</v>
       </c>
       <c r="AZ38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.35964869140565164</v>
+        <f t="shared" si="197"/>
+        <v>0.35703993925609723</v>
       </c>
       <c r="BA38" s="12">
-        <f t="shared" si="201"/>
-        <v>0.36166857053688578</v>
+        <f t="shared" si="197"/>
+        <v>0.35871636409328606</v>
       </c>
       <c r="BC38" t="s">
         <v>51</v>
       </c>
       <c r="BD38" s="6">
         <f>Main!D3</f>
-        <v>350.14</v>
+        <v>271.73</v>
       </c>
     </row>
     <row r="39" spans="2:56" x14ac:dyDescent="0.3">
@@ -7448,7 +7445,7 @@
       </c>
       <c r="BD39" s="13">
         <f>BD37/BD38-1</f>
-        <v>-4.0349863112979167E-2</v>
+        <v>0.33696027720687871</v>
       </c>
     </row>
     <row r="40" spans="2:56" x14ac:dyDescent="0.3">

--- a/Financial Analysis/ADBE.xlsx
+++ b/Financial Analysis/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E347E133-1BF4-49D6-B1FE-C2D7C89CD371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5F4F72-6C65-428C-8C4B-D8C5AA4D6B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{030F5AE8-2ADC-4446-9A99-98294E370635}"/>
   </bookViews>
@@ -848,14 +848,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>271.73</v>
+        <v>261.24</v>
       </c>
       <c r="E3" s="4">
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="G3" s="4">
         <v>46093</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>113311.41</v>
+        <v>108937.08</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>39</v>
@@ -942,7 +942,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>113764.41</v>
+        <v>109390.08</v>
       </c>
     </row>
   </sheetData>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="BD38" s="6">
         <f>Main!D3</f>
-        <v>271.73</v>
+        <v>261.24</v>
       </c>
     </row>
     <row r="39" spans="2:56" x14ac:dyDescent="0.3">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="BD39" s="13">
         <f>BD37/BD38-1</f>
-        <v>0.33696027720687871</v>
+        <v>0.39064544528182954</v>
       </c>
     </row>
     <row r="40" spans="2:56" x14ac:dyDescent="0.3">
